--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="145">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,201 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Mexican Liga MX</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
+  </si>
+  <si>
+    <t>Latvian Virsliga</t>
+  </si>
+  <si>
+    <t>Swiss Super League</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>German 3 Liga</t>
+  </si>
+  <si>
+    <t>English National League</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Boyaca Chico</t>
+  </si>
+  <si>
+    <t>Puebla</t>
+  </si>
+  <si>
+    <t>El Gounah</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia</t>
+  </si>
+  <si>
+    <t>FK Auda</t>
+  </si>
+  <si>
+    <t>Thun</t>
+  </si>
+  <si>
+    <t>Lugano</t>
+  </si>
+  <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Atletico Madrid</t>
+  </si>
+  <si>
+    <t>Deportivo</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Waldhof Mannheim</t>
+  </si>
+  <si>
+    <t>Ghazl El Mahallah</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
+    <t>Preussen Munster</t>
+  </si>
+  <si>
+    <t>Altrincham</t>
+  </si>
+  <si>
+    <t>Kidderminster</t>
+  </si>
+  <si>
+    <t>Scunthorpe</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Levante</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Alianza FC Valledupar</t>
+  </si>
+  <si>
+    <t>Toluca</t>
+  </si>
+  <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>St Gallen</t>
+  </si>
+  <si>
+    <t>Mjallby</t>
+  </si>
+  <si>
+    <t>Osasuna</t>
+  </si>
+  <si>
+    <t>Sevilla</t>
+  </si>
+  <si>
+    <t>Hoffenheim II</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>Pyramids</t>
+  </si>
+  <si>
+    <t>Saarbrucken</t>
+  </si>
+  <si>
+    <t>Hartlepool</t>
+  </si>
+  <si>
+    <t>Gateshead</t>
+  </si>
+  <si>
+    <t>Boreham Wood</t>
+  </si>
+  <si>
+    <t>Racing Santander</t>
+  </si>
+  <si>
+    <t>Athletic Bilbao</t>
+  </si>
+  <si>
+    <t>2026-09-14 01:45:40</t>
   </si>
 </sst>
 </file>
@@ -585,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1023,5330 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2">
+        <v>1.86</v>
+      </c>
+      <c r="G2">
+        <v>1.96</v>
+      </c>
+      <c r="H2">
+        <v>4.4</v>
+      </c>
+      <c r="I2">
+        <v>4.7</v>
+      </c>
+      <c r="J2">
+        <v>3.8</v>
+      </c>
+      <c r="K2">
+        <v>4.1</v>
+      </c>
+      <c r="L2">
+        <v>1.35</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
+        <v>4.1</v>
+      </c>
+      <c r="O2">
+        <v>1.27</v>
+      </c>
+      <c r="P2">
+        <v>2.12</v>
+      </c>
+      <c r="Q2">
+        <v>1.79</v>
+      </c>
+      <c r="R2">
+        <v>1.45</v>
+      </c>
+      <c r="S2">
+        <v>2.98</v>
+      </c>
+      <c r="T2">
+        <v>1.74</v>
+      </c>
+      <c r="U2">
+        <v>2.24</v>
+      </c>
+      <c r="V2">
+        <v>1.27</v>
+      </c>
+      <c r="W2">
+        <v>2.04</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>970</v>
+      </c>
+      <c r="AC2">
+        <v>9</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>55</v>
+      </c>
+      <c r="AF2">
+        <v>28</v>
+      </c>
+      <c r="AG2">
+        <v>970</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>65</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>970</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.52</v>
+      </c>
+      <c r="AQ2">
+        <v>1.52</v>
+      </c>
+      <c r="AR2">
+        <v>1.52</v>
+      </c>
+      <c r="AS2">
+        <v>1.52</v>
+      </c>
+      <c r="AT2">
+        <v>7.4</v>
+      </c>
+      <c r="AU2">
+        <v>7.8</v>
+      </c>
+      <c r="AV2">
+        <v>1.52</v>
+      </c>
+      <c r="AW2">
+        <v>1.48</v>
+      </c>
+      <c r="AX2">
+        <v>8.4</v>
+      </c>
+      <c r="AY2">
+        <v>7.2</v>
+      </c>
+      <c r="AZ2">
+        <v>1.52</v>
+      </c>
+      <c r="BA2">
+        <v>1.48</v>
+      </c>
+      <c r="BB2">
+        <v>1.52</v>
+      </c>
+      <c r="BC2">
+        <v>1.52</v>
+      </c>
+      <c r="BD2">
+        <v>1.52</v>
+      </c>
+      <c r="BE2">
+        <v>1.52</v>
+      </c>
+      <c r="BF2">
+        <v>1.41</v>
+      </c>
+      <c r="BG2">
+        <v>1.52</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.23</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.19</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.19</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.32</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.19</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.19</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.74</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.19</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.19</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.19</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3">
+        <v>2.3</v>
+      </c>
+      <c r="G3">
+        <v>2.7</v>
+      </c>
+      <c r="H3">
+        <v>3.2</v>
+      </c>
+      <c r="I3">
+        <v>3.85</v>
+      </c>
+      <c r="J3">
+        <v>2.96</v>
+      </c>
+      <c r="K3">
+        <v>3.85</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.08</v>
+      </c>
+      <c r="N3">
+        <v>2.58</v>
+      </c>
+      <c r="O3">
+        <v>1.51</v>
+      </c>
+      <c r="P3">
+        <v>1.53</v>
+      </c>
+      <c r="Q3">
+        <v>2.42</v>
+      </c>
+      <c r="R3">
+        <v>1.18</v>
+      </c>
+      <c r="S3">
+        <v>4.2</v>
+      </c>
+      <c r="T3">
+        <v>2.02</v>
+      </c>
+      <c r="U3">
+        <v>1.71</v>
+      </c>
+      <c r="V3">
+        <v>1.36</v>
+      </c>
+      <c r="W3">
+        <v>1.59</v>
+      </c>
+      <c r="X3">
+        <v>970</v>
+      </c>
+      <c r="Y3">
+        <v>970</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>13.5</v>
+      </c>
+      <c r="AC3">
+        <v>12</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>38</v>
+      </c>
+      <c r="AG3">
+        <v>36</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.4</v>
+      </c>
+      <c r="AQ3">
+        <v>1.41</v>
+      </c>
+      <c r="AR3">
+        <v>1.54</v>
+      </c>
+      <c r="AS3">
+        <v>1.54</v>
+      </c>
+      <c r="AT3">
+        <v>5.8</v>
+      </c>
+      <c r="AU3">
+        <v>5.6</v>
+      </c>
+      <c r="AV3">
+        <v>1.54</v>
+      </c>
+      <c r="AW3">
+        <v>1.54</v>
+      </c>
+      <c r="AX3">
+        <v>7.2</v>
+      </c>
+      <c r="AY3">
+        <v>7.2</v>
+      </c>
+      <c r="AZ3">
+        <v>1.54</v>
+      </c>
+      <c r="BA3">
+        <v>1.54</v>
+      </c>
+      <c r="BB3">
+        <v>1.54</v>
+      </c>
+      <c r="BC3">
+        <v>1.54</v>
+      </c>
+      <c r="BD3">
+        <v>1.54</v>
+      </c>
+      <c r="BE3">
+        <v>1.54</v>
+      </c>
+      <c r="BF3">
+        <v>1.54</v>
+      </c>
+      <c r="BG3">
+        <v>1.54</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>5.3</v>
+      </c>
+      <c r="H4">
+        <v>1.69</v>
+      </c>
+      <c r="I4">
+        <v>1.73</v>
+      </c>
+      <c r="J4">
+        <v>4.4</v>
+      </c>
+      <c r="K4">
+        <v>4.6</v>
+      </c>
+      <c r="L4">
+        <v>1.26</v>
+      </c>
+      <c r="M4">
+        <v>1.02</v>
+      </c>
+      <c r="N4">
+        <v>5.2</v>
+      </c>
+      <c r="O4">
+        <v>1.21</v>
+      </c>
+      <c r="P4">
+        <v>2.46</v>
+      </c>
+      <c r="Q4">
+        <v>1.63</v>
+      </c>
+      <c r="R4">
+        <v>1.58</v>
+      </c>
+      <c r="S4">
+        <v>2.58</v>
+      </c>
+      <c r="T4">
+        <v>1.68</v>
+      </c>
+      <c r="U4">
+        <v>2.32</v>
+      </c>
+      <c r="V4">
+        <v>2.36</v>
+      </c>
+      <c r="W4">
+        <v>1.23</v>
+      </c>
+      <c r="X4">
+        <v>28</v>
+      </c>
+      <c r="Y4">
+        <v>14</v>
+      </c>
+      <c r="Z4">
+        <v>12.5</v>
+      </c>
+      <c r="AA4">
+        <v>22</v>
+      </c>
+      <c r="AB4">
+        <v>28</v>
+      </c>
+      <c r="AC4">
+        <v>10.5</v>
+      </c>
+      <c r="AD4">
+        <v>10.5</v>
+      </c>
+      <c r="AE4">
+        <v>20</v>
+      </c>
+      <c r="AF4">
+        <v>55</v>
+      </c>
+      <c r="AG4">
+        <v>25</v>
+      </c>
+      <c r="AH4">
+        <v>22</v>
+      </c>
+      <c r="AI4">
+        <v>34</v>
+      </c>
+      <c r="AJ4">
+        <v>130</v>
+      </c>
+      <c r="AK4">
+        <v>70</v>
+      </c>
+      <c r="AL4">
+        <v>65</v>
+      </c>
+      <c r="AM4">
+        <v>90</v>
+      </c>
+      <c r="AN4">
+        <v>60</v>
+      </c>
+      <c r="AO4">
+        <v>7.8</v>
+      </c>
+      <c r="AP4">
+        <v>17</v>
+      </c>
+      <c r="AQ4">
+        <v>10</v>
+      </c>
+      <c r="AR4">
+        <v>10.5</v>
+      </c>
+      <c r="AS4">
+        <v>15.5</v>
+      </c>
+      <c r="AT4">
+        <v>20</v>
+      </c>
+      <c r="AU4">
+        <v>9.4</v>
+      </c>
+      <c r="AV4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW4">
+        <v>14.5</v>
+      </c>
+      <c r="AX4">
+        <v>6</v>
+      </c>
+      <c r="AY4">
+        <v>17.5</v>
+      </c>
+      <c r="AZ4">
+        <v>15.5</v>
+      </c>
+      <c r="BA4">
+        <v>5.5</v>
+      </c>
+      <c r="BB4">
+        <v>6.4</v>
+      </c>
+      <c r="BC4">
+        <v>6</v>
+      </c>
+      <c r="BD4">
+        <v>6</v>
+      </c>
+      <c r="BE4">
+        <v>6.2</v>
+      </c>
+      <c r="BF4">
+        <v>6</v>
+      </c>
+      <c r="BG4">
+        <v>6.8</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>3.45</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>6.6</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>6.4</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>3.75</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>7.4</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>9.6</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3.6</v>
+      </c>
+      <c r="H5">
+        <v>2.54</v>
+      </c>
+      <c r="I5">
+        <v>3.3</v>
+      </c>
+      <c r="J5">
+        <v>2.78</v>
+      </c>
+      <c r="K5">
+        <v>3.2</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.45</v>
+      </c>
+      <c r="Q5">
+        <v>2.46</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6">
+        <v>5.4</v>
+      </c>
+      <c r="G6">
+        <v>6.4</v>
+      </c>
+      <c r="H6">
+        <v>1.59</v>
+      </c>
+      <c r="I6">
+        <v>1.69</v>
+      </c>
+      <c r="J6">
+        <v>4.3</v>
+      </c>
+      <c r="K6">
+        <v>4.8</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>2.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7">
+        <v>1.04</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>1.04</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.01</v>
+      </c>
+      <c r="K7">
+        <v>880</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.24</v>
+      </c>
+      <c r="Q7">
+        <v>1.02</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8">
+        <v>2.76</v>
+      </c>
+      <c r="G8">
+        <v>2.98</v>
+      </c>
+      <c r="H8">
+        <v>2.32</v>
+      </c>
+      <c r="I8">
+        <v>2.5</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>4.5</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>2.8</v>
+      </c>
+      <c r="Q8">
+        <v>1.47</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9">
+        <v>1.1</v>
+      </c>
+      <c r="G9">
+        <v>2.3</v>
+      </c>
+      <c r="H9">
+        <v>1.29</v>
+      </c>
+      <c r="I9">
+        <v>10.5</v>
+      </c>
+      <c r="J9">
+        <v>3.7</v>
+      </c>
+      <c r="K9">
+        <v>5.3</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>2.58</v>
+      </c>
+      <c r="Q9">
+        <v>1.37</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>2.24</v>
+      </c>
+      <c r="G10">
+        <v>2.34</v>
+      </c>
+      <c r="H10">
+        <v>3.25</v>
+      </c>
+      <c r="I10">
+        <v>3.4</v>
+      </c>
+      <c r="J10">
+        <v>3.7</v>
+      </c>
+      <c r="K10">
+        <v>3.95</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.12</v>
+      </c>
+      <c r="Q10">
+        <v>1.72</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11">
+        <v>1.47</v>
+      </c>
+      <c r="G11">
+        <v>1.49</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>8.4</v>
+      </c>
+      <c r="J11">
+        <v>4.9</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.05</v>
+      </c>
+      <c r="N11">
+        <v>4.5</v>
+      </c>
+      <c r="O11">
+        <v>1.27</v>
+      </c>
+      <c r="P11">
+        <v>2.18</v>
+      </c>
+      <c r="Q11">
+        <v>1.79</v>
+      </c>
+      <c r="R11">
+        <v>1.46</v>
+      </c>
+      <c r="S11">
+        <v>3</v>
+      </c>
+      <c r="T11">
+        <v>2</v>
+      </c>
+      <c r="U11">
+        <v>1.94</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>20</v>
+      </c>
+      <c r="Y11">
+        <v>27</v>
+      </c>
+      <c r="Z11">
+        <v>75</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>8.6</v>
+      </c>
+      <c r="AC11">
+        <v>11</v>
+      </c>
+      <c r="AD11">
+        <v>32</v>
+      </c>
+      <c r="AE11">
+        <v>130</v>
+      </c>
+      <c r="AF11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+      <c r="AH11">
+        <v>25</v>
+      </c>
+      <c r="AI11">
+        <v>110</v>
+      </c>
+      <c r="AJ11">
+        <v>13</v>
+      </c>
+      <c r="AK11">
+        <v>16</v>
+      </c>
+      <c r="AL11">
+        <v>38</v>
+      </c>
+      <c r="AM11">
+        <v>140</v>
+      </c>
+      <c r="AN11">
+        <v>7</v>
+      </c>
+      <c r="AO11">
+        <v>170</v>
+      </c>
+      <c r="AP11">
+        <v>17</v>
+      </c>
+      <c r="AQ11">
+        <v>18</v>
+      </c>
+      <c r="AR11">
+        <v>30</v>
+      </c>
+      <c r="AS11">
+        <v>48</v>
+      </c>
+      <c r="AT11">
+        <v>8</v>
+      </c>
+      <c r="AU11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV11">
+        <v>19.5</v>
+      </c>
+      <c r="AW11">
+        <v>40</v>
+      </c>
+      <c r="AX11">
+        <v>8</v>
+      </c>
+      <c r="AY11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11">
+        <v>21</v>
+      </c>
+      <c r="BA11">
+        <v>38</v>
+      </c>
+      <c r="BB11">
+        <v>11.5</v>
+      </c>
+      <c r="BC11">
+        <v>13.5</v>
+      </c>
+      <c r="BD11">
+        <v>22</v>
+      </c>
+      <c r="BE11">
+        <v>42</v>
+      </c>
+      <c r="BF11">
+        <v>6.4</v>
+      </c>
+      <c r="BG11">
+        <v>42</v>
+      </c>
+      <c r="BH11">
+        <v>3.85</v>
+      </c>
+      <c r="BI11">
+        <v>3.6</v>
+      </c>
+      <c r="BJ11">
+        <v>13</v>
+      </c>
+      <c r="BK11">
+        <v>5.5</v>
+      </c>
+      <c r="BL11">
+        <v>160</v>
+      </c>
+      <c r="BM11">
+        <v>8.6</v>
+      </c>
+      <c r="BN11">
+        <v>3.95</v>
+      </c>
+      <c r="BO11">
+        <v>3.65</v>
+      </c>
+      <c r="BP11">
+        <v>10.5</v>
+      </c>
+      <c r="BQ11">
+        <v>7.8</v>
+      </c>
+      <c r="BR11">
+        <v>27</v>
+      </c>
+      <c r="BS11">
+        <v>6.8</v>
+      </c>
+      <c r="BT11">
+        <v>13</v>
+      </c>
+      <c r="BU11">
+        <v>5.6</v>
+      </c>
+      <c r="BV11">
+        <v>75</v>
+      </c>
+      <c r="BW11">
+        <v>8</v>
+      </c>
+      <c r="BX11">
+        <v>75</v>
+      </c>
+      <c r="BY11">
+        <v>8</v>
+      </c>
+      <c r="BZ11">
+        <v>17</v>
+      </c>
+      <c r="CA11">
+        <v>5.9</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12">
+        <v>2.6</v>
+      </c>
+      <c r="G12">
+        <v>2.64</v>
+      </c>
+      <c r="H12">
+        <v>3.2</v>
+      </c>
+      <c r="I12">
+        <v>3.3</v>
+      </c>
+      <c r="J12">
+        <v>3.15</v>
+      </c>
+      <c r="K12">
+        <v>3.2</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1.11</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12">
+        <v>1.47</v>
+      </c>
+      <c r="P12">
+        <v>1.67</v>
+      </c>
+      <c r="Q12">
+        <v>2.4</v>
+      </c>
+      <c r="R12">
+        <v>1.25</v>
+      </c>
+      <c r="S12">
+        <v>4.8</v>
+      </c>
+      <c r="T12">
+        <v>1.99</v>
+      </c>
+      <c r="U12">
+        <v>1.95</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>10</v>
+      </c>
+      <c r="Y12">
+        <v>10.5</v>
+      </c>
+      <c r="Z12">
+        <v>21</v>
+      </c>
+      <c r="AA12">
+        <v>65</v>
+      </c>
+      <c r="AB12">
+        <v>9</v>
+      </c>
+      <c r="AC12">
+        <v>7</v>
+      </c>
+      <c r="AD12">
+        <v>15</v>
+      </c>
+      <c r="AE12">
+        <v>46</v>
+      </c>
+      <c r="AF12">
+        <v>16</v>
+      </c>
+      <c r="AG12">
+        <v>12.5</v>
+      </c>
+      <c r="AH12">
+        <v>21</v>
+      </c>
+      <c r="AI12">
+        <v>65</v>
+      </c>
+      <c r="AJ12">
+        <v>40</v>
+      </c>
+      <c r="AK12">
+        <v>34</v>
+      </c>
+      <c r="AL12">
+        <v>55</v>
+      </c>
+      <c r="AM12">
+        <v>140</v>
+      </c>
+      <c r="AN12">
+        <v>36</v>
+      </c>
+      <c r="AO12">
+        <v>55</v>
+      </c>
+      <c r="AP12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ12">
+        <v>9.4</v>
+      </c>
+      <c r="AR12">
+        <v>18</v>
+      </c>
+      <c r="AS12">
+        <v>29</v>
+      </c>
+      <c r="AT12">
+        <v>8</v>
+      </c>
+      <c r="AU12">
+        <v>6.6</v>
+      </c>
+      <c r="AV12">
+        <v>13</v>
+      </c>
+      <c r="AW12">
+        <v>32</v>
+      </c>
+      <c r="AX12">
+        <v>13.5</v>
+      </c>
+      <c r="AY12">
+        <v>11</v>
+      </c>
+      <c r="AZ12">
+        <v>18</v>
+      </c>
+      <c r="BA12">
+        <v>32</v>
+      </c>
+      <c r="BB12">
+        <v>23</v>
+      </c>
+      <c r="BC12">
+        <v>21</v>
+      </c>
+      <c r="BD12">
+        <v>29</v>
+      </c>
+      <c r="BE12">
+        <v>44</v>
+      </c>
+      <c r="BF12">
+        <v>21</v>
+      </c>
+      <c r="BG12">
+        <v>36</v>
+      </c>
+      <c r="BH12">
+        <v>2.88</v>
+      </c>
+      <c r="BI12">
+        <v>2.74</v>
+      </c>
+      <c r="BJ12">
+        <v>12.5</v>
+      </c>
+      <c r="BK12">
+        <v>4.5</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>6.4</v>
+      </c>
+      <c r="BN12">
+        <v>6.4</v>
+      </c>
+      <c r="BO12">
+        <v>4.9</v>
+      </c>
+      <c r="BP12">
+        <v>26</v>
+      </c>
+      <c r="BQ12">
+        <v>5.2</v>
+      </c>
+      <c r="BR12">
+        <v>48</v>
+      </c>
+      <c r="BS12">
+        <v>5.8</v>
+      </c>
+      <c r="BT12">
+        <v>7.4</v>
+      </c>
+      <c r="BU12">
+        <v>5.6</v>
+      </c>
+      <c r="BV12">
+        <v>34</v>
+      </c>
+      <c r="BW12">
+        <v>5.5</v>
+      </c>
+      <c r="BX12">
+        <v>55</v>
+      </c>
+      <c r="BY12">
+        <v>5.9</v>
+      </c>
+      <c r="BZ12">
+        <v>48</v>
+      </c>
+      <c r="CA12">
+        <v>5.8</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F13">
+        <v>1.89</v>
+      </c>
+      <c r="G13">
+        <v>2.32</v>
+      </c>
+      <c r="H13">
+        <v>3.4</v>
+      </c>
+      <c r="I13">
+        <v>5.1</v>
+      </c>
+      <c r="J13">
+        <v>3.65</v>
+      </c>
+      <c r="K13">
+        <v>5.7</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.56</v>
+      </c>
+      <c r="Q13">
+        <v>1.43</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14">
+        <v>1.52</v>
+      </c>
+      <c r="G14">
+        <v>1.73</v>
+      </c>
+      <c r="H14">
+        <v>4.9</v>
+      </c>
+      <c r="I14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J14">
+        <v>4.6</v>
+      </c>
+      <c r="K14">
+        <v>7.4</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>3</v>
+      </c>
+      <c r="Q14">
+        <v>1.35</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15">
+        <v>2.84</v>
+      </c>
+      <c r="G15">
+        <v>3.25</v>
+      </c>
+      <c r="H15">
+        <v>2.22</v>
+      </c>
+      <c r="I15">
+        <v>2.52</v>
+      </c>
+      <c r="J15">
+        <v>3.35</v>
+      </c>
+      <c r="K15">
+        <v>4.5</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>2.48</v>
+      </c>
+      <c r="Q15">
+        <v>1.54</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16">
+        <v>5.3</v>
+      </c>
+      <c r="G16">
+        <v>10.5</v>
+      </c>
+      <c r="H16">
+        <v>1.69</v>
+      </c>
+      <c r="I16">
+        <v>1.89</v>
+      </c>
+      <c r="J16">
+        <v>3.2</v>
+      </c>
+      <c r="K16">
+        <v>3.95</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.63</v>
+      </c>
+      <c r="Q16">
+        <v>1.01</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17">
+        <v>1.29</v>
+      </c>
+      <c r="G17">
+        <v>22</v>
+      </c>
+      <c r="H17">
+        <v>1.47</v>
+      </c>
+      <c r="I17">
+        <v>1000</v>
+      </c>
+      <c r="J17">
+        <v>3.65</v>
+      </c>
+      <c r="K17">
+        <v>4.4</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1.58</v>
+      </c>
+      <c r="Q17">
+        <v>1.01</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18">
+        <v>1.04</v>
+      </c>
+      <c r="G18">
+        <v>1000</v>
+      </c>
+      <c r="H18">
+        <v>1.04</v>
+      </c>
+      <c r="I18">
+        <v>1000</v>
+      </c>
+      <c r="J18">
+        <v>1.01</v>
+      </c>
+      <c r="K18">
+        <v>1000</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.24</v>
+      </c>
+      <c r="Q18">
+        <v>1.01</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19">
+        <v>2.28</v>
+      </c>
+      <c r="G19">
+        <v>2.66</v>
+      </c>
+      <c r="H19">
+        <v>2.82</v>
+      </c>
+      <c r="I19">
+        <v>3.45</v>
+      </c>
+      <c r="J19">
+        <v>3.6</v>
+      </c>
+      <c r="K19">
+        <v>4.9</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2</v>
+      </c>
+      <c r="Q19">
+        <v>1.75</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20">
+        <v>1.68</v>
+      </c>
+      <c r="G20">
+        <v>1.87</v>
+      </c>
+      <c r="H20">
+        <v>4.6</v>
+      </c>
+      <c r="I20">
+        <v>7</v>
+      </c>
+      <c r="J20">
+        <v>3.85</v>
+      </c>
+      <c r="K20">
+        <v>5.3</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>1.98</v>
+      </c>
+      <c r="Q20">
+        <v>1.78</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21">
+        <v>3.95</v>
+      </c>
+      <c r="G21">
+        <v>5.8</v>
+      </c>
+      <c r="H21">
+        <v>1.74</v>
+      </c>
+      <c r="I21">
+        <v>1.96</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="K21">
+        <v>5.9</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2.56</v>
+      </c>
+      <c r="Q21">
+        <v>1.01</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22">
+        <v>1.07</v>
+      </c>
+      <c r="G22">
+        <v>1.08</v>
+      </c>
+      <c r="H22">
+        <v>36</v>
+      </c>
+      <c r="I22">
+        <v>40</v>
+      </c>
+      <c r="J22">
+        <v>22</v>
+      </c>
+      <c r="K22">
+        <v>24</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>17.5</v>
+      </c>
+      <c r="O22">
+        <v>1.05</v>
+      </c>
+      <c r="P22">
+        <v>6.8</v>
+      </c>
+      <c r="Q22">
+        <v>1.15</v>
+      </c>
+      <c r="R22">
+        <v>3.3</v>
+      </c>
+      <c r="S22">
+        <v>1.42</v>
+      </c>
+      <c r="T22">
+        <v>1.98</v>
+      </c>
+      <c r="U22">
+        <v>1.96</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>240</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>480</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>27</v>
+      </c>
+      <c r="AC22">
+        <v>1000</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>540</v>
+      </c>
+      <c r="AF22">
+        <v>15</v>
+      </c>
+      <c r="AG22">
+        <v>19.5</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>10.5</v>
+      </c>
+      <c r="AK22">
+        <v>16.5</v>
+      </c>
+      <c r="AL22">
+        <v>40</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1.79</v>
+      </c>
+      <c r="AO22">
+        <v>340</v>
+      </c>
+      <c r="AP22">
+        <v>46</v>
+      </c>
+      <c r="AQ22">
+        <v>46</v>
+      </c>
+      <c r="AR22">
+        <v>95</v>
+      </c>
+      <c r="AS22">
+        <v>95</v>
+      </c>
+      <c r="AT22">
+        <v>22</v>
+      </c>
+      <c r="AU22">
+        <v>30</v>
+      </c>
+      <c r="AV22">
+        <v>40</v>
+      </c>
+      <c r="AW22">
+        <v>55</v>
+      </c>
+      <c r="AX22">
+        <v>12.5</v>
+      </c>
+      <c r="AY22">
+        <v>17.5</v>
+      </c>
+      <c r="AZ22">
+        <v>34</v>
+      </c>
+      <c r="BA22">
+        <v>48</v>
+      </c>
+      <c r="BB22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC22">
+        <v>14.5</v>
+      </c>
+      <c r="BD22">
+        <v>23</v>
+      </c>
+      <c r="BE22">
+        <v>100</v>
+      </c>
+      <c r="BF22">
+        <v>1.73</v>
+      </c>
+      <c r="BG22">
+        <v>95</v>
+      </c>
+      <c r="BH22">
+        <v>12</v>
+      </c>
+      <c r="BI22">
+        <v>3.45</v>
+      </c>
+      <c r="BJ22">
+        <v>17.5</v>
+      </c>
+      <c r="BK22">
+        <v>3.85</v>
+      </c>
+      <c r="BL22">
+        <v>120</v>
+      </c>
+      <c r="BM22">
+        <v>4.6</v>
+      </c>
+      <c r="BN22">
+        <v>5.9</v>
+      </c>
+      <c r="BO22">
+        <v>4.3</v>
+      </c>
+      <c r="BP22">
+        <v>6.8</v>
+      </c>
+      <c r="BQ22">
+        <v>4.9</v>
+      </c>
+      <c r="BR22">
+        <v>19.5</v>
+      </c>
+      <c r="BS22">
+        <v>3.95</v>
+      </c>
+      <c r="BT22">
+        <v>32</v>
+      </c>
+      <c r="BU22">
+        <v>4.1</v>
+      </c>
+      <c r="BV22">
+        <v>170</v>
+      </c>
+      <c r="BW22">
+        <v>4.6</v>
+      </c>
+      <c r="BX22">
+        <v>100</v>
+      </c>
+      <c r="BY22">
+        <v>4.5</v>
+      </c>
+      <c r="BZ22">
+        <v>4.4</v>
+      </c>
+      <c r="CA22">
+        <v>3</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23">
+        <v>3.6</v>
+      </c>
+      <c r="G23">
+        <v>3.65</v>
+      </c>
+      <c r="H23">
+        <v>2.2</v>
+      </c>
+      <c r="I23">
+        <v>2.22</v>
+      </c>
+      <c r="J23">
+        <v>3.6</v>
+      </c>
+      <c r="K23">
+        <v>3.7</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1.07</v>
+      </c>
+      <c r="N23">
+        <v>4.1</v>
+      </c>
+      <c r="O23">
+        <v>1.31</v>
+      </c>
+      <c r="P23">
+        <v>2.06</v>
+      </c>
+      <c r="Q23">
+        <v>1.9</v>
+      </c>
+      <c r="R23">
+        <v>1.4</v>
+      </c>
+      <c r="S23">
+        <v>3.3</v>
+      </c>
+      <c r="T23">
+        <v>1.75</v>
+      </c>
+      <c r="U23">
+        <v>2.26</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>15.5</v>
+      </c>
+      <c r="Y23">
+        <v>10.5</v>
+      </c>
+      <c r="Z23">
+        <v>14.5</v>
+      </c>
+      <c r="AA23">
+        <v>28</v>
+      </c>
+      <c r="AB23">
+        <v>14.5</v>
+      </c>
+      <c r="AC23">
+        <v>8</v>
+      </c>
+      <c r="AD23">
+        <v>11</v>
+      </c>
+      <c r="AE23">
+        <v>24</v>
+      </c>
+      <c r="AF23">
+        <v>27</v>
+      </c>
+      <c r="AG23">
+        <v>15</v>
+      </c>
+      <c r="AH23">
+        <v>17</v>
+      </c>
+      <c r="AI23">
+        <v>38</v>
+      </c>
+      <c r="AJ23">
+        <v>70</v>
+      </c>
+      <c r="AK23">
+        <v>42</v>
+      </c>
+      <c r="AL23">
+        <v>50</v>
+      </c>
+      <c r="AM23">
+        <v>85</v>
+      </c>
+      <c r="AN23">
+        <v>40</v>
+      </c>
+      <c r="AO23">
+        <v>15.5</v>
+      </c>
+      <c r="AP23">
+        <v>14</v>
+      </c>
+      <c r="AQ23">
+        <v>9.6</v>
+      </c>
+      <c r="AR23">
+        <v>12.5</v>
+      </c>
+      <c r="AS23">
+        <v>18</v>
+      </c>
+      <c r="AT23">
+        <v>13</v>
+      </c>
+      <c r="AU23">
+        <v>7.4</v>
+      </c>
+      <c r="AV23">
+        <v>10</v>
+      </c>
+      <c r="AW23">
+        <v>19</v>
+      </c>
+      <c r="AX23">
+        <v>21</v>
+      </c>
+      <c r="AY23">
+        <v>13.5</v>
+      </c>
+      <c r="AZ23">
+        <v>15</v>
+      </c>
+      <c r="BA23">
+        <v>23</v>
+      </c>
+      <c r="BB23">
+        <v>30</v>
+      </c>
+      <c r="BC23">
+        <v>23</v>
+      </c>
+      <c r="BD23">
+        <v>27</v>
+      </c>
+      <c r="BE23">
+        <v>36</v>
+      </c>
+      <c r="BF23">
+        <v>23</v>
+      </c>
+      <c r="BG23">
+        <v>14</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.01</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.01</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.01</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.01</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.01</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.01</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="143">
   <si>
     <t>League</t>
   </si>
@@ -349,6 +349,9 @@
     <t>Deportivo</t>
   </si>
   <si>
+    <t>Preussen Munster</t>
+  </si>
+  <si>
     <t>Ingolstadt</t>
   </si>
   <si>
@@ -361,12 +364,6 @@
     <t>Ghazl El Mahallah</t>
   </si>
   <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
-    <t>Preussen Munster</t>
-  </si>
-  <si>
     <t>Altrincham</t>
   </si>
   <si>
@@ -415,6 +412,9 @@
     <t>Sevilla</t>
   </si>
   <si>
+    <t>Saarbrucken</t>
+  </si>
+  <si>
     <t>Hoffenheim II</t>
   </si>
   <si>
@@ -427,12 +427,6 @@
     <t>Zamalek</t>
   </si>
   <si>
-    <t>Pyramids</t>
-  </si>
-  <si>
-    <t>Saarbrucken</t>
-  </si>
-  <si>
     <t>Hartlepool</t>
   </si>
   <si>
@@ -448,7 +442,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-09-14 01:45:40</t>
+    <t>2026-09-14 04:00:46</t>
   </si>
 </sst>
 </file>
@@ -780,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1039,7 +1033,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F2">
         <v>1.86</v>
@@ -1054,7 +1048,7 @@
         <v>4.7</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K2">
         <v>4.1</v>
@@ -1066,7 +1060,7 @@
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
         <v>1.27</v>
@@ -1087,7 +1081,7 @@
         <v>1.74</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.27</v>
@@ -1096,112 +1090,112 @@
         <v>2.04</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB2">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC2">
         <v>9</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE2">
         <v>55</v>
       </c>
       <c r="AF2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI2">
         <v>65</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN2">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP2">
-        <v>1.52</v>
+        <v>15</v>
       </c>
       <c r="AQ2">
-        <v>1.52</v>
+        <v>15</v>
       </c>
       <c r="AR2">
-        <v>1.52</v>
+        <v>7</v>
       </c>
       <c r="AS2">
-        <v>1.52</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
+        <v>9</v>
+      </c>
+      <c r="AU2">
+        <v>8</v>
+      </c>
+      <c r="AV2">
+        <v>15</v>
+      </c>
+      <c r="AW2">
+        <v>7.2</v>
+      </c>
+      <c r="AX2">
+        <v>10.5</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>15</v>
+      </c>
+      <c r="BA2">
         <v>7.4</v>
       </c>
-      <c r="AU2">
+      <c r="BB2">
+        <v>18</v>
+      </c>
+      <c r="BC2">
+        <v>16</v>
+      </c>
+      <c r="BD2">
+        <v>6.8</v>
+      </c>
+      <c r="BE2">
         <v>7.8</v>
       </c>
-      <c r="AV2">
-        <v>1.52</v>
-      </c>
-      <c r="AW2">
-        <v>1.48</v>
-      </c>
-      <c r="AX2">
-        <v>8.4</v>
-      </c>
-      <c r="AY2">
-        <v>7.2</v>
-      </c>
-      <c r="AZ2">
-        <v>1.52</v>
-      </c>
-      <c r="BA2">
-        <v>1.48</v>
-      </c>
-      <c r="BB2">
-        <v>1.52</v>
-      </c>
-      <c r="BC2">
-        <v>1.52</v>
-      </c>
-      <c r="BD2">
-        <v>1.52</v>
-      </c>
-      <c r="BE2">
-        <v>1.52</v>
-      </c>
       <c r="BF2">
-        <v>1.41</v>
+        <v>10</v>
       </c>
       <c r="BG2">
-        <v>1.52</v>
+        <v>7.4</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1264,7 +1258,7 @@
         <v>1.19</v>
       </c>
       <c r="CB2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1281,169 +1275,169 @@
         <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G3">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="O3">
         <v>1.51</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB3">
+        <v>7.8</v>
+      </c>
+      <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>19</v>
+      </c>
+      <c r="AE3">
+        <v>65</v>
+      </c>
+      <c r="AF3">
+        <v>15</v>
+      </c>
+      <c r="AG3">
+        <v>15</v>
+      </c>
+      <c r="AH3">
+        <v>25</v>
+      </c>
+      <c r="AI3">
+        <v>90</v>
+      </c>
+      <c r="AJ3">
+        <v>46</v>
+      </c>
+      <c r="AK3">
+        <v>42</v>
+      </c>
+      <c r="AL3">
+        <v>75</v>
+      </c>
+      <c r="AM3">
+        <v>210</v>
+      </c>
+      <c r="AN3">
+        <v>42</v>
+      </c>
+      <c r="AO3">
+        <v>90</v>
+      </c>
+      <c r="AP3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR3">
+        <v>20</v>
+      </c>
+      <c r="AS3">
+        <v>6.8</v>
+      </c>
+      <c r="AT3">
+        <v>7</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
         <v>13.5</v>
       </c>
-      <c r="AC3">
-        <v>12</v>
-      </c>
-      <c r="AD3">
-        <v>1000</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>38</v>
-      </c>
-      <c r="AG3">
-        <v>36</v>
-      </c>
-      <c r="AH3">
-        <v>1000</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>1.4</v>
-      </c>
-      <c r="AQ3">
-        <v>1.41</v>
-      </c>
-      <c r="AR3">
-        <v>1.54</v>
-      </c>
-      <c r="AS3">
-        <v>1.54</v>
-      </c>
-      <c r="AT3">
-        <v>5.8</v>
-      </c>
-      <c r="AU3">
+      <c r="AW3">
+        <v>6.6</v>
+      </c>
+      <c r="AX3">
+        <v>12.5</v>
+      </c>
+      <c r="AY3">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3">
         <v>5.6</v>
       </c>
-      <c r="AV3">
-        <v>1.54</v>
-      </c>
-      <c r="AW3">
-        <v>1.54</v>
-      </c>
-      <c r="AX3">
-        <v>7.2</v>
-      </c>
-      <c r="AY3">
-        <v>7.2</v>
-      </c>
-      <c r="AZ3">
-        <v>1.54</v>
-      </c>
       <c r="BA3">
-        <v>1.54</v>
+        <v>6.8</v>
       </c>
       <c r="BB3">
-        <v>1.54</v>
+        <v>6.4</v>
       </c>
       <c r="BC3">
-        <v>1.54</v>
+        <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>1.54</v>
+        <v>6.8</v>
       </c>
       <c r="BE3">
-        <v>1.54</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
-        <v>1.54</v>
+        <v>6.2</v>
       </c>
       <c r="BG3">
-        <v>1.54</v>
+        <v>6.8</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1506,7 +1500,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1523,10 +1517,10 @@
         <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G4">
         <v>5.3</v>
@@ -1535,7 +1529,7 @@
         <v>1.69</v>
       </c>
       <c r="I4">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J4">
         <v>4.4</v>
@@ -1550,7 +1544,7 @@
         <v>1.02</v>
       </c>
       <c r="N4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O4">
         <v>1.21</v>
@@ -1562,19 +1556,19 @@
         <v>1.63</v>
       </c>
       <c r="R4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T4">
         <v>1.68</v>
       </c>
       <c r="U4">
+        <v>2.34</v>
+      </c>
+      <c r="V4">
         <v>2.32</v>
-      </c>
-      <c r="V4">
-        <v>2.36</v>
       </c>
       <c r="W4">
         <v>1.23</v>
@@ -1607,7 +1601,7 @@
         <v>55</v>
       </c>
       <c r="AG4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH4">
         <v>22</v>
@@ -1748,7 +1742,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1765,25 +1759,25 @@
         <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G5">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I5">
+        <v>3.45</v>
+      </c>
+      <c r="J5">
+        <v>2.6</v>
+      </c>
+      <c r="K5">
         <v>3.3</v>
-      </c>
-      <c r="J5">
-        <v>2.78</v>
-      </c>
-      <c r="K5">
-        <v>3.2</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1990,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2007,7 +2001,7 @@
         <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F6">
         <v>5.4</v>
@@ -2016,7 +2010,7 @@
         <v>6.4</v>
       </c>
       <c r="H6">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I6">
         <v>1.69</v>
@@ -2040,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2232,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2249,22 +2243,22 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I7">
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
         <v>880</v>
@@ -2474,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2491,13 +2485,13 @@
         <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F8">
         <v>2.76</v>
       </c>
       <c r="G8">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>2.32</v>
@@ -2509,7 +2503,7 @@
         <v>4</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2524,10 +2518,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q8">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2716,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2733,25 +2727,25 @@
         <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.98</v>
       </c>
       <c r="G9">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="H9">
-        <v>1.29</v>
+        <v>3.4</v>
       </c>
       <c r="I9">
-        <v>10.5</v>
+        <v>3.65</v>
       </c>
       <c r="J9">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2766,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="Q9">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2958,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2975,10 +2969,10 @@
         <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F10">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G10">
         <v>2.34</v>
@@ -2990,10 +2984,10 @@
         <v>3.4</v>
       </c>
       <c r="J10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K10">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3011,7 +3005,7 @@
         <v>2.12</v>
       </c>
       <c r="Q10">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3200,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3217,13 +3211,13 @@
         <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F11">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G11">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H11">
         <v>8</v>
@@ -3232,10 +3226,10 @@
         <v>8.4</v>
       </c>
       <c r="J11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3247,16 +3241,16 @@
         <v>4.5</v>
       </c>
       <c r="O11">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q11">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S11">
         <v>3</v>
@@ -3265,7 +3259,7 @@
         <v>2</v>
       </c>
       <c r="U11">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3298,7 +3292,7 @@
         <v>130</v>
       </c>
       <c r="AF11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -3310,7 +3304,7 @@
         <v>110</v>
       </c>
       <c r="AJ11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK11">
         <v>16</v>
@@ -3331,22 +3325,22 @@
         <v>17</v>
       </c>
       <c r="AQ11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS11">
         <v>48</v>
       </c>
       <c r="AT11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV11">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AW11">
         <v>40</v>
@@ -3364,7 +3358,7 @@
         <v>38</v>
       </c>
       <c r="BB11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC11">
         <v>13.5</v>
@@ -3376,7 +3370,7 @@
         <v>42</v>
       </c>
       <c r="BF11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG11">
         <v>42</v>
@@ -3397,7 +3391,7 @@
         <v>160</v>
       </c>
       <c r="BM11">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN11">
         <v>3.95</v>
@@ -3406,16 +3400,16 @@
         <v>3.65</v>
       </c>
       <c r="BP11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR11">
         <v>27</v>
       </c>
       <c r="BS11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT11">
         <v>13</v>
@@ -3427,22 +3421,22 @@
         <v>75</v>
       </c>
       <c r="BW11">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX11">
         <v>75</v>
       </c>
       <c r="BY11">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11">
         <v>17</v>
       </c>
       <c r="CA11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3459,7 +3453,7 @@
         <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F12">
         <v>2.6</v>
@@ -3495,7 +3489,7 @@
         <v>1.67</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R12">
         <v>1.25</v>
@@ -3684,7 +3678,7 @@
         <v>5.8</v>
       </c>
       <c r="CB12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3701,25 +3695,25 @@
         <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F13">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="G13">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I13">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K13">
-        <v>5.7</v>
+        <v>890</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3734,10 +3728,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3926,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3943,25 +3937,25 @@
         <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F14">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="G14">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="H14">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="I14">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="J14">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="K14">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3976,10 +3970,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="Q14">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4168,7 +4162,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4185,25 +4179,25 @@
         <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F15">
-        <v>2.84</v>
+        <v>1.52</v>
       </c>
       <c r="G15">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="H15">
-        <v>2.22</v>
+        <v>4.9</v>
       </c>
       <c r="I15">
-        <v>2.52</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4218,10 +4212,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="Q15">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4410,12 +4404,12 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
@@ -4427,25 +4421,25 @@
         <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F16">
-        <v>5.3</v>
+        <v>2.84</v>
       </c>
       <c r="G16">
-        <v>10.5</v>
+        <v>3.25</v>
       </c>
       <c r="H16">
-        <v>1.69</v>
+        <v>2.22</v>
       </c>
       <c r="I16">
-        <v>1.89</v>
+        <v>2.52</v>
       </c>
       <c r="J16">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K16">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4460,10 +4454,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.63</v>
+        <v>2.46</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4652,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4669,25 +4663,25 @@
         <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F17">
-        <v>1.29</v>
+        <v>5.3</v>
       </c>
       <c r="G17">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="H17">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="I17">
-        <v>1000</v>
+        <v>1.89</v>
       </c>
       <c r="J17">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4702,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Q17">
         <v>1.01</v>
@@ -4894,42 +4888,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
         <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
         <v>116</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="I18">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J18">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K18">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4944,10 +4938,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5136,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5153,25 +5147,25 @@
         <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F19">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="G19">
-        <v>2.66</v>
+        <v>1.87</v>
       </c>
       <c r="H19">
-        <v>2.82</v>
+        <v>4.6</v>
       </c>
       <c r="I19">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K19">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5186,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5378,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5395,25 +5389,25 @@
         <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F20">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="G20">
-        <v>1.87</v>
+        <v>5.8</v>
       </c>
       <c r="H20">
-        <v>4.6</v>
+        <v>1.74</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>1.96</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5428,10 +5422,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="Q20">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5620,249 +5614,249 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
         <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
         <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F21">
+        <v>1.07</v>
+      </c>
+      <c r="G21">
+        <v>1.08</v>
+      </c>
+      <c r="H21">
+        <v>34</v>
+      </c>
+      <c r="I21">
+        <v>40</v>
+      </c>
+      <c r="J21">
+        <v>22</v>
+      </c>
+      <c r="K21">
+        <v>23</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>15.5</v>
+      </c>
+      <c r="O21">
+        <v>1.05</v>
+      </c>
+      <c r="P21">
+        <v>7</v>
+      </c>
+      <c r="Q21">
+        <v>1.15</v>
+      </c>
+      <c r="R21">
+        <v>3.35</v>
+      </c>
+      <c r="S21">
+        <v>1.41</v>
+      </c>
+      <c r="T21">
+        <v>1.99</v>
+      </c>
+      <c r="U21">
+        <v>1.98</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>240</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>500</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>29</v>
+      </c>
+      <c r="AC21">
+        <v>1000</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>540</v>
+      </c>
+      <c r="AF21">
+        <v>15.5</v>
+      </c>
+      <c r="AG21">
+        <v>20</v>
+      </c>
+      <c r="AH21">
+        <v>90</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>10.5</v>
+      </c>
+      <c r="AK21">
+        <v>16.5</v>
+      </c>
+      <c r="AL21">
+        <v>40</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1.76</v>
+      </c>
+      <c r="AO21">
+        <v>340</v>
+      </c>
+      <c r="AP21">
+        <v>46</v>
+      </c>
+      <c r="AQ21">
+        <v>46</v>
+      </c>
+      <c r="AR21">
+        <v>100</v>
+      </c>
+      <c r="AS21">
+        <v>95</v>
+      </c>
+      <c r="AT21">
+        <v>24</v>
+      </c>
+      <c r="AU21">
+        <v>50</v>
+      </c>
+      <c r="AV21">
+        <v>42</v>
+      </c>
+      <c r="AW21">
+        <v>120</v>
+      </c>
+      <c r="AX21">
+        <v>13.5</v>
+      </c>
+      <c r="AY21">
+        <v>18</v>
+      </c>
+      <c r="AZ21">
+        <v>50</v>
+      </c>
+      <c r="BA21">
+        <v>48</v>
+      </c>
+      <c r="BB21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC21">
+        <v>14.5</v>
+      </c>
+      <c r="BD21">
+        <v>30</v>
+      </c>
+      <c r="BE21">
+        <v>48</v>
+      </c>
+      <c r="BF21">
+        <v>1.7</v>
+      </c>
+      <c r="BG21">
+        <v>95</v>
+      </c>
+      <c r="BH21">
+        <v>12</v>
+      </c>
+      <c r="BI21">
+        <v>3.55</v>
+      </c>
+      <c r="BJ21">
+        <v>17.5</v>
+      </c>
+      <c r="BK21">
+        <v>3.9</v>
+      </c>
+      <c r="BL21">
+        <v>120</v>
+      </c>
+      <c r="BM21">
+        <v>4.8</v>
+      </c>
+      <c r="BN21">
+        <v>5.9</v>
+      </c>
+      <c r="BO21">
+        <v>4.3</v>
+      </c>
+      <c r="BP21">
+        <v>6.6</v>
+      </c>
+      <c r="BQ21">
+        <v>4.9</v>
+      </c>
+      <c r="BR21">
+        <v>19</v>
+      </c>
+      <c r="BS21">
         <v>3.95</v>
       </c>
-      <c r="G21">
-        <v>5.8</v>
-      </c>
-      <c r="H21">
-        <v>1.74</v>
-      </c>
-      <c r="I21">
-        <v>1.96</v>
-      </c>
-      <c r="J21">
-        <v>4</v>
-      </c>
-      <c r="K21">
-        <v>5.9</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>2.56</v>
-      </c>
-      <c r="Q21">
-        <v>1.01</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>0</v>
-      </c>
-      <c r="BC21">
-        <v>0</v>
-      </c>
-      <c r="BD21">
-        <v>0</v>
-      </c>
-      <c r="BE21">
-        <v>0</v>
-      </c>
-      <c r="BF21">
-        <v>0</v>
-      </c>
-      <c r="BG21">
-        <v>0</v>
-      </c>
-      <c r="BH21">
-        <v>0</v>
-      </c>
-      <c r="BI21">
-        <v>0</v>
-      </c>
-      <c r="BJ21">
-        <v>0</v>
-      </c>
-      <c r="BK21">
-        <v>0</v>
-      </c>
-      <c r="BL21">
-        <v>0</v>
-      </c>
-      <c r="BM21">
-        <v>0</v>
-      </c>
-      <c r="BN21">
-        <v>0</v>
-      </c>
-      <c r="BO21">
-        <v>0</v>
-      </c>
-      <c r="BP21">
-        <v>0</v>
-      </c>
-      <c r="BQ21">
-        <v>0</v>
-      </c>
-      <c r="BR21">
-        <v>0</v>
-      </c>
-      <c r="BS21">
-        <v>0</v>
-      </c>
       <c r="BT21">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CB21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5879,474 +5873,232 @@
         <v>120</v>
       </c>
       <c r="E22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22">
+        <v>3.6</v>
+      </c>
+      <c r="G22">
+        <v>3.7</v>
+      </c>
+      <c r="H22">
+        <v>2.2</v>
+      </c>
+      <c r="I22">
+        <v>2.22</v>
+      </c>
+      <c r="J22">
+        <v>3.6</v>
+      </c>
+      <c r="K22">
+        <v>3.7</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>1.07</v>
+      </c>
+      <c r="N22">
+        <v>4.1</v>
+      </c>
+      <c r="O22">
+        <v>1.3</v>
+      </c>
+      <c r="P22">
+        <v>2.06</v>
+      </c>
+      <c r="Q22">
+        <v>1.9</v>
+      </c>
+      <c r="R22">
+        <v>1.4</v>
+      </c>
+      <c r="S22">
+        <v>3.3</v>
+      </c>
+      <c r="T22">
+        <v>1.75</v>
+      </c>
+      <c r="U22">
+        <v>2.26</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>15.5</v>
+      </c>
+      <c r="Y22">
+        <v>10.5</v>
+      </c>
+      <c r="Z22">
+        <v>14.5</v>
+      </c>
+      <c r="AA22">
+        <v>28</v>
+      </c>
+      <c r="AB22">
+        <v>14.5</v>
+      </c>
+      <c r="AC22">
+        <v>8</v>
+      </c>
+      <c r="AD22">
+        <v>11</v>
+      </c>
+      <c r="AE22">
+        <v>24</v>
+      </c>
+      <c r="AF22">
+        <v>27</v>
+      </c>
+      <c r="AG22">
+        <v>15</v>
+      </c>
+      <c r="AH22">
+        <v>17</v>
+      </c>
+      <c r="AI22">
+        <v>38</v>
+      </c>
+      <c r="AJ22">
+        <v>70</v>
+      </c>
+      <c r="AK22">
+        <v>42</v>
+      </c>
+      <c r="AL22">
+        <v>50</v>
+      </c>
+      <c r="AM22">
+        <v>85</v>
+      </c>
+      <c r="AN22">
+        <v>40</v>
+      </c>
+      <c r="AO22">
+        <v>15.5</v>
+      </c>
+      <c r="AP22">
+        <v>14</v>
+      </c>
+      <c r="AQ22">
+        <v>9.6</v>
+      </c>
+      <c r="AR22">
+        <v>12.5</v>
+      </c>
+      <c r="AS22">
+        <v>18</v>
+      </c>
+      <c r="AT22">
+        <v>13</v>
+      </c>
+      <c r="AU22">
+        <v>7.4</v>
+      </c>
+      <c r="AV22">
+        <v>10</v>
+      </c>
+      <c r="AW22">
+        <v>19</v>
+      </c>
+      <c r="AX22">
+        <v>21</v>
+      </c>
+      <c r="AY22">
+        <v>13.5</v>
+      </c>
+      <c r="AZ22">
+        <v>15</v>
+      </c>
+      <c r="BA22">
+        <v>23</v>
+      </c>
+      <c r="BB22">
+        <v>30</v>
+      </c>
+      <c r="BC22">
+        <v>23</v>
+      </c>
+      <c r="BD22">
+        <v>27</v>
+      </c>
+      <c r="BE22">
+        <v>36</v>
+      </c>
+      <c r="BF22">
+        <v>23</v>
+      </c>
+      <c r="BG22">
+        <v>14</v>
+      </c>
+      <c r="BH22">
+        <v>3.5</v>
+      </c>
+      <c r="BI22">
+        <v>3.25</v>
+      </c>
+      <c r="BJ22">
+        <v>9.4</v>
+      </c>
+      <c r="BK22">
+        <v>8.4</v>
+      </c>
+      <c r="BL22">
+        <v>110</v>
+      </c>
+      <c r="BM22">
+        <v>14</v>
+      </c>
+      <c r="BN22">
+        <v>6.8</v>
+      </c>
+      <c r="BO22">
+        <v>6.2</v>
+      </c>
+      <c r="BP22">
+        <v>29</v>
+      </c>
+      <c r="BQ22">
+        <v>10</v>
+      </c>
+      <c r="BR22">
+        <v>40</v>
+      </c>
+      <c r="BS22">
+        <v>11.5</v>
+      </c>
+      <c r="BT22">
+        <v>5.1</v>
+      </c>
+      <c r="BU22">
+        <v>4.6</v>
+      </c>
+      <c r="BV22">
+        <v>16.5</v>
+      </c>
+      <c r="BW22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX22">
+        <v>29</v>
+      </c>
+      <c r="BY22">
+        <v>10</v>
+      </c>
+      <c r="BZ22">
+        <v>25</v>
+      </c>
+      <c r="CA22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB22" t="s">
         <v>142</v>
-      </c>
-      <c r="F22">
-        <v>1.07</v>
-      </c>
-      <c r="G22">
-        <v>1.08</v>
-      </c>
-      <c r="H22">
-        <v>36</v>
-      </c>
-      <c r="I22">
-        <v>40</v>
-      </c>
-      <c r="J22">
-        <v>22</v>
-      </c>
-      <c r="K22">
-        <v>24</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>1.01</v>
-      </c>
-      <c r="N22">
-        <v>17.5</v>
-      </c>
-      <c r="O22">
-        <v>1.05</v>
-      </c>
-      <c r="P22">
-        <v>6.8</v>
-      </c>
-      <c r="Q22">
-        <v>1.15</v>
-      </c>
-      <c r="R22">
-        <v>3.3</v>
-      </c>
-      <c r="S22">
-        <v>1.42</v>
-      </c>
-      <c r="T22">
-        <v>1.98</v>
-      </c>
-      <c r="U22">
-        <v>1.96</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>240</v>
-      </c>
-      <c r="Y22">
-        <v>1000</v>
-      </c>
-      <c r="Z22">
-        <v>480</v>
-      </c>
-      <c r="AA22">
-        <v>1000</v>
-      </c>
-      <c r="AB22">
-        <v>27</v>
-      </c>
-      <c r="AC22">
-        <v>1000</v>
-      </c>
-      <c r="AD22">
-        <v>1000</v>
-      </c>
-      <c r="AE22">
-        <v>540</v>
-      </c>
-      <c r="AF22">
-        <v>15</v>
-      </c>
-      <c r="AG22">
-        <v>19.5</v>
-      </c>
-      <c r="AH22">
-        <v>1000</v>
-      </c>
-      <c r="AI22">
-        <v>1000</v>
-      </c>
-      <c r="AJ22">
-        <v>10.5</v>
-      </c>
-      <c r="AK22">
-        <v>16.5</v>
-      </c>
-      <c r="AL22">
-        <v>40</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>1.79</v>
-      </c>
-      <c r="AO22">
-        <v>340</v>
-      </c>
-      <c r="AP22">
-        <v>46</v>
-      </c>
-      <c r="AQ22">
-        <v>46</v>
-      </c>
-      <c r="AR22">
-        <v>95</v>
-      </c>
-      <c r="AS22">
-        <v>95</v>
-      </c>
-      <c r="AT22">
-        <v>22</v>
-      </c>
-      <c r="AU22">
-        <v>30</v>
-      </c>
-      <c r="AV22">
-        <v>40</v>
-      </c>
-      <c r="AW22">
-        <v>55</v>
-      </c>
-      <c r="AX22">
-        <v>12.5</v>
-      </c>
-      <c r="AY22">
-        <v>17.5</v>
-      </c>
-      <c r="AZ22">
-        <v>34</v>
-      </c>
-      <c r="BA22">
-        <v>48</v>
-      </c>
-      <c r="BB22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC22">
-        <v>14.5</v>
-      </c>
-      <c r="BD22">
-        <v>23</v>
-      </c>
-      <c r="BE22">
-        <v>100</v>
-      </c>
-      <c r="BF22">
-        <v>1.73</v>
-      </c>
-      <c r="BG22">
-        <v>95</v>
-      </c>
-      <c r="BH22">
-        <v>12</v>
-      </c>
-      <c r="BI22">
-        <v>3.45</v>
-      </c>
-      <c r="BJ22">
-        <v>17.5</v>
-      </c>
-      <c r="BK22">
-        <v>3.85</v>
-      </c>
-      <c r="BL22">
-        <v>120</v>
-      </c>
-      <c r="BM22">
-        <v>4.6</v>
-      </c>
-      <c r="BN22">
-        <v>5.9</v>
-      </c>
-      <c r="BO22">
-        <v>4.3</v>
-      </c>
-      <c r="BP22">
-        <v>6.8</v>
-      </c>
-      <c r="BQ22">
-        <v>4.9</v>
-      </c>
-      <c r="BR22">
-        <v>19.5</v>
-      </c>
-      <c r="BS22">
-        <v>3.95</v>
-      </c>
-      <c r="BT22">
-        <v>32</v>
-      </c>
-      <c r="BU22">
-        <v>4.1</v>
-      </c>
-      <c r="BV22">
-        <v>170</v>
-      </c>
-      <c r="BW22">
-        <v>4.6</v>
-      </c>
-      <c r="BX22">
-        <v>100</v>
-      </c>
-      <c r="BY22">
-        <v>4.5</v>
-      </c>
-      <c r="BZ22">
-        <v>4.4</v>
-      </c>
-      <c r="CA22">
-        <v>3</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:80">
-      <c r="A23" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" t="s">
-        <v>143</v>
-      </c>
-      <c r="F23">
-        <v>3.6</v>
-      </c>
-      <c r="G23">
-        <v>3.65</v>
-      </c>
-      <c r="H23">
-        <v>2.2</v>
-      </c>
-      <c r="I23">
-        <v>2.22</v>
-      </c>
-      <c r="J23">
-        <v>3.6</v>
-      </c>
-      <c r="K23">
-        <v>3.7</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>1.07</v>
-      </c>
-      <c r="N23">
-        <v>4.1</v>
-      </c>
-      <c r="O23">
-        <v>1.31</v>
-      </c>
-      <c r="P23">
-        <v>2.06</v>
-      </c>
-      <c r="Q23">
-        <v>1.9</v>
-      </c>
-      <c r="R23">
-        <v>1.4</v>
-      </c>
-      <c r="S23">
-        <v>3.3</v>
-      </c>
-      <c r="T23">
-        <v>1.75</v>
-      </c>
-      <c r="U23">
-        <v>2.26</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>15.5</v>
-      </c>
-      <c r="Y23">
-        <v>10.5</v>
-      </c>
-      <c r="Z23">
-        <v>14.5</v>
-      </c>
-      <c r="AA23">
-        <v>28</v>
-      </c>
-      <c r="AB23">
-        <v>14.5</v>
-      </c>
-      <c r="AC23">
-        <v>8</v>
-      </c>
-      <c r="AD23">
-        <v>11</v>
-      </c>
-      <c r="AE23">
-        <v>24</v>
-      </c>
-      <c r="AF23">
-        <v>27</v>
-      </c>
-      <c r="AG23">
-        <v>15</v>
-      </c>
-      <c r="AH23">
-        <v>17</v>
-      </c>
-      <c r="AI23">
-        <v>38</v>
-      </c>
-      <c r="AJ23">
-        <v>70</v>
-      </c>
-      <c r="AK23">
-        <v>42</v>
-      </c>
-      <c r="AL23">
-        <v>50</v>
-      </c>
-      <c r="AM23">
-        <v>85</v>
-      </c>
-      <c r="AN23">
-        <v>40</v>
-      </c>
-      <c r="AO23">
-        <v>15.5</v>
-      </c>
-      <c r="AP23">
-        <v>14</v>
-      </c>
-      <c r="AQ23">
-        <v>9.6</v>
-      </c>
-      <c r="AR23">
-        <v>12.5</v>
-      </c>
-      <c r="AS23">
-        <v>18</v>
-      </c>
-      <c r="AT23">
-        <v>13</v>
-      </c>
-      <c r="AU23">
-        <v>7.4</v>
-      </c>
-      <c r="AV23">
-        <v>10</v>
-      </c>
-      <c r="AW23">
-        <v>19</v>
-      </c>
-      <c r="AX23">
-        <v>21</v>
-      </c>
-      <c r="AY23">
-        <v>13.5</v>
-      </c>
-      <c r="AZ23">
-        <v>15</v>
-      </c>
-      <c r="BA23">
-        <v>23</v>
-      </c>
-      <c r="BB23">
-        <v>30</v>
-      </c>
-      <c r="BC23">
-        <v>23</v>
-      </c>
-      <c r="BD23">
-        <v>27</v>
-      </c>
-      <c r="BE23">
-        <v>36</v>
-      </c>
-      <c r="BF23">
-        <v>23</v>
-      </c>
-      <c r="BG23">
-        <v>14</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
-      <c r="BI23">
-        <v>1.01</v>
-      </c>
-      <c r="BJ23">
-        <v>1000</v>
-      </c>
-      <c r="BK23">
-        <v>1.01</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.01</v>
-      </c>
-      <c r="BN23">
-        <v>1000</v>
-      </c>
-      <c r="BO23">
-        <v>1.01</v>
-      </c>
-      <c r="BP23">
-        <v>1000</v>
-      </c>
-      <c r="BQ23">
-        <v>1.01</v>
-      </c>
-      <c r="BR23">
-        <v>1000</v>
-      </c>
-      <c r="BS23">
-        <v>1.01</v>
-      </c>
-      <c r="BT23">
-        <v>1000</v>
-      </c>
-      <c r="BU23">
-        <v>1.01</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.01</v>
-      </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>1.01</v>
-      </c>
-      <c r="BZ23">
-        <v>1000</v>
-      </c>
-      <c r="CA23">
-        <v>1.01</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="149">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Mexican Liga MX</t>
   </si>
   <si>
+    <t>Indonesian Super League</t>
+  </si>
+  <si>
     <t>Egyptian Premier</t>
   </si>
   <si>
@@ -301,6 +304,9 @@
     <t>01:00:00</t>
   </si>
   <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -325,6 +331,9 @@
     <t>Puebla</t>
   </si>
   <si>
+    <t>Pusamania Borneo FC</t>
+  </si>
+  <si>
     <t>El Gounah</t>
   </si>
   <si>
@@ -364,6 +373,9 @@
     <t>Ghazl El Mahallah</t>
   </si>
   <si>
+    <t>Fortuna Koln</t>
+  </si>
+  <si>
     <t>Altrincham</t>
   </si>
   <si>
@@ -388,6 +400,9 @@
     <t>Toluca</t>
   </si>
   <si>
+    <t>Dewa United FC</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
@@ -427,6 +442,9 @@
     <t>Zamalek</t>
   </si>
   <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
     <t>Hartlepool</t>
   </si>
   <si>
@@ -442,7 +460,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-09-14 04:00:46</t>
+    <t>2026-09-14 06:16:16</t>
   </si>
 </sst>
 </file>
@@ -774,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1024,19 +1042,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F2">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="G2">
         <v>1.96</v>
@@ -1048,13 +1066,13 @@
         <v>4.7</v>
       </c>
       <c r="J2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -1066,7 +1084,7 @@
         <v>1.27</v>
       </c>
       <c r="P2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q2">
         <v>1.79</v>
@@ -1075,13 +1093,13 @@
         <v>1.45</v>
       </c>
       <c r="S2">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T2">
         <v>1.74</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
         <v>1.27</v>
@@ -1096,7 +1114,7 @@
         <v>19</v>
       </c>
       <c r="Z2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA2">
         <v>110</v>
@@ -1108,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE2">
         <v>55</v>
@@ -1129,10 +1147,10 @@
         <v>23</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM2">
         <v>100</v>
@@ -1150,10 +1168,10 @@
         <v>15</v>
       </c>
       <c r="AR2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2">
         <v>9</v>
@@ -1165,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1177,7 +1195,7 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
         <v>18</v>
@@ -1186,79 +1204,79 @@
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF2">
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
-        <v>1.23</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>1.19</v>
+        <v>5.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.19</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO2">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2">
-        <v>1.19</v>
+        <v>6.2</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS2">
-        <v>1.19</v>
+        <v>8</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>1.74</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA2">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1266,16 +1284,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F3">
         <v>2.38</v>
@@ -1293,7 +1311,7 @@
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1320,7 +1338,7 @@
         <v>5.1</v>
       </c>
       <c r="T3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U3">
         <v>1.83</v>
@@ -1335,7 +1353,7 @@
         <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z3">
         <v>34</v>
@@ -1401,7 +1419,7 @@
         <v>7</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
         <v>13.5</v>
@@ -1431,7 +1449,7 @@
         <v>6.8</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF3">
         <v>6.2</v>
@@ -1500,7 +1518,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1508,16 +1526,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>4.9</v>
@@ -1529,7 +1547,7 @@
         <v>1.69</v>
       </c>
       <c r="I4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J4">
         <v>4.4</v>
@@ -1568,7 +1586,7 @@
         <v>2.34</v>
       </c>
       <c r="V4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W4">
         <v>1.23</v>
@@ -1601,7 +1619,7 @@
         <v>55</v>
       </c>
       <c r="AG4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH4">
         <v>22</v>
@@ -1661,13 +1679,13 @@
         <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB4">
         <v>6.4</v>
       </c>
       <c r="BC4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD4">
         <v>6</v>
@@ -1742,7 +1760,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1750,241 +1768,241 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F5">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2.14</v>
       </c>
       <c r="H5">
-        <v>2.56</v>
+        <v>3.65</v>
       </c>
       <c r="I5">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="J5">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q5">
-        <v>2.46</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CB5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1992,34 +2010,34 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="H6">
-        <v>1.6</v>
+        <v>2.56</v>
       </c>
       <c r="I6">
-        <v>1.69</v>
+        <v>2.94</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="K6">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2034,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>1.54</v>
       </c>
       <c r="Q6">
-        <v>1.56</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2226,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2234,40 +2252,40 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F7">
-        <v>1.05</v>
+        <v>5.4</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>1.69</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="K7">
-        <v>880</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -2276,10 +2294,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2468,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2476,40 +2494,40 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F8">
-        <v>2.76</v>
+        <v>1.05</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>2.32</v>
+        <v>1.1</v>
       </c>
       <c r="I8">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>880</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2518,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.51</v>
+        <v>1.02</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2710,43 +2728,43 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F9">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="G9">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="I9">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9">
         <v>4.2</v>
       </c>
-      <c r="K9">
-        <v>4.6</v>
-      </c>
       <c r="L9">
         <v>0</v>
       </c>
@@ -2760,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="Q9">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2952,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2960,34 +2978,34 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="G10">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="H10">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I10">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J10">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="K10">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3002,10 +3020,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.12</v>
+        <v>2.9</v>
       </c>
       <c r="Q10">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3194,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3202,64 +3220,64 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F11">
-        <v>1.46</v>
+        <v>2.26</v>
       </c>
       <c r="G11">
-        <v>1.48</v>
+        <v>2.34</v>
       </c>
       <c r="H11">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="I11">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q11">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="R11">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3268,417 +3286,417 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL11">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AR11">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AX11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AY11">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ11">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BA11">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BC11">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BD11">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BG11">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BH11">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BI11">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BJ11">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK11">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BL11">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BM11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BN11">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BO11">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BP11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BQ11">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BR11">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BS11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BT11">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BU11">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BV11">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BW11">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BX11">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BY11">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BZ11">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12">
+        <v>1.45</v>
+      </c>
+      <c r="G12">
+        <v>1.47</v>
+      </c>
+      <c r="H12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I12">
+        <v>8.6</v>
+      </c>
+      <c r="J12">
+        <v>5</v>
+      </c>
+      <c r="K12">
+        <v>5.2</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1.05</v>
+      </c>
+      <c r="N12">
+        <v>4.5</v>
+      </c>
+      <c r="O12">
+        <v>1.26</v>
+      </c>
+      <c r="P12">
+        <v>2.22</v>
+      </c>
+      <c r="Q12">
+        <v>1.77</v>
+      </c>
+      <c r="R12">
+        <v>1.47</v>
+      </c>
+      <c r="S12">
+        <v>2.98</v>
+      </c>
+      <c r="T12">
+        <v>2.02</v>
+      </c>
+      <c r="U12">
+        <v>1.92</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>20</v>
+      </c>
+      <c r="Y12">
+        <v>27</v>
+      </c>
+      <c r="Z12">
+        <v>75</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>8.6</v>
+      </c>
+      <c r="AC12">
+        <v>11.5</v>
+      </c>
+      <c r="AD12">
+        <v>32</v>
+      </c>
+      <c r="AE12">
+        <v>150</v>
+      </c>
+      <c r="AF12">
+        <v>8.6</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+      <c r="AH12">
+        <v>27</v>
+      </c>
+      <c r="AI12">
         <v>110</v>
       </c>
-      <c r="E12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F12">
-        <v>2.6</v>
-      </c>
-      <c r="G12">
-        <v>2.64</v>
-      </c>
-      <c r="H12">
-        <v>3.2</v>
-      </c>
-      <c r="I12">
-        <v>3.3</v>
-      </c>
-      <c r="J12">
-        <v>3.15</v>
-      </c>
-      <c r="K12">
-        <v>3.2</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>1.11</v>
-      </c>
-      <c r="N12">
-        <v>3</v>
-      </c>
-      <c r="O12">
-        <v>1.47</v>
-      </c>
-      <c r="P12">
-        <v>1.67</v>
-      </c>
-      <c r="Q12">
-        <v>2.38</v>
-      </c>
-      <c r="R12">
-        <v>1.25</v>
-      </c>
-      <c r="S12">
-        <v>4.8</v>
-      </c>
-      <c r="T12">
-        <v>1.99</v>
-      </c>
-      <c r="U12">
-        <v>1.95</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>10</v>
-      </c>
-      <c r="Y12">
-        <v>10.5</v>
-      </c>
-      <c r="Z12">
-        <v>21</v>
-      </c>
-      <c r="AA12">
-        <v>65</v>
-      </c>
-      <c r="AB12">
-        <v>9</v>
-      </c>
-      <c r="AC12">
-        <v>7</v>
-      </c>
-      <c r="AD12">
-        <v>15</v>
-      </c>
-      <c r="AE12">
-        <v>46</v>
-      </c>
-      <c r="AF12">
+      <c r="AJ12">
+        <v>12.5</v>
+      </c>
+      <c r="AK12">
         <v>16</v>
       </c>
-      <c r="AG12">
-        <v>12.5</v>
-      </c>
-      <c r="AH12">
-        <v>21</v>
-      </c>
-      <c r="AI12">
-        <v>65</v>
-      </c>
-      <c r="AJ12">
-        <v>40</v>
-      </c>
-      <c r="AK12">
-        <v>34</v>
-      </c>
       <c r="AL12">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AM12">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN12">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="AO12">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AP12">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AQ12">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="AR12">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AS12">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AT12">
         <v>8</v>
       </c>
       <c r="AU12">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AV12">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AW12">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AX12">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AY12">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
         <v>18</v>
       </c>
       <c r="BA12">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BB12">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BC12">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BD12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF12">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BH12">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="BI12">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="BJ12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK12">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM12">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN12">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="BO12">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="BP12">
-        <v>26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ12">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR12">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BS12">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT12">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="BU12">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV12">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="BW12">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BX12">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BY12">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BZ12">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="CA12">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3686,64 +3704,64 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F13">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H13">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J13">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K13">
-        <v>890</v>
+        <v>3.2</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3752,210 +3770,210 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="CB13" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="G14">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="H14">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I14">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J14">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K14">
-        <v>5.7</v>
+        <v>890</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3970,10 +3988,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q14">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4162,42 +4180,42 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="G15">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="H15">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="I15">
-        <v>8.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="J15">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4212,10 +4230,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q15">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4404,42 +4422,42 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F16">
-        <v>2.84</v>
+        <v>1.55</v>
       </c>
       <c r="G16">
-        <v>3.25</v>
+        <v>1.68</v>
       </c>
       <c r="H16">
-        <v>2.22</v>
+        <v>4.9</v>
       </c>
       <c r="I16">
-        <v>2.52</v>
+        <v>5.9</v>
       </c>
       <c r="J16">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K16">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4454,10 +4472,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="Q16">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4646,42 +4664,42 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F17">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="G17">
-        <v>10.5</v>
+        <v>3.2</v>
       </c>
       <c r="H17">
-        <v>1.69</v>
+        <v>2.24</v>
       </c>
       <c r="I17">
-        <v>1.89</v>
+        <v>2.52</v>
       </c>
       <c r="J17">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="K17">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4696,10 +4714,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.63</v>
+        <v>2.46</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4888,42 +4906,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F18">
-        <v>2.32</v>
+        <v>5.5</v>
       </c>
       <c r="G18">
-        <v>2.56</v>
+        <v>7.2</v>
       </c>
       <c r="H18">
-        <v>2.94</v>
+        <v>1.71</v>
       </c>
       <c r="I18">
-        <v>3.3</v>
+        <v>1.86</v>
       </c>
       <c r="J18">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4938,10 +4956,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Q18">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5130,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5138,34 +5156,34 @@
         <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F19">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="G19">
-        <v>1.87</v>
+        <v>1000</v>
       </c>
       <c r="H19">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K19">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5180,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="Q19">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5372,43 +5390,43 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F20">
+        <v>2.34</v>
+      </c>
+      <c r="G20">
+        <v>2.56</v>
+      </c>
+      <c r="H20">
+        <v>2.94</v>
+      </c>
+      <c r="I20">
+        <v>3.25</v>
+      </c>
+      <c r="J20">
+        <v>3.6</v>
+      </c>
+      <c r="K20">
         <v>3.95</v>
       </c>
-      <c r="G20">
-        <v>5.8</v>
-      </c>
-      <c r="H20">
-        <v>1.74</v>
-      </c>
-      <c r="I20">
-        <v>1.96</v>
-      </c>
-      <c r="J20">
-        <v>4</v>
-      </c>
-      <c r="K20">
-        <v>5.9</v>
-      </c>
       <c r="L20">
         <v>0</v>
       </c>
@@ -5422,10 +5440,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="Q20">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5614,72 +5632,72 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F21">
-        <v>1.07</v>
+        <v>1.68</v>
       </c>
       <c r="G21">
-        <v>1.08</v>
+        <v>1.87</v>
       </c>
       <c r="H21">
-        <v>34</v>
+        <v>4.6</v>
       </c>
       <c r="I21">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="K21">
-        <v>23</v>
+        <v>5.3</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>7</v>
+        <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="R21">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -5688,417 +5706,901 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AO21">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AQ21">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AR21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AS21">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AU21">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AV21">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AW21">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AX21">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AZ21">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BA21">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BB21">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC21">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BE21">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BF21">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BG21">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BH21">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BI21">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BJ21">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BK21">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BL21">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM21">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BN21">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BO21">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BP21">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BQ21">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BR21">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BS21">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BT21">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BU21">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BV21">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BW21">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BX21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BY21">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BZ21">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="CA21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>4.6</v>
+      </c>
+      <c r="H22">
+        <v>1.77</v>
+      </c>
+      <c r="I22">
+        <v>1.91</v>
+      </c>
+      <c r="J22">
+        <v>4.2</v>
+      </c>
+      <c r="K22">
+        <v>4.9</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.56</v>
+      </c>
+      <c r="Q22">
+        <v>1.01</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23">
+        <v>1.07</v>
+      </c>
+      <c r="G23">
+        <v>1.08</v>
+      </c>
+      <c r="H23">
+        <v>30</v>
+      </c>
+      <c r="I23">
+        <v>36</v>
+      </c>
+      <c r="J23">
+        <v>21</v>
+      </c>
+      <c r="K23">
+        <v>23</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>18</v>
+      </c>
+      <c r="O23">
+        <v>1.05</v>
+      </c>
+      <c r="P23">
+        <v>6.8</v>
+      </c>
+      <c r="Q23">
+        <v>1.15</v>
+      </c>
+      <c r="R23">
+        <v>3.3</v>
+      </c>
+      <c r="S23">
+        <v>1.42</v>
+      </c>
+      <c r="T23">
+        <v>1.95</v>
+      </c>
+      <c r="U23">
+        <v>2.02</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>240</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>450</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>29</v>
+      </c>
+      <c r="AC23">
+        <v>70</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>480</v>
+      </c>
+      <c r="AF23">
+        <v>15.5</v>
+      </c>
+      <c r="AG23">
+        <v>19.5</v>
+      </c>
+      <c r="AH23">
+        <v>75</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>11</v>
+      </c>
+      <c r="AK23">
+        <v>16.5</v>
+      </c>
+      <c r="AL23">
+        <v>40</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1.79</v>
+      </c>
+      <c r="AO23">
+        <v>290</v>
+      </c>
+      <c r="AP23">
+        <v>46</v>
+      </c>
+      <c r="AQ23">
+        <v>46</v>
+      </c>
+      <c r="AR23">
+        <v>110</v>
+      </c>
+      <c r="AS23">
+        <v>60</v>
+      </c>
+      <c r="AT23">
+        <v>23</v>
+      </c>
+      <c r="AU23">
+        <v>48</v>
+      </c>
+      <c r="AV23">
+        <v>40</v>
+      </c>
+      <c r="AW23">
         <v>120</v>
       </c>
-      <c r="E22" t="s">
-        <v>141</v>
-      </c>
-      <c r="F22">
+      <c r="AX23">
+        <v>13</v>
+      </c>
+      <c r="AY23">
+        <v>17.5</v>
+      </c>
+      <c r="AZ23">
+        <v>50</v>
+      </c>
+      <c r="BA23">
+        <v>48</v>
+      </c>
+      <c r="BB23">
+        <v>10</v>
+      </c>
+      <c r="BC23">
+        <v>14</v>
+      </c>
+      <c r="BD23">
+        <v>32</v>
+      </c>
+      <c r="BE23">
+        <v>46</v>
+      </c>
+      <c r="BF23">
+        <v>1.74</v>
+      </c>
+      <c r="BG23">
+        <v>100</v>
+      </c>
+      <c r="BH23">
+        <v>12</v>
+      </c>
+      <c r="BI23">
         <v>3.6</v>
       </c>
-      <c r="G22">
-        <v>3.7</v>
-      </c>
-      <c r="H22">
+      <c r="BJ23">
+        <v>17</v>
+      </c>
+      <c r="BK23">
+        <v>3.95</v>
+      </c>
+      <c r="BL23">
+        <v>110</v>
+      </c>
+      <c r="BM23">
+        <v>4.9</v>
+      </c>
+      <c r="BN23">
+        <v>5.8</v>
+      </c>
+      <c r="BO23">
+        <v>4.4</v>
+      </c>
+      <c r="BP23">
+        <v>6.8</v>
+      </c>
+      <c r="BQ23">
+        <v>4.9</v>
+      </c>
+      <c r="BR23">
+        <v>19</v>
+      </c>
+      <c r="BS23">
+        <v>4</v>
+      </c>
+      <c r="BT23">
+        <v>30</v>
+      </c>
+      <c r="BU23">
+        <v>4.3</v>
+      </c>
+      <c r="BV23">
+        <v>160</v>
+      </c>
+      <c r="BW23">
+        <v>4.9</v>
+      </c>
+      <c r="BX23">
+        <v>95</v>
+      </c>
+      <c r="BY23">
+        <v>4.8</v>
+      </c>
+      <c r="BZ23">
+        <v>4.3</v>
+      </c>
+      <c r="CA23">
+        <v>3</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24">
+        <v>3.6</v>
+      </c>
+      <c r="G24">
+        <v>3.65</v>
+      </c>
+      <c r="H24">
         <v>2.2</v>
       </c>
-      <c r="I22">
+      <c r="I24">
         <v>2.22</v>
       </c>
-      <c r="J22">
+      <c r="J24">
         <v>3.6</v>
       </c>
-      <c r="K22">
-        <v>3.7</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
+      <c r="K24">
+        <v>3.65</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>1.07</v>
       </c>
-      <c r="N22">
+      <c r="N24">
         <v>4.1</v>
       </c>
-      <c r="O22">
-        <v>1.3</v>
-      </c>
-      <c r="P22">
+      <c r="O24">
+        <v>1.31</v>
+      </c>
+      <c r="P24">
         <v>2.06</v>
       </c>
-      <c r="Q22">
+      <c r="Q24">
         <v>1.9</v>
       </c>
-      <c r="R22">
+      <c r="R24">
         <v>1.4</v>
       </c>
-      <c r="S22">
+      <c r="S24">
         <v>3.3</v>
       </c>
-      <c r="T22">
+      <c r="T24">
         <v>1.75</v>
       </c>
-      <c r="U22">
+      <c r="U24">
         <v>2.26</v>
       </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
         <v>15.5</v>
       </c>
-      <c r="Y22">
+      <c r="Y24">
         <v>10.5</v>
       </c>
-      <c r="Z22">
+      <c r="Z24">
         <v>14.5</v>
       </c>
-      <c r="AA22">
+      <c r="AA24">
         <v>28</v>
       </c>
-      <c r="AB22">
+      <c r="AB24">
         <v>14.5</v>
       </c>
-      <c r="AC22">
+      <c r="AC24">
         <v>8</v>
       </c>
-      <c r="AD22">
+      <c r="AD24">
         <v>11</v>
       </c>
-      <c r="AE22">
+      <c r="AE24">
         <v>24</v>
       </c>
-      <c r="AF22">
+      <c r="AF24">
         <v>27</v>
       </c>
-      <c r="AG22">
+      <c r="AG24">
         <v>15</v>
       </c>
-      <c r="AH22">
-        <v>17</v>
-      </c>
-      <c r="AI22">
+      <c r="AH24">
+        <v>16.5</v>
+      </c>
+      <c r="AI24">
         <v>38</v>
       </c>
-      <c r="AJ22">
+      <c r="AJ24">
         <v>70</v>
       </c>
-      <c r="AK22">
+      <c r="AK24">
         <v>42</v>
       </c>
-      <c r="AL22">
+      <c r="AL24">
         <v>50</v>
       </c>
-      <c r="AM22">
+      <c r="AM24">
         <v>85</v>
       </c>
-      <c r="AN22">
+      <c r="AN24">
         <v>40</v>
       </c>
-      <c r="AO22">
+      <c r="AO24">
         <v>15.5</v>
       </c>
-      <c r="AP22">
+      <c r="AP24">
         <v>14</v>
       </c>
-      <c r="AQ22">
-        <v>9.6</v>
-      </c>
-      <c r="AR22">
+      <c r="AQ24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR24">
         <v>12.5</v>
       </c>
-      <c r="AS22">
+      <c r="AS24">
+        <v>18.5</v>
+      </c>
+      <c r="AT24">
+        <v>13</v>
+      </c>
+      <c r="AU24">
+        <v>7.4</v>
+      </c>
+      <c r="AV24">
+        <v>10</v>
+      </c>
+      <c r="AW24">
+        <v>19</v>
+      </c>
+      <c r="AX24">
         <v>18</v>
       </c>
-      <c r="AT22">
-        <v>13</v>
-      </c>
-      <c r="AU22">
-        <v>7.4</v>
-      </c>
-      <c r="AV22">
+      <c r="AY24">
+        <v>13.5</v>
+      </c>
+      <c r="AZ24">
+        <v>15</v>
+      </c>
+      <c r="BA24">
+        <v>22</v>
+      </c>
+      <c r="BB24">
+        <v>30</v>
+      </c>
+      <c r="BC24">
+        <v>23</v>
+      </c>
+      <c r="BD24">
+        <v>27</v>
+      </c>
+      <c r="BE24">
+        <v>36</v>
+      </c>
+      <c r="BF24">
+        <v>23</v>
+      </c>
+      <c r="BG24">
+        <v>14</v>
+      </c>
+      <c r="BH24">
+        <v>3.5</v>
+      </c>
+      <c r="BI24">
+        <v>3.25</v>
+      </c>
+      <c r="BJ24">
+        <v>9.4</v>
+      </c>
+      <c r="BK24">
+        <v>8.4</v>
+      </c>
+      <c r="BL24">
+        <v>110</v>
+      </c>
+      <c r="BM24">
+        <v>14.5</v>
+      </c>
+      <c r="BN24">
+        <v>6.8</v>
+      </c>
+      <c r="BO24">
+        <v>6.2</v>
+      </c>
+      <c r="BP24">
+        <v>29</v>
+      </c>
+      <c r="BQ24">
+        <v>10.5</v>
+      </c>
+      <c r="BR24">
+        <v>40</v>
+      </c>
+      <c r="BS24">
+        <v>11.5</v>
+      </c>
+      <c r="BT24">
+        <v>5.1</v>
+      </c>
+      <c r="BU24">
+        <v>4.6</v>
+      </c>
+      <c r="BV24">
+        <v>16</v>
+      </c>
+      <c r="BW24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX24">
+        <v>29</v>
+      </c>
+      <c r="BY24">
+        <v>10.5</v>
+      </c>
+      <c r="BZ24">
+        <v>25</v>
+      </c>
+      <c r="CA24">
         <v>10</v>
       </c>
-      <c r="AW22">
-        <v>19</v>
-      </c>
-      <c r="AX22">
-        <v>21</v>
-      </c>
-      <c r="AY22">
-        <v>13.5</v>
-      </c>
-      <c r="AZ22">
-        <v>15</v>
-      </c>
-      <c r="BA22">
-        <v>23</v>
-      </c>
-      <c r="BB22">
-        <v>30</v>
-      </c>
-      <c r="BC22">
-        <v>23</v>
-      </c>
-      <c r="BD22">
-        <v>27</v>
-      </c>
-      <c r="BE22">
-        <v>36</v>
-      </c>
-      <c r="BF22">
-        <v>23</v>
-      </c>
-      <c r="BG22">
-        <v>14</v>
-      </c>
-      <c r="BH22">
-        <v>3.5</v>
-      </c>
-      <c r="BI22">
-        <v>3.25</v>
-      </c>
-      <c r="BJ22">
-        <v>9.4</v>
-      </c>
-      <c r="BK22">
-        <v>8.4</v>
-      </c>
-      <c r="BL22">
-        <v>110</v>
-      </c>
-      <c r="BM22">
-        <v>14</v>
-      </c>
-      <c r="BN22">
-        <v>6.8</v>
-      </c>
-      <c r="BO22">
-        <v>6.2</v>
-      </c>
-      <c r="BP22">
-        <v>29</v>
-      </c>
-      <c r="BQ22">
-        <v>10</v>
-      </c>
-      <c r="BR22">
-        <v>40</v>
-      </c>
-      <c r="BS22">
-        <v>11.5</v>
-      </c>
-      <c r="BT22">
-        <v>5.1</v>
-      </c>
-      <c r="BU22">
-        <v>4.6</v>
-      </c>
-      <c r="BV22">
-        <v>16.5</v>
-      </c>
-      <c r="BW22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX22">
-        <v>29</v>
-      </c>
-      <c r="BY22">
-        <v>10</v>
-      </c>
-      <c r="BZ22">
-        <v>25</v>
-      </c>
-      <c r="CA22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>142</v>
+      <c r="CB24" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -460,7 +460,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-09-14 06:16:16</t>
+    <t>2026-09-14 08:32:38</t>
   </si>
 </sst>
 </file>
@@ -1060,55 +1060,55 @@
         <v>1.96</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
         <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O2">
         <v>1.27</v>
       </c>
       <c r="P2">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q2">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S2">
         <v>3.05</v>
       </c>
       <c r="T2">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Y2">
         <v>19</v>
@@ -1117,22 +1117,22 @@
         <v>38</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
         <v>11</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
         <v>11</v>
@@ -1141,25 +1141,25 @@
         <v>18.5</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
         <v>15</v>
@@ -1168,22 +1168,22 @@
         <v>15</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS2">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AT2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1195,85 +1195,85 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="BB2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC2">
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE2">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.45</v>
+        <v>1.35</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>5.4</v>
+        <v>1.98</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>1.22</v>
       </c>
       <c r="BN2">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>1.46</v>
       </c>
       <c r="BP2">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>1.98</v>
       </c>
       <c r="BR2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>8</v>
+        <v>1.22</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>1.73</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="BZ2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>7.4</v>
+        <v>1.22</v>
       </c>
       <c r="CB2" t="s">
         <v>148</v>
@@ -1296,25 +1296,25 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="G3">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1323,19 +1323,19 @@
         <v>2.74</v>
       </c>
       <c r="O3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q3">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="T3">
         <v>2.08</v>
@@ -1344,124 +1344,124 @@
         <v>1.83</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X3">
         <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AB3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
+        <v>50</v>
+      </c>
+      <c r="AK3">
         <v>46</v>
       </c>
-      <c r="AK3">
-        <v>42</v>
-      </c>
       <c r="AL3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM3">
         <v>210</v>
       </c>
       <c r="AN3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO3">
         <v>90</v>
       </c>
       <c r="AP3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR3">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AS3">
+        <v>8.6</v>
+      </c>
+      <c r="AT3">
         <v>6.8</v>
       </c>
-      <c r="AT3">
-        <v>7</v>
-      </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW3">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BA3">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB3">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC3">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD3">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE3">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BF3">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG3">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1479,7 +1479,7 @@
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP3">
         <v>1000</v>
@@ -1541,16 +1541,16 @@
         <v>4.9</v>
       </c>
       <c r="G4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H4">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="J4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K4">
         <v>4.6</v>
@@ -1559,7 +1559,7 @@
         <v>1.26</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
         <v>5.3</v>
@@ -1568,7 +1568,7 @@
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q4">
         <v>1.63</v>
@@ -1577,10 +1577,10 @@
         <v>1.59</v>
       </c>
       <c r="S4">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U4">
         <v>2.34</v>
@@ -1595,7 +1595,7 @@
         <v>28</v>
       </c>
       <c r="Y4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z4">
         <v>12.5</v>
@@ -1610,19 +1610,19 @@
         <v>10.5</v>
       </c>
       <c r="AD4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AE4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AF4">
         <v>55</v>
       </c>
       <c r="AG4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI4">
         <v>34</v>
@@ -1637,31 +1637,31 @@
         <v>65</v>
       </c>
       <c r="AM4">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN4">
         <v>60</v>
       </c>
       <c r="AO4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4">
         <v>10</v>
       </c>
       <c r="AR4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4">
         <v>9.199999999999999</v>
@@ -1670,31 +1670,31 @@
         <v>14.5</v>
       </c>
       <c r="AX4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AZ4">
         <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB4">
+        <v>7</v>
+      </c>
+      <c r="BC4">
+        <v>6.6</v>
+      </c>
+      <c r="BD4">
         <v>6.4</v>
       </c>
-      <c r="BC4">
-        <v>6.2</v>
-      </c>
-      <c r="BD4">
-        <v>6</v>
-      </c>
       <c r="BE4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG4">
         <v>6.8</v>
@@ -1703,7 +1703,7 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
@@ -1739,7 +1739,7 @@
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1751,7 +1751,7 @@
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1780,226 +1780,226 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G5">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H5">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I5">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R5">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S5">
         <v>2.66</v>
       </c>
       <c r="T5">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X5">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD5">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="AO5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG5">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP5">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2022,22 +2022,22 @@
         <v>129</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="G6">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="H6">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="I6">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="J6">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="Q6">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2264,19 +2264,19 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="G7">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="H7">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="I7">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K7">
         <v>4.8</v>
@@ -2294,10 +2294,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>2.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>1.1</v>
       </c>
       <c r="K8">
-        <v>880</v>
+        <v>950</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2748,22 +2748,22 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G9">
         <v>3</v>
       </c>
       <c r="H9">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I9">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q9">
         <v>1.52</v>
@@ -2990,19 +2990,19 @@
         <v>133</v>
       </c>
       <c r="F10">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G10">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I10">
         <v>3.65</v>
       </c>
       <c r="J10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K10">
         <v>4.6</v>
@@ -3020,10 +3020,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q10">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3232,7 +3232,7 @@
         <v>134</v>
       </c>
       <c r="F11">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G11">
         <v>2.34</v>
@@ -3241,10 +3241,10 @@
         <v>3.25</v>
       </c>
       <c r="I11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K11">
         <v>3.9</v>
@@ -3265,7 +3265,7 @@
         <v>2.12</v>
       </c>
       <c r="Q11">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3477,19 +3477,19 @@
         <v>1.45</v>
       </c>
       <c r="G12">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3498,22 +3498,22 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P12">
         <v>2.22</v>
       </c>
       <c r="Q12">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R12">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S12">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="T12">
         <v>2.02</v>
@@ -3528,13 +3528,13 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y12">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA12">
         <v>1000</v>
@@ -3546,46 +3546,46 @@
         <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE12">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF12">
         <v>8.6</v>
       </c>
       <c r="AG12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI12">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ12">
         <v>12.5</v>
       </c>
       <c r="AK12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL12">
         <v>38</v>
       </c>
       <c r="AM12">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN12">
         <v>6.6</v>
       </c>
       <c r="AO12">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR12">
         <v>32</v>
@@ -3597,10 +3597,10 @@
         <v>8</v>
       </c>
       <c r="AU12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV12">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AW12">
         <v>40</v>
@@ -3621,10 +3621,10 @@
         <v>11</v>
       </c>
       <c r="BC12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD12">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE12">
         <v>42</v>
@@ -3645,13 +3645,13 @@
         <v>13</v>
       </c>
       <c r="BK12">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BL12">
         <v>170</v>
       </c>
       <c r="BM12">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BN12">
         <v>3.85</v>
@@ -3669,25 +3669,25 @@
         <v>28</v>
       </c>
       <c r="BS12">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BU12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BV12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BW12">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BX12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY12">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12">
         <v>16.5</v>
@@ -3716,10 +3716,10 @@
         <v>136</v>
       </c>
       <c r="F13">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G13">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H13">
         <v>3.2</v>
@@ -3746,22 +3746,22 @@
         <v>1.47</v>
       </c>
       <c r="P13">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q13">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R13">
         <v>1.25</v>
       </c>
       <c r="S13">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T13">
         <v>1.99</v>
       </c>
       <c r="U13">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3776,13 +3776,13 @@
         <v>10.5</v>
       </c>
       <c r="Z13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA13">
         <v>65</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -3794,19 +3794,19 @@
         <v>44</v>
       </c>
       <c r="AF13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH13">
         <v>21</v>
       </c>
       <c r="AI13">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ13">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK13">
         <v>34</v>
@@ -3815,16 +3815,16 @@
         <v>55</v>
       </c>
       <c r="AM13">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AN13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO13">
         <v>55</v>
       </c>
       <c r="AP13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ13">
         <v>9.4</v>
@@ -3833,10 +3833,10 @@
         <v>18</v>
       </c>
       <c r="AS13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU13">
         <v>6.6</v>
@@ -3845,7 +3845,7 @@
         <v>13</v>
       </c>
       <c r="AW13">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AX13">
         <v>13.5</v>
@@ -3854,7 +3854,7 @@
         <v>11</v>
       </c>
       <c r="AZ13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA13">
         <v>32</v>
@@ -3875,46 +3875,46 @@
         <v>21</v>
       </c>
       <c r="BG13">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BH13">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BI13">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ13">
         <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL13">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="BM13">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BN13">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO13">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP13">
         <v>26</v>
       </c>
       <c r="BQ13">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR13">
         <v>48</v>
       </c>
       <c r="BS13">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT13">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU13">
         <v>5.6</v>
@@ -3923,19 +3923,19 @@
         <v>34</v>
       </c>
       <c r="BW13">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BX13">
         <v>55</v>
       </c>
       <c r="BY13">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13">
         <v>48</v>
       </c>
       <c r="CA13">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3958,22 +3958,22 @@
         <v>137</v>
       </c>
       <c r="F14">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H14">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="J14">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="K14">
-        <v>890</v>
+        <v>4.7</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3988,10 +3988,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4203,16 +4203,16 @@
         <v>1.92</v>
       </c>
       <c r="G15">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H15">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I15">
         <v>3.9</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15">
         <v>4.7</v>
@@ -4230,10 +4230,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q15">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4442,22 +4442,22 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G16">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H16">
-        <v>4.9</v>
+        <v>1.16</v>
       </c>
       <c r="I16">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="K16">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4472,10 +4472,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4684,22 +4684,22 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H17">
         <v>2.24</v>
       </c>
       <c r="I17">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="J17">
         <v>3.9</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4714,10 +4714,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4926,22 +4926,22 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="H18">
         <v>1.71</v>
       </c>
       <c r="I18">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="J18">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K18">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4956,10 +4956,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>1.01</v>
       </c>
       <c r="K19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>143</v>
       </c>
       <c r="F20">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G20">
         <v>2.56</v>
@@ -5419,13 +5419,13 @@
         <v>2.94</v>
       </c>
       <c r="I20">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J20">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K20">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>2.06</v>
       </c>
       <c r="Q20">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5652,22 +5652,22 @@
         <v>144</v>
       </c>
       <c r="F21">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G21">
         <v>1.87</v>
       </c>
       <c r="H21">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J21">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K21">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5894,22 +5894,22 @@
         <v>145</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G22">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="H22">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="I22">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="J22">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K22">
-        <v>4.9</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5924,10 +5924,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.56</v>
+        <v>1.12</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6142,16 +6142,16 @@
         <v>1.08</v>
       </c>
       <c r="H23">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I23">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J23">
+        <v>20</v>
+      </c>
+      <c r="K23">
         <v>21</v>
-      </c>
-      <c r="K23">
-        <v>23</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6163,7 +6163,7 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P23">
         <v>6.8</v>
@@ -6175,13 +6175,13 @@
         <v>3.3</v>
       </c>
       <c r="S23">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T23">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U23">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -6196,13 +6196,13 @@
         <v>1000</v>
       </c>
       <c r="Z23">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="AA23">
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC23">
         <v>70</v>
@@ -6211,16 +6211,16 @@
         <v>1000</v>
       </c>
       <c r="AE23">
-        <v>480</v>
+        <v>610</v>
       </c>
       <c r="AF23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG23">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AH23">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AI23">
         <v>1000</v>
@@ -6232,46 +6232,46 @@
         <v>16.5</v>
       </c>
       <c r="AL23">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM23">
         <v>1000</v>
       </c>
       <c r="AN23">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AO23">
-        <v>290</v>
+        <v>400</v>
       </c>
       <c r="AP23">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AQ23">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AR23">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AS23">
         <v>60</v>
       </c>
       <c r="AT23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU23">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AV23">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW23">
         <v>120</v>
       </c>
       <c r="AX23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY23">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ23">
         <v>50</v>
@@ -6283,16 +6283,16 @@
         <v>10</v>
       </c>
       <c r="BC23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD23">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE23">
         <v>46</v>
       </c>
       <c r="BF23">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="BG23">
         <v>100</v>
@@ -6301,19 +6301,19 @@
         <v>12</v>
       </c>
       <c r="BI23">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="BJ23">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BK23">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BL23">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="BM23">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BN23">
         <v>5.8</v>
@@ -6322,40 +6322,40 @@
         <v>4.4</v>
       </c>
       <c r="BP23">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BQ23">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BS23">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BT23">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BU23">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV23">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="BW23">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BX23">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BY23">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BZ23">
         <v>4.3</v>
       </c>
       <c r="CA23">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="CB23" t="s">
         <v>148</v>
@@ -6378,13 +6378,13 @@
         <v>147</v>
       </c>
       <c r="F24">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G24">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H24">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I24">
         <v>2.22</v>
@@ -6393,7 +6393,7 @@
         <v>3.6</v>
       </c>
       <c r="K24">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6411,7 +6411,7 @@
         <v>2.06</v>
       </c>
       <c r="Q24">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R24">
         <v>1.4</v>
@@ -6435,13 +6435,13 @@
         <v>15.5</v>
       </c>
       <c r="Y24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z24">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB24">
         <v>14.5</v>
@@ -6453,16 +6453,16 @@
         <v>11</v>
       </c>
       <c r="AE24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG24">
         <v>15</v>
       </c>
       <c r="AH24">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI24">
         <v>38</v>
@@ -6471,25 +6471,25 @@
         <v>70</v>
       </c>
       <c r="AK24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL24">
         <v>50</v>
       </c>
       <c r="AM24">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN24">
         <v>40</v>
       </c>
       <c r="AO24">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP24">
         <v>14</v>
       </c>
       <c r="AQ24">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR24">
         <v>12.5</v>
@@ -6507,10 +6507,10 @@
         <v>10</v>
       </c>
       <c r="AW24">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX24">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AY24">
         <v>13.5</v>
@@ -6531,13 +6531,13 @@
         <v>27</v>
       </c>
       <c r="BE24">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BF24">
         <v>23</v>
       </c>
       <c r="BG24">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH24">
         <v>3.5</v>
@@ -6552,10 +6552,10 @@
         <v>8.4</v>
       </c>
       <c r="BL24">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BM24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN24">
         <v>6.8</v>
@@ -6567,7 +6567,7 @@
         <v>29</v>
       </c>
       <c r="BQ24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR24">
         <v>40</v>
@@ -6582,22 +6582,22 @@
         <v>4.6</v>
       </c>
       <c r="BV24">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW24">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX24">
         <v>29</v>
       </c>
       <c r="BY24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ24">
         <v>25</v>
       </c>
       <c r="CA24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB24" t="s">
         <v>148</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -460,7 +460,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-09-14 08:32:38</t>
+    <t>2026-09-14 10:48:56</t>
   </si>
 </sst>
 </file>
@@ -1054,22 +1054,22 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H2">
         <v>4.3</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
         <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.37</v>
@@ -1084,19 +1084,19 @@
         <v>1.27</v>
       </c>
       <c r="P2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q2">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="R2">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S2">
         <v>3.05</v>
       </c>
       <c r="T2">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="U2">
         <v>2.22</v>
@@ -1105,7 +1105,7 @@
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X2">
         <v>21</v>
@@ -1117,7 +1117,7 @@
         <v>38</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB2">
         <v>11</v>
@@ -1129,37 +1129,37 @@
         <v>18.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF2">
         <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
         <v>18.5</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP2">
         <v>15</v>
@@ -1168,22 +1168,22 @@
         <v>15</v>
       </c>
       <c r="AR2">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AS2">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV2">
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1195,85 +1195,85 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE2">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF2">
         <v>9.800000000000001</v>
       </c>
       <c r="BG2">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
-        <v>1.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK2">
-        <v>1.98</v>
+        <v>7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.22</v>
+        <v>13</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>1.46</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2">
-        <v>1.98</v>
+        <v>8.6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS2">
-        <v>1.22</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>1.73</v>
+        <v>7</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.22</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.22</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA2">
-        <v>1.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>148</v>
@@ -1296,61 +1296,61 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G3">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T3">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U3">
         <v>1.83</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
         <v>10.5</v>
@@ -1368,7 +1368,7 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
         <v>70</v>
@@ -1380,13 +1380,13 @@
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>100</v>
       </c>
       <c r="AJ3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK3">
         <v>46</v>
@@ -1404,16 +1404,16 @@
         <v>90</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AS3">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1422,52 +1422,52 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA3">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BB3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BD3">
+        <v>7.8</v>
+      </c>
+      <c r="BE3">
         <v>8.4</v>
       </c>
-      <c r="BE3">
-        <v>9</v>
-      </c>
       <c r="BF3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BG3">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1476,46 +1476,46 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="CB3" t="s">
         <v>148</v>
@@ -1541,10 +1541,10 @@
         <v>4.9</v>
       </c>
       <c r="G4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H4">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I4">
         <v>1.75</v>
@@ -1559,7 +1559,7 @@
         <v>1.26</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
         <v>5.3</v>
@@ -1568,10 +1568,10 @@
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
         <v>1.59</v>
@@ -1580,13 +1580,13 @@
         <v>2.58</v>
       </c>
       <c r="T4">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U4">
         <v>2.34</v>
       </c>
       <c r="V4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="W4">
         <v>1.23</v>
@@ -1595,13 +1595,13 @@
         <v>28</v>
       </c>
       <c r="Y4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z4">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA4">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AB4">
         <v>28</v>
@@ -1610,7 +1610,7 @@
         <v>10.5</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE4">
         <v>17</v>
@@ -1622,7 +1622,7 @@
         <v>24</v>
       </c>
       <c r="AH4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>34</v>
@@ -1643,7 +1643,7 @@
         <v>60</v>
       </c>
       <c r="AO4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AP4">
         <v>16.5</v>
@@ -1658,43 +1658,43 @@
         <v>16</v>
       </c>
       <c r="AT4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU4">
         <v>9.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW4">
         <v>14.5</v>
       </c>
       <c r="AX4">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="AY4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ4">
         <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BC4">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD4">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG4">
         <v>6.8</v>
@@ -1783,115 +1783,115 @@
         <v>1.92</v>
       </c>
       <c r="G5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H5">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
         <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O5">
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S5">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T5">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
         <v>1.9</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB5">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
+        <v>11.5</v>
+      </c>
+      <c r="AD5">
+        <v>20</v>
+      </c>
+      <c r="AE5">
+        <v>55</v>
+      </c>
+      <c r="AF5">
+        <v>17.5</v>
+      </c>
+      <c r="AG5">
+        <v>13</v>
+      </c>
+      <c r="AH5">
+        <v>20</v>
+      </c>
+      <c r="AI5">
+        <v>55</v>
+      </c>
+      <c r="AJ5">
+        <v>29</v>
+      </c>
+      <c r="AK5">
+        <v>24</v>
+      </c>
+      <c r="AL5">
+        <v>36</v>
+      </c>
+      <c r="AM5">
+        <v>90</v>
+      </c>
+      <c r="AN5">
         <v>13.5</v>
       </c>
-      <c r="AD5">
-        <v>1000</v>
-      </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
-      <c r="AF5">
-        <v>1000</v>
-      </c>
-      <c r="AG5">
-        <v>18.5</v>
-      </c>
-      <c r="AH5">
-        <v>1000</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>1000</v>
-      </c>
-      <c r="AK5">
-        <v>1000</v>
-      </c>
-      <c r="AL5">
-        <v>1000</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>19</v>
-      </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR5">
         <v>1.03</v>
@@ -1900,106 +1900,106 @@
         <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW5">
         <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA5">
         <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE5">
         <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI5">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2022,19 +2022,19 @@
         <v>129</v>
       </c>
       <c r="F6">
+        <v>3.05</v>
+      </c>
+      <c r="G6">
+        <v>3.5</v>
+      </c>
+      <c r="H6">
+        <v>2.56</v>
+      </c>
+      <c r="I6">
         <v>2.94</v>
       </c>
-      <c r="G6">
-        <v>4.2</v>
-      </c>
-      <c r="H6">
-        <v>2.22</v>
-      </c>
-      <c r="I6">
-        <v>3.2</v>
-      </c>
       <c r="J6">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="K6">
         <v>3.2</v>
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2264,22 +2264,22 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G7">
         <v>7</v>
       </c>
       <c r="H7">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I7">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2294,10 +2294,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q7">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="Q9">
         <v>1.52</v>
@@ -2993,7 +2993,7 @@
         <v>1.99</v>
       </c>
       <c r="G10">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H10">
         <v>3.35</v>
@@ -3002,7 +3002,7 @@
         <v>3.65</v>
       </c>
       <c r="J10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K10">
         <v>4.6</v>
@@ -3020,10 +3020,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q10">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q11">
         <v>1.64</v>
@@ -3489,7 +3489,7 @@
         <v>5.1</v>
       </c>
       <c r="K12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3513,10 +3513,10 @@
         <v>1.48</v>
       </c>
       <c r="S12">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T12">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U12">
         <v>1.92</v>
@@ -3540,7 +3540,7 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12">
         <v>11.5</v>
@@ -3558,13 +3558,13 @@
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI12">
         <v>120</v>
       </c>
       <c r="AJ12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK12">
         <v>15.5</v>
@@ -3582,10 +3582,10 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AR12">
         <v>32</v>
@@ -3597,10 +3597,10 @@
         <v>8</v>
       </c>
       <c r="AU12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV12">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AW12">
         <v>40</v>
@@ -3624,7 +3624,7 @@
         <v>14</v>
       </c>
       <c r="BD12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE12">
         <v>42</v>
@@ -3636,7 +3636,7 @@
         <v>42</v>
       </c>
       <c r="BH12">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI12">
         <v>3.6</v>
@@ -3648,13 +3648,13 @@
         <v>10</v>
       </c>
       <c r="BL12">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM12">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN12">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO12">
         <v>3.6</v>
@@ -3666,13 +3666,13 @@
         <v>7.6</v>
       </c>
       <c r="BR12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BU12">
         <v>10</v>
@@ -3681,19 +3681,19 @@
         <v>85</v>
       </c>
       <c r="BW12">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BY12">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ12">
         <v>16.5</v>
       </c>
       <c r="CA12">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB12" t="s">
         <v>148</v>
@@ -3716,7 +3716,7 @@
         <v>136</v>
       </c>
       <c r="F13">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G13">
         <v>2.66</v>
@@ -3761,7 +3761,7 @@
         <v>1.99</v>
       </c>
       <c r="U13">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>10.5</v>
       </c>
       <c r="Z13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA13">
         <v>65</v>
@@ -3788,22 +3788,22 @@
         <v>7</v>
       </c>
       <c r="AD13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE13">
         <v>44</v>
       </c>
       <c r="AF13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH13">
         <v>21</v>
       </c>
       <c r="AI13">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ13">
         <v>42</v>
@@ -3815,7 +3815,7 @@
         <v>55</v>
       </c>
       <c r="AM13">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AN13">
         <v>36</v>
@@ -3866,22 +3866,22 @@
         <v>21</v>
       </c>
       <c r="BD13">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BE13">
         <v>44</v>
       </c>
       <c r="BF13">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BG13">
         <v>27</v>
       </c>
       <c r="BH13">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI13">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13">
         <v>12.5</v>
@@ -3893,49 +3893,49 @@
         <v>200</v>
       </c>
       <c r="BM13">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN13">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR13">
         <v>48</v>
       </c>
       <c r="BS13">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13">
         <v>6.2</v>
       </c>
       <c r="BU13">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV13">
         <v>34</v>
       </c>
       <c r="BW13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX13">
         <v>55</v>
       </c>
       <c r="BY13">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ13">
         <v>48</v>
       </c>
       <c r="CA13">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3961,19 +3961,19 @@
         <v>2.54</v>
       </c>
       <c r="G14">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="H14">
         <v>2.46</v>
       </c>
       <c r="I14">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J14">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3991,7 +3991,7 @@
         <v>2.2</v>
       </c>
       <c r="Q14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4206,7 +4206,7 @@
         <v>2.1</v>
       </c>
       <c r="H15">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I15">
         <v>3.9</v>
@@ -4230,10 +4230,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4442,22 +4442,22 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="G16">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H16">
-        <v>1.16</v>
+        <v>4.8</v>
       </c>
       <c r="I16">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="J16">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K16">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4472,10 +4472,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>3.05</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4684,10 +4684,10 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G17">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H17">
         <v>2.24</v>
@@ -4714,10 +4714,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q17">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4926,10 +4926,10 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G18">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="H18">
         <v>1.71</v>
@@ -4938,10 +4938,10 @@
         <v>1.87</v>
       </c>
       <c r="J18">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K18">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4956,10 +4956,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5410,19 +5410,19 @@
         <v>143</v>
       </c>
       <c r="F20">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G20">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H20">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="J20">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K20">
         <v>3.9</v>
@@ -5440,10 +5440,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5655,19 +5655,19 @@
         <v>1.69</v>
       </c>
       <c r="G21">
-        <v>1.87</v>
+        <v>1000</v>
       </c>
       <c r="H21">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="I21">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J21">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K21">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5685,7 +5685,7 @@
         <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5894,22 +5894,22 @@
         <v>145</v>
       </c>
       <c r="F22">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="G22">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="H22">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I22">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="J22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Q22">
         <v>1.46</v>
@@ -6145,13 +6145,13 @@
         <v>36</v>
       </c>
       <c r="I23">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6172,16 +6172,16 @@
         <v>1.15</v>
       </c>
       <c r="R23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="S23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -6202,25 +6202,25 @@
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC23">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AD23">
         <v>1000</v>
       </c>
       <c r="AE23">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG23">
         <v>22</v>
       </c>
       <c r="AH23">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AI23">
         <v>1000</v>
@@ -6238,7 +6238,7 @@
         <v>1000</v>
       </c>
       <c r="AN23">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AO23">
         <v>400</v>
@@ -6247,7 +6247,7 @@
         <v>90</v>
       </c>
       <c r="AQ23">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AR23">
         <v>55</v>
@@ -6259,22 +6259,22 @@
         <v>24</v>
       </c>
       <c r="AU23">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AV23">
         <v>42</v>
       </c>
       <c r="AW23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AX23">
         <v>13.5</v>
       </c>
       <c r="AY23">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BA23">
         <v>48</v>
@@ -6286,37 +6286,37 @@
         <v>15</v>
       </c>
       <c r="BD23">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE23">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF23">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BG23">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BH23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BI23">
         <v>8.4</v>
       </c>
       <c r="BJ23">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BK23">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL23">
         <v>130</v>
       </c>
       <c r="BM23">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BN23">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO23">
         <v>4.4</v>
@@ -6325,37 +6325,37 @@
         <v>5.6</v>
       </c>
       <c r="BQ23">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BR23">
         <v>20</v>
       </c>
       <c r="BS23">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT23">
         <v>34</v>
       </c>
       <c r="BU23">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV23">
         <v>190</v>
       </c>
       <c r="BW23">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX23">
         <v>110</v>
       </c>
       <c r="BY23">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ23">
         <v>4.3</v>
       </c>
       <c r="CA23">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CB23" t="s">
         <v>148</v>
@@ -6378,10 +6378,10 @@
         <v>147</v>
       </c>
       <c r="F24">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G24">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H24">
         <v>2.18</v>
@@ -6393,7 +6393,7 @@
         <v>3.6</v>
       </c>
       <c r="K24">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6405,13 +6405,13 @@
         <v>4.1</v>
       </c>
       <c r="O24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P24">
         <v>2.06</v>
       </c>
       <c r="Q24">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R24">
         <v>1.4</v>
@@ -6435,13 +6435,13 @@
         <v>15.5</v>
       </c>
       <c r="Y24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z24">
         <v>15</v>
       </c>
       <c r="AA24">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB24">
         <v>14.5</v>
@@ -6456,7 +6456,7 @@
         <v>23</v>
       </c>
       <c r="AF24">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG24">
         <v>15</v>
@@ -6471,7 +6471,7 @@
         <v>70</v>
       </c>
       <c r="AK24">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL24">
         <v>50</v>
@@ -6495,7 +6495,7 @@
         <v>12.5</v>
       </c>
       <c r="AS24">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT24">
         <v>13</v>
@@ -6519,19 +6519,19 @@
         <v>15</v>
       </c>
       <c r="BA24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB24">
         <v>30</v>
       </c>
       <c r="BC24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE24">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BF24">
         <v>23</v>
@@ -6543,7 +6543,7 @@
         <v>3.5</v>
       </c>
       <c r="BI24">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="BJ24">
         <v>9.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="153">
   <si>
     <t>League</t>
   </si>
@@ -292,6 +292,9 @@
     <t>English National League</t>
   </si>
   <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
     <t>2026-09-16</t>
   </si>
   <si>
@@ -319,6 +322,9 @@
     <t>18:45:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>19:30:00</t>
   </si>
   <si>
@@ -385,6 +391,9 @@
     <t>Scunthorpe</t>
   </si>
   <si>
+    <t>Guabira</t>
+  </si>
+  <si>
     <t>Barcelona</t>
   </si>
   <si>
@@ -454,13 +463,16 @@
     <t>Boreham Wood</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Racing Santander</t>
   </si>
   <si>
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-09-14 10:48:56</t>
+    <t>2026-09-14 13:06:21</t>
   </si>
 </sst>
 </file>
@@ -792,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1042,25 +1054,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F2">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G2">
         <v>1.95</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
         <v>4.7</v>
@@ -1069,10 +1081,10 @@
         <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -1099,7 +1111,7 @@
         <v>1.74</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
         <v>1.27</v>
@@ -1108,7 +1120,7 @@
         <v>2.04</v>
       </c>
       <c r="X2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y2">
         <v>19</v>
@@ -1123,10 +1135,10 @@
         <v>11</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE2">
         <v>60</v>
@@ -1150,7 +1162,7 @@
         <v>20</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM2">
         <v>100</v>
@@ -1159,7 +1171,7 @@
         <v>11.5</v>
       </c>
       <c r="AO2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP2">
         <v>15</v>
@@ -1168,10 +1180,10 @@
         <v>15</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1183,10 +1195,10 @@
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
         <v>9.199999999999999</v>
@@ -1195,7 +1207,7 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB2">
         <v>18</v>
@@ -1204,16 +1216,16 @@
         <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
         <v>3.75</v>
@@ -1222,16 +1234,16 @@
         <v>3.45</v>
       </c>
       <c r="BJ2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
         <v>4.7</v>
@@ -1243,40 +1255,40 @@
         <v>13.5</v>
       </c>
       <c r="BQ2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR2">
         <v>26</v>
       </c>
       <c r="BS2">
+        <v>8.6</v>
+      </c>
+      <c r="BT2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU2">
+        <v>6</v>
+      </c>
+      <c r="BV2">
+        <v>36</v>
+      </c>
+      <c r="BW2">
         <v>9.6</v>
-      </c>
-      <c r="BT2">
-        <v>7.8</v>
-      </c>
-      <c r="BU2">
-        <v>7</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>21</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1284,52 +1296,52 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F3">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G3">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
         <v>1.22</v>
@@ -1338,22 +1350,22 @@
         <v>5.1</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
         <v>1.83</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z3">
         <v>29</v>
@@ -1368,7 +1380,7 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE3">
         <v>70</v>
@@ -1380,16 +1392,16 @@
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI3">
         <v>100</v>
       </c>
       <c r="AJ3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK3">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AL3">
         <v>70</v>
@@ -1398,70 +1410,70 @@
         <v>210</v>
       </c>
       <c r="AN3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO3">
         <v>90</v>
       </c>
       <c r="AP3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>9.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS3">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
+        <v>6.2</v>
+      </c>
+      <c r="BA3">
+        <v>7.2</v>
+      </c>
+      <c r="BB3">
+        <v>6.6</v>
+      </c>
+      <c r="BC3">
         <v>6.4</v>
       </c>
-      <c r="BA3">
-        <v>8</v>
-      </c>
-      <c r="BB3">
+      <c r="BD3">
+        <v>7</v>
+      </c>
+      <c r="BE3">
+        <v>7</v>
+      </c>
+      <c r="BF3">
+        <v>6.4</v>
+      </c>
+      <c r="BG3">
         <v>7.2</v>
-      </c>
-      <c r="BC3">
-        <v>7</v>
-      </c>
-      <c r="BD3">
-        <v>7.8</v>
-      </c>
-      <c r="BE3">
-        <v>8.4</v>
-      </c>
-      <c r="BF3">
-        <v>7</v>
-      </c>
-      <c r="BG3">
-        <v>8</v>
       </c>
       <c r="BH3">
         <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="BJ3">
         <v>13.5</v>
@@ -1482,7 +1494,7 @@
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
         <v>15</v>
@@ -1506,19 +1518,19 @@
         <v>24</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY3">
         <v>38</v>
       </c>
       <c r="BZ3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="CA3">
         <v>32</v>
       </c>
       <c r="CB3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1526,16 +1538,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F4">
         <v>4.9</v>
@@ -1547,19 +1559,19 @@
         <v>1.69</v>
       </c>
       <c r="I4">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="J4">
         <v>4.3</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L4">
         <v>1.26</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
         <v>5.3</v>
@@ -1568,10 +1580,10 @@
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R4">
         <v>1.59</v>
@@ -1580,7 +1592,7 @@
         <v>2.58</v>
       </c>
       <c r="T4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U4">
         <v>2.34</v>
@@ -1598,10 +1610,10 @@
         <v>14</v>
       </c>
       <c r="Z4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AB4">
         <v>28</v>
@@ -1646,7 +1658,7 @@
         <v>7.8</v>
       </c>
       <c r="AP4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ4">
         <v>10</v>
@@ -1655,7 +1667,7 @@
         <v>11</v>
       </c>
       <c r="AS4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AT4">
         <v>20</v>
@@ -1670,7 +1682,7 @@
         <v>14.5</v>
       </c>
       <c r="AX4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY4">
         <v>17.5</v>
@@ -1679,22 +1691,22 @@
         <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB4">
+        <v>5.6</v>
+      </c>
+      <c r="BC4">
+        <v>5.4</v>
+      </c>
+      <c r="BD4">
+        <v>5.3</v>
+      </c>
+      <c r="BE4">
         <v>5.5</v>
       </c>
-      <c r="BC4">
-        <v>5.3</v>
-      </c>
-      <c r="BD4">
-        <v>5.2</v>
-      </c>
-      <c r="BE4">
+      <c r="BF4">
         <v>5.4</v>
-      </c>
-      <c r="BF4">
-        <v>5.3</v>
       </c>
       <c r="BG4">
         <v>6.8</v>
@@ -1739,19 +1751,19 @@
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1760,7 +1772,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1768,40 +1780,40 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F5">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="G5">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
         <v>1.28</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
         <v>4.5</v>
@@ -1810,16 +1822,16 @@
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R5">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S5">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T5">
         <v>1.63</v>
@@ -1846,7 +1858,7 @@
         <v>90</v>
       </c>
       <c r="AB5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC5">
         <v>11.5</v>
@@ -1858,7 +1870,7 @@
         <v>55</v>
       </c>
       <c r="AF5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG5">
         <v>13</v>
@@ -1876,7 +1888,7 @@
         <v>24</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM5">
         <v>90</v>
@@ -1906,7 +1918,7 @@
         <v>8</v>
       </c>
       <c r="AV5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW5">
         <v>1.03</v>
@@ -1918,7 +1930,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA5">
         <v>1.03</v>
@@ -1927,7 +1939,7 @@
         <v>17</v>
       </c>
       <c r="BC5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
         <v>21</v>
@@ -1936,7 +1948,7 @@
         <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
         <v>25</v>
@@ -1963,7 +1975,7 @@
         <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP5">
         <v>16</v>
@@ -1990,7 +2002,7 @@
         <v>20</v>
       </c>
       <c r="BX5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY5">
         <v>25</v>
@@ -2002,7 +2014,7 @@
         <v>13</v>
       </c>
       <c r="CB5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2010,241 +2022,241 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G6">
         <v>3.5</v>
       </c>
       <c r="H6">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I6">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J6">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K6">
         <v>3.2</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q6">
         <v>2.48</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="CB6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2252,34 +2264,34 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F7">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="G7">
         <v>7</v>
       </c>
       <c r="H7">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="I7">
         <v>1.69</v>
       </c>
       <c r="J7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2294,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q7">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2486,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2494,16 +2506,16 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F8">
         <v>1.05</v>
@@ -2728,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2736,16 +2748,16 @@
         <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F9">
         <v>2.84</v>
@@ -2778,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q9">
         <v>1.52</v>
@@ -2970,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2978,25 +2990,25 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F10">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G10">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I10">
         <v>3.65</v>
@@ -3023,7 +3035,7 @@
         <v>2.9</v>
       </c>
       <c r="Q10">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3212,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3220,34 +3232,34 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F11">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G11">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H11">
         <v>3.25</v>
       </c>
       <c r="I11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J11">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3265,7 +3277,7 @@
         <v>2.16</v>
       </c>
       <c r="Q11">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3454,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3462,16 +3474,16 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F12">
         <v>1.45</v>
@@ -3498,28 +3510,28 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O12">
         <v>1.25</v>
       </c>
       <c r="P12">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q12">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R12">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S12">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T12">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3534,13 +3546,13 @@
         <v>29</v>
       </c>
       <c r="Z12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>11.5</v>
@@ -3549,7 +3561,7 @@
         <v>34</v>
       </c>
       <c r="AE12">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF12">
         <v>8.6</v>
@@ -3570,16 +3582,16 @@
         <v>15.5</v>
       </c>
       <c r="AL12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM12">
         <v>150</v>
       </c>
       <c r="AN12">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP12">
         <v>17.5</v>
@@ -3594,10 +3606,10 @@
         <v>48</v>
       </c>
       <c r="AT12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV12">
         <v>26</v>
@@ -3609,7 +3621,7 @@
         <v>7.8</v>
       </c>
       <c r="AY12">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12">
         <v>18</v>
@@ -3618,19 +3630,19 @@
         <v>40</v>
       </c>
       <c r="BB12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE12">
         <v>42</v>
       </c>
       <c r="BF12">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG12">
         <v>42</v>
@@ -3642,61 +3654,61 @@
         <v>3.6</v>
       </c>
       <c r="BJ12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="BL12">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM12">
         <v>8.6</v>
       </c>
       <c r="BN12">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO12">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP12">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BQ12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS12">
         <v>6.8</v>
       </c>
       <c r="BT12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU12">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="BV12">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BW12">
         <v>8.199999999999999</v>
       </c>
       <c r="BX12">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BY12">
         <v>8.199999999999999</v>
       </c>
       <c r="BZ12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA12">
         <v>6</v>
       </c>
       <c r="CB12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3704,16 +3716,16 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F13">
         <v>2.62</v>
@@ -3740,16 +3752,16 @@
         <v>1.11</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O13">
         <v>1.47</v>
       </c>
       <c r="P13">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q13">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R13">
         <v>1.25</v>
@@ -3776,7 +3788,7 @@
         <v>10.5</v>
       </c>
       <c r="Z13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA13">
         <v>65</v>
@@ -3830,7 +3842,7 @@
         <v>9.4</v>
       </c>
       <c r="AR13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS13">
         <v>28</v>
@@ -3842,7 +3854,7 @@
         <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
         <v>36</v>
@@ -3875,7 +3887,7 @@
         <v>28</v>
       </c>
       <c r="BG13">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BH13">
         <v>2.9</v>
@@ -3887,13 +3899,13 @@
         <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BL13">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="BM13">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BN13">
         <v>5.4</v>
@@ -3905,16 +3917,16 @@
         <v>27</v>
       </c>
       <c r="BQ13">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR13">
         <v>48</v>
       </c>
       <c r="BS13">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BT13">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BU13">
         <v>5.5</v>
@@ -3923,22 +3935,22 @@
         <v>34</v>
       </c>
       <c r="BW13">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BX13">
         <v>55</v>
       </c>
       <c r="BY13">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ13">
         <v>48</v>
       </c>
       <c r="CA13">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="CB13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3946,34 +3958,34 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F14">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G14">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I14">
         <v>2.8</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3988,10 +4000,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q14">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4180,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4188,16 +4200,16 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F15">
         <v>1.92</v>
@@ -4206,13 +4218,13 @@
         <v>2.1</v>
       </c>
       <c r="H15">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I15">
         <v>3.9</v>
       </c>
       <c r="J15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <v>4.7</v>
@@ -4233,7 +4245,7 @@
         <v>2.7</v>
       </c>
       <c r="Q15">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4422,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4430,25 +4442,25 @@
         <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F16">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G16">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H16">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I16">
         <v>5.6</v>
@@ -4472,10 +4484,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q16">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4664,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4672,19 +4684,19 @@
         <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F17">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G17">
         <v>3.3</v>
@@ -4693,10 +4705,10 @@
         <v>2.24</v>
       </c>
       <c r="I17">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K17">
         <v>4.3</v>
@@ -4714,10 +4726,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q17">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4906,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4914,22 +4926,22 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F18">
         <v>5.5</v>
       </c>
       <c r="G18">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="H18">
         <v>1.71</v>
@@ -4941,7 +4953,7 @@
         <v>3.45</v>
       </c>
       <c r="K18">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4956,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q18">
         <v>2.22</v>
@@ -5148,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5156,34 +5168,34 @@
         <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F19">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="H19">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="J19">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="K19">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5198,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5390,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5398,31 +5410,31 @@
         <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F20">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="G20">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="I20">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J20">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
         <v>3.9</v>
@@ -5440,10 +5452,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q20">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5632,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5640,34 +5652,34 @@
         <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F21">
         <v>1.69</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="H21">
-        <v>1.25</v>
+        <v>4.7</v>
       </c>
       <c r="I21">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J21">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K21">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5685,7 +5697,7 @@
         <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -5874,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5882,28 +5894,28 @@
         <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F22">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="G22">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H22">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="I22">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J22">
         <v>4.2</v>
@@ -5924,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="Q22">
         <v>1.46</v>
@@ -6116,72 +6128,72 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F23">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="G23">
-        <v>1.08</v>
+        <v>1000</v>
       </c>
       <c r="H23">
-        <v>36</v>
+        <v>1.04</v>
       </c>
       <c r="I23">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="J23">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="K23">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.24</v>
+      </c>
+      <c r="Q23">
         <v>1.01</v>
       </c>
-      <c r="N23">
-        <v>18</v>
-      </c>
-      <c r="O23">
-        <v>1.04</v>
-      </c>
-      <c r="P23">
-        <v>6.8</v>
-      </c>
-      <c r="Q23">
-        <v>1.15</v>
-      </c>
       <c r="R23">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -6190,175 +6202,175 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AL23">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AO23">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AP23">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AR23">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AU23">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AV23">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY23">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AZ23">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BA23">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BB23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BC23">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BD23">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BE23">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BF23">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BG23">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BH23">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BI23">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BJ23">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BK23">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BL23">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BM23">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BN23">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BO23">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP23">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BQ23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BR23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BS23">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BT23">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BU23">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BV23">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="BW23">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BX23">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BY23">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BZ23">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="CA23">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6366,241 +6378,483 @@
         <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F24">
-        <v>3.7</v>
+        <v>1.07</v>
       </c>
       <c r="G24">
+        <v>1.08</v>
+      </c>
+      <c r="H24">
+        <v>36</v>
+      </c>
+      <c r="I24">
+        <v>40</v>
+      </c>
+      <c r="J24">
+        <v>22</v>
+      </c>
+      <c r="K24">
+        <v>24</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>15.5</v>
+      </c>
+      <c r="O24">
+        <v>1.04</v>
+      </c>
+      <c r="P24">
+        <v>6.8</v>
+      </c>
+      <c r="Q24">
+        <v>1.15</v>
+      </c>
+      <c r="R24">
+        <v>3.35</v>
+      </c>
+      <c r="S24">
+        <v>1.39</v>
+      </c>
+      <c r="T24">
+        <v>2</v>
+      </c>
+      <c r="U24">
+        <v>1.95</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>240</v>
+      </c>
+      <c r="Y24">
+        <v>1000</v>
+      </c>
+      <c r="Z24">
+        <v>510</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>29</v>
+      </c>
+      <c r="AC24">
+        <v>75</v>
+      </c>
+      <c r="AD24">
+        <v>1000</v>
+      </c>
+      <c r="AE24">
+        <v>570</v>
+      </c>
+      <c r="AF24">
+        <v>15</v>
+      </c>
+      <c r="AG24">
+        <v>22</v>
+      </c>
+      <c r="AH24">
+        <v>1000</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>11</v>
+      </c>
+      <c r="AK24">
+        <v>16.5</v>
+      </c>
+      <c r="AL24">
+        <v>44</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>1.72</v>
+      </c>
+      <c r="AO24">
+        <v>360</v>
+      </c>
+      <c r="AP24">
+        <v>95</v>
+      </c>
+      <c r="AQ24">
+        <v>46</v>
+      </c>
+      <c r="AR24">
+        <v>55</v>
+      </c>
+      <c r="AS24">
+        <v>60</v>
+      </c>
+      <c r="AT24">
+        <v>24</v>
+      </c>
+      <c r="AU24">
+        <v>48</v>
+      </c>
+      <c r="AV24">
+        <v>42</v>
+      </c>
+      <c r="AW24">
+        <v>100</v>
+      </c>
+      <c r="AX24">
+        <v>13.5</v>
+      </c>
+      <c r="AY24">
+        <v>19.5</v>
+      </c>
+      <c r="AZ24">
+        <v>50</v>
+      </c>
+      <c r="BA24">
+        <v>75</v>
+      </c>
+      <c r="BB24">
+        <v>10</v>
+      </c>
+      <c r="BC24">
+        <v>15</v>
+      </c>
+      <c r="BD24">
+        <v>36</v>
+      </c>
+      <c r="BE24">
+        <v>48</v>
+      </c>
+      <c r="BF24">
+        <v>1.68</v>
+      </c>
+      <c r="BG24">
+        <v>110</v>
+      </c>
+      <c r="BH24">
+        <v>12</v>
+      </c>
+      <c r="BI24">
+        <v>3.9</v>
+      </c>
+      <c r="BJ24">
+        <v>18</v>
+      </c>
+      <c r="BK24">
+        <v>4.4</v>
+      </c>
+      <c r="BL24">
+        <v>130</v>
+      </c>
+      <c r="BM24">
+        <v>5.4</v>
+      </c>
+      <c r="BN24">
+        <v>5.8</v>
+      </c>
+      <c r="BO24">
+        <v>4.4</v>
+      </c>
+      <c r="BP24">
+        <v>5.6</v>
+      </c>
+      <c r="BQ24">
+        <v>5</v>
+      </c>
+      <c r="BR24">
+        <v>19.5</v>
+      </c>
+      <c r="BS24">
+        <v>4.4</v>
+      </c>
+      <c r="BT24">
+        <v>34</v>
+      </c>
+      <c r="BU24">
+        <v>4.8</v>
+      </c>
+      <c r="BV24">
+        <v>190</v>
+      </c>
+      <c r="BW24">
+        <v>5.5</v>
+      </c>
+      <c r="BX24">
+        <v>110</v>
+      </c>
+      <c r="BY24">
+        <v>5.4</v>
+      </c>
+      <c r="BZ24">
+        <v>4.3</v>
+      </c>
+      <c r="CA24">
+        <v>2.94</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25">
+        <v>3.65</v>
+      </c>
+      <c r="G25">
         <v>3.75</v>
       </c>
-      <c r="H24">
+      <c r="H25">
         <v>2.18</v>
       </c>
-      <c r="I24">
+      <c r="I25">
         <v>2.22</v>
       </c>
-      <c r="J24">
+      <c r="J25">
         <v>3.6</v>
       </c>
-      <c r="K24">
+      <c r="K25">
         <v>3.65</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>1.07</v>
       </c>
-      <c r="N24">
+      <c r="N25">
         <v>4.1</v>
       </c>
-      <c r="O24">
-        <v>1.3</v>
-      </c>
-      <c r="P24">
+      <c r="O25">
+        <v>1.31</v>
+      </c>
+      <c r="P25">
         <v>2.06</v>
       </c>
-      <c r="Q24">
-        <v>1.9</v>
-      </c>
-      <c r="R24">
-        <v>1.4</v>
-      </c>
-      <c r="S24">
-        <v>3.3</v>
-      </c>
-      <c r="T24">
-        <v>1.75</v>
-      </c>
-      <c r="U24">
+      <c r="Q25">
+        <v>1.89</v>
+      </c>
+      <c r="R25">
+        <v>1.41</v>
+      </c>
+      <c r="S25">
+        <v>3.25</v>
+      </c>
+      <c r="T25">
+        <v>1.74</v>
+      </c>
+      <c r="U25">
         <v>2.26</v>
       </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
         <v>15.5</v>
       </c>
-      <c r="Y24">
-        <v>10.5</v>
-      </c>
-      <c r="Z24">
+      <c r="Y25">
+        <v>11</v>
+      </c>
+      <c r="Z25">
+        <v>14.5</v>
+      </c>
+      <c r="AA25">
+        <v>27</v>
+      </c>
+      <c r="AB25">
+        <v>15.5</v>
+      </c>
+      <c r="AC25">
+        <v>8</v>
+      </c>
+      <c r="AD25">
+        <v>11</v>
+      </c>
+      <c r="AE25">
+        <v>22</v>
+      </c>
+      <c r="AF25">
+        <v>27</v>
+      </c>
+      <c r="AG25">
         <v>15</v>
       </c>
-      <c r="AA24">
-        <v>28</v>
-      </c>
-      <c r="AB24">
-        <v>14.5</v>
-      </c>
-      <c r="AC24">
-        <v>8</v>
-      </c>
-      <c r="AD24">
-        <v>11</v>
-      </c>
-      <c r="AE24">
+      <c r="AH25">
+        <v>17</v>
+      </c>
+      <c r="AI25">
+        <v>38</v>
+      </c>
+      <c r="AJ25">
+        <v>70</v>
+      </c>
+      <c r="AK25">
+        <v>42</v>
+      </c>
+      <c r="AL25">
+        <v>50</v>
+      </c>
+      <c r="AM25">
+        <v>85</v>
+      </c>
+      <c r="AN25">
+        <v>40</v>
+      </c>
+      <c r="AO25">
+        <v>16</v>
+      </c>
+      <c r="AP25">
+        <v>14</v>
+      </c>
+      <c r="AQ25">
+        <v>9.6</v>
+      </c>
+      <c r="AR25">
+        <v>13</v>
+      </c>
+      <c r="AS25">
+        <v>17.5</v>
+      </c>
+      <c r="AT25">
+        <v>13</v>
+      </c>
+      <c r="AU25">
+        <v>7.6</v>
+      </c>
+      <c r="AV25">
+        <v>10</v>
+      </c>
+      <c r="AW25">
+        <v>19</v>
+      </c>
+      <c r="AX25">
+        <v>22</v>
+      </c>
+      <c r="AY25">
+        <v>13.5</v>
+      </c>
+      <c r="AZ25">
+        <v>15</v>
+      </c>
+      <c r="BA25">
+        <v>22</v>
+      </c>
+      <c r="BB25">
+        <v>30</v>
+      </c>
+      <c r="BC25">
         <v>23</v>
       </c>
-      <c r="AF24">
+      <c r="BD25">
         <v>27</v>
       </c>
-      <c r="AG24">
-        <v>15</v>
-      </c>
-      <c r="AH24">
-        <v>17</v>
-      </c>
-      <c r="AI24">
-        <v>38</v>
-      </c>
-      <c r="AJ24">
-        <v>70</v>
-      </c>
-      <c r="AK24">
-        <v>42</v>
-      </c>
-      <c r="AL24">
-        <v>50</v>
-      </c>
-      <c r="AM24">
-        <v>90</v>
-      </c>
-      <c r="AN24">
+      <c r="BE25">
+        <v>36</v>
+      </c>
+      <c r="BF25">
+        <v>23</v>
+      </c>
+      <c r="BG25">
+        <v>13.5</v>
+      </c>
+      <c r="BH25">
+        <v>3.5</v>
+      </c>
+      <c r="BI25">
+        <v>2.92</v>
+      </c>
+      <c r="BJ25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK25">
+        <v>8.4</v>
+      </c>
+      <c r="BL25">
+        <v>120</v>
+      </c>
+      <c r="BM25">
+        <v>12</v>
+      </c>
+      <c r="BN25">
+        <v>7.2</v>
+      </c>
+      <c r="BO25">
+        <v>5.4</v>
+      </c>
+      <c r="BP25">
+        <v>29</v>
+      </c>
+      <c r="BQ25">
+        <v>9</v>
+      </c>
+      <c r="BR25">
         <v>40</v>
       </c>
-      <c r="AO24">
-        <v>16</v>
-      </c>
-      <c r="AP24">
-        <v>14</v>
-      </c>
-      <c r="AQ24">
-        <v>9.6</v>
-      </c>
-      <c r="AR24">
-        <v>12.5</v>
-      </c>
-      <c r="AS24">
-        <v>17.5</v>
-      </c>
-      <c r="AT24">
-        <v>13</v>
-      </c>
-      <c r="AU24">
-        <v>7.4</v>
-      </c>
-      <c r="AV24">
+      <c r="BS25">
         <v>10</v>
       </c>
-      <c r="AW24">
-        <v>19.5</v>
-      </c>
-      <c r="AX24">
-        <v>22</v>
-      </c>
-      <c r="AY24">
-        <v>13.5</v>
-      </c>
-      <c r="AZ24">
-        <v>15</v>
-      </c>
-      <c r="BA24">
-        <v>23</v>
-      </c>
-      <c r="BB24">
-        <v>30</v>
-      </c>
-      <c r="BC24">
-        <v>24</v>
-      </c>
-      <c r="BD24">
-        <v>28</v>
-      </c>
-      <c r="BE24">
-        <v>36</v>
-      </c>
-      <c r="BF24">
-        <v>23</v>
-      </c>
-      <c r="BG24">
-        <v>14.5</v>
-      </c>
-      <c r="BH24">
-        <v>3.5</v>
-      </c>
-      <c r="BI24">
-        <v>2.92</v>
-      </c>
-      <c r="BJ24">
-        <v>9.4</v>
-      </c>
-      <c r="BK24">
-        <v>8.4</v>
-      </c>
-      <c r="BL24">
-        <v>120</v>
-      </c>
-      <c r="BM24">
-        <v>14</v>
-      </c>
-      <c r="BN24">
-        <v>6.8</v>
-      </c>
-      <c r="BO24">
-        <v>6.2</v>
-      </c>
-      <c r="BP24">
+      <c r="BT25">
+        <v>5.1</v>
+      </c>
+      <c r="BU25">
+        <v>4.4</v>
+      </c>
+      <c r="BV25">
+        <v>16.5</v>
+      </c>
+      <c r="BW25">
+        <v>7.6</v>
+      </c>
+      <c r="BX25">
         <v>29</v>
       </c>
-      <c r="BQ24">
-        <v>10</v>
-      </c>
-      <c r="BR24">
-        <v>40</v>
-      </c>
-      <c r="BS24">
-        <v>11.5</v>
-      </c>
-      <c r="BT24">
-        <v>5.1</v>
-      </c>
-      <c r="BU24">
-        <v>4.6</v>
-      </c>
-      <c r="BV24">
-        <v>16.5</v>
-      </c>
-      <c r="BW24">
-        <v>8</v>
-      </c>
-      <c r="BX24">
-        <v>29</v>
-      </c>
-      <c r="BY24">
-        <v>10</v>
-      </c>
-      <c r="BZ24">
+      <c r="BY25">
+        <v>9</v>
+      </c>
+      <c r="BZ25">
         <v>25</v>
       </c>
-      <c r="CA24">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>148</v>
+      <c r="CA25">
+        <v>8.6</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -607,7 +607,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-09-14 15:24:20</t>
+    <t>2026-09-14 17:40:22</t>
   </si>
 </sst>
 </file>
@@ -1213,13 +1213,13 @@
         <v>4.6</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -1231,7 +1231,7 @@
         <v>1.27</v>
       </c>
       <c r="P2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q2">
         <v>1.79</v>
@@ -1270,28 +1270,28 @@
         <v>11</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE2">
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI2">
         <v>65</v>
       </c>
       <c r="AJ2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK2">
         <v>20</v>
@@ -1300,7 +1300,7 @@
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN2">
         <v>11.5</v>
@@ -1315,10 +1315,10 @@
         <v>15</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1330,7 +1330,7 @@
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX2">
         <v>11</v>
@@ -1342,7 +1342,7 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB2">
         <v>18</v>
@@ -1351,76 +1351,76 @@
         <v>16.5</v>
       </c>
       <c r="BD2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF2">
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.45</v>
+        <v>1.21</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>1.69</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>1.21</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="BP2">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>6.6</v>
+        <v>1.21</v>
       </c>
       <c r="BR2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>1.21</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.3</v>
+        <v>1.69</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>1.21</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>1.21</v>
       </c>
       <c r="BZ2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>8</v>
+        <v>1.21</v>
       </c>
       <c r="CB2" t="s">
         <v>197</v>
@@ -1458,22 +1458,22 @@
         <v>3.25</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="O3">
         <v>1.51</v>
       </c>
       <c r="P3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -1485,10 +1485,10 @@
         <v>5.1</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U3">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V3">
         <v>1.36</v>
@@ -1500,7 +1500,7 @@
         <v>12</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
         <v>29</v>
@@ -1509,7 +1509,7 @@
         <v>100</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
@@ -1521,7 +1521,7 @@
         <v>70</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
         <v>12</v>
@@ -1560,7 +1560,7 @@
         <v>20</v>
       </c>
       <c r="AS3">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
@@ -1572,37 +1572,37 @@
         <v>14</v>
       </c>
       <c r="AW3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB3">
+        <v>7.2</v>
+      </c>
+      <c r="BC3">
         <v>6.8</v>
       </c>
-      <c r="BC3">
-        <v>6.6</v>
-      </c>
       <c r="BD3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE3">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1715,7 +1715,7 @@
         <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
         <v>1.63</v>
@@ -1724,7 +1724,7 @@
         <v>1.59</v>
       </c>
       <c r="S4">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T4">
         <v>1.68</v>
@@ -1742,16 +1742,16 @@
         <v>28</v>
       </c>
       <c r="Y4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z4">
         <v>15</v>
       </c>
       <c r="AA4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AC4">
         <v>10.5</v>
@@ -1769,10 +1769,10 @@
         <v>24</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ4">
         <v>130</v>
@@ -1817,7 +1817,7 @@
         <v>14.5</v>
       </c>
       <c r="AX4">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY4">
         <v>17.5</v>
@@ -1826,22 +1826,22 @@
         <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB4">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BC4">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD4">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE4">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG4">
         <v>6.8</v>
@@ -1933,7 +1933,7 @@
         <v>2.1</v>
       </c>
       <c r="H5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I5">
         <v>4.4</v>
@@ -1942,7 +1942,7 @@
         <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1960,13 +1960,13 @@
         <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S5">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
         <v>1.63</v>
@@ -1981,7 +1981,7 @@
         <v>1.9</v>
       </c>
       <c r="X5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y5">
         <v>22</v>
@@ -2086,7 +2086,7 @@
         <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2169,49 +2169,49 @@
         <v>158</v>
       </c>
       <c r="F6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G6">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H6">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="I6">
         <v>2.92</v>
       </c>
       <c r="J6">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K6">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
         <v>1.45</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="O6">
         <v>1.51</v>
       </c>
       <c r="P6">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Q6">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T6">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
         <v>1.75</v>
@@ -2220,10 +2220,10 @@
         <v>1.52</v>
       </c>
       <c r="W6">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
         <v>15.5</v>
@@ -2435,13 +2435,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O7">
         <v>1.12</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q7">
         <v>1.12</v>
@@ -2450,7 +2450,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2653,22 +2653,22 @@
         <v>160</v>
       </c>
       <c r="F8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G8">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H8">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I8">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="J8">
         <v>4.6</v>
       </c>
       <c r="K8">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2677,22 +2677,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O8">
         <v>1.13</v>
       </c>
       <c r="P8">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R8">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2704,7 +2704,7 @@
         <v>1.1</v>
       </c>
       <c r="W8">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2895,13 +2895,13 @@
         <v>161</v>
       </c>
       <c r="F9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I9">
         <v>1000</v>
@@ -2919,13 +2919,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
         <v>1.01</v>
@@ -2934,7 +2934,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -3161,16 +3161,16 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O10">
         <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R10">
         <v>1.18</v>
@@ -3379,7 +3379,7 @@
         <v>163</v>
       </c>
       <c r="F11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G11">
         <v>6.4</v>
@@ -3391,7 +3391,7 @@
         <v>1.68</v>
       </c>
       <c r="J11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
         <v>4.8</v>
@@ -3418,7 +3418,7 @@
         <v>1.54</v>
       </c>
       <c r="S11">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T11">
         <v>1.73</v>
@@ -3580,7 +3580,7 @@
         <v>5.9</v>
       </c>
       <c r="BU11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV11">
         <v>14.5</v>
@@ -3624,10 +3624,10 @@
         <v>4.2</v>
       </c>
       <c r="G12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H12">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I12">
         <v>2.06</v>
@@ -3639,22 +3639,22 @@
         <v>3.65</v>
       </c>
       <c r="L12">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M12">
         <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O12">
         <v>1.38</v>
       </c>
       <c r="P12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q12">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R12">
         <v>1.32</v>
@@ -3666,7 +3666,7 @@
         <v>1.95</v>
       </c>
       <c r="U12">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V12">
         <v>1.94</v>
@@ -3681,7 +3681,7 @@
         <v>8.4</v>
       </c>
       <c r="Z12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA12">
         <v>25</v>
@@ -3699,7 +3699,7 @@
         <v>24</v>
       </c>
       <c r="AF12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG12">
         <v>18.5</v>
@@ -3711,16 +3711,16 @@
         <v>44</v>
       </c>
       <c r="AJ12">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL12">
         <v>70</v>
       </c>
       <c r="AM12">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN12">
         <v>75</v>
@@ -3732,7 +3732,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR12">
         <v>10.5</v>
@@ -3783,64 +3783,64 @@
         <v>15</v>
       </c>
       <c r="BH12">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="BI12">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BJ12">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BK12">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM12">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BN12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO12">
+        <v>6.6</v>
+      </c>
+      <c r="BP12">
+        <v>42</v>
+      </c>
+      <c r="BQ12">
+        <v>29</v>
+      </c>
+      <c r="BR12">
+        <v>60</v>
+      </c>
+      <c r="BS12">
+        <v>38</v>
+      </c>
+      <c r="BT12">
+        <v>4.7</v>
+      </c>
+      <c r="BU12">
+        <v>4.1</v>
+      </c>
+      <c r="BV12">
+        <v>17</v>
+      </c>
+      <c r="BW12">
         <v>9.6</v>
       </c>
-      <c r="BO12">
-        <v>5.8</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>13</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>15.5</v>
-      </c>
-      <c r="BT12">
-        <v>5.3</v>
-      </c>
-      <c r="BU12">
-        <v>3.9</v>
-      </c>
-      <c r="BV12">
-        <v>20</v>
-      </c>
-      <c r="BW12">
-        <v>11</v>
-      </c>
       <c r="BX12">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BY12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BZ12">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CA12">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="CB12" t="s">
         <v>197</v>
@@ -3863,7 +3863,7 @@
         <v>165</v>
       </c>
       <c r="F13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G13">
         <v>5.6</v>
@@ -3872,7 +3872,7 @@
         <v>1.68</v>
       </c>
       <c r="I13">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="J13">
         <v>4.3</v>
@@ -3881,10 +3881,10 @@
         <v>4.5</v>
       </c>
       <c r="L13">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
         <v>4.8</v>
@@ -3902,16 +3902,16 @@
         <v>1.52</v>
       </c>
       <c r="S13">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T13">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U13">
         <v>2.2</v>
       </c>
       <c r="V13">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="W13">
         <v>1.21</v>
@@ -3941,7 +3941,7 @@
         <v>16.5</v>
       </c>
       <c r="AF13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG13">
         <v>22</v>
@@ -3968,10 +3968,10 @@
         <v>65</v>
       </c>
       <c r="AO13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ13">
         <v>9.4</v>
@@ -4001,7 +4001,7 @@
         <v>18.5</v>
       </c>
       <c r="AZ13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA13">
         <v>26</v>
@@ -4040,7 +4040,7 @@
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
         <v>1000</v>
@@ -4052,13 +4052,13 @@
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
         <v>1000</v>
@@ -4076,13 +4076,13 @@
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>197</v>
@@ -4129,22 +4129,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
+        <v>1.26</v>
+      </c>
+      <c r="O14">
+        <v>1.02</v>
+      </c>
+      <c r="P14">
+        <v>1.26</v>
+      </c>
+      <c r="Q14">
+        <v>1.02</v>
+      </c>
+      <c r="R14">
         <v>1.25</v>
       </c>
-      <c r="O14">
-        <v>1.01</v>
-      </c>
-      <c r="P14">
-        <v>1.25</v>
-      </c>
-      <c r="Q14">
-        <v>1.01</v>
-      </c>
-      <c r="R14">
-        <v>1.24</v>
-      </c>
       <c r="S14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4347,13 +4347,13 @@
         <v>167</v>
       </c>
       <c r="F15">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H15">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I15">
         <v>2.48</v>
@@ -4365,16 +4365,16 @@
         <v>4.3</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M15">
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
         <v>2.7</v>
@@ -4389,22 +4389,22 @@
         <v>2.18</v>
       </c>
       <c r="T15">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="U15">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="V15">
         <v>1.67</v>
       </c>
       <c r="W15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y15">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Z15">
         <v>23</v>
@@ -4437,7 +4437,7 @@
         <v>32</v>
       </c>
       <c r="AJ15">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AK15">
         <v>30</v>
@@ -4464,7 +4464,7 @@
         <v>15.5</v>
       </c>
       <c r="AS15">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="AT15">
         <v>14.5</v>
@@ -4476,7 +4476,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW15">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX15">
         <v>16</v>
@@ -4488,25 +4488,25 @@
         <v>11.5</v>
       </c>
       <c r="BA15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB15">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD15">
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF15">
         <v>11.5</v>
       </c>
       <c r="BG15">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4589,25 +4589,25 @@
         <v>168</v>
       </c>
       <c r="F16">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H16">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I16">
         <v>3.6</v>
       </c>
       <c r="J16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M16">
         <v>1.01</v>
@@ -4619,28 +4619,28 @@
         <v>1.15</v>
       </c>
       <c r="P16">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q16">
         <v>1.47</v>
       </c>
       <c r="R16">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="S16">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T16">
         <v>1.49</v>
       </c>
       <c r="U16">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V16">
         <v>1.38</v>
       </c>
       <c r="W16">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X16">
         <v>32</v>
@@ -4748,10 +4748,10 @@
         <v>7.2</v>
       </c>
       <c r="BG16">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BH16">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
         <v>3.85</v>
@@ -4769,7 +4769,7 @@
         <v>21</v>
       </c>
       <c r="BN16">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BO16">
         <v>4.5</v>
@@ -4855,22 +4855,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
+        <v>1.26</v>
+      </c>
+      <c r="O17">
+        <v>1.02</v>
+      </c>
+      <c r="P17">
+        <v>1.26</v>
+      </c>
+      <c r="Q17">
+        <v>1.02</v>
+      </c>
+      <c r="R17">
         <v>1.25</v>
       </c>
-      <c r="O17">
-        <v>1.01</v>
-      </c>
-      <c r="P17">
-        <v>1.25</v>
-      </c>
-      <c r="Q17">
-        <v>1.01</v>
-      </c>
-      <c r="R17">
-        <v>1.24</v>
-      </c>
       <c r="S17">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T17">
         <v>1.11</v>
@@ -5097,22 +5097,22 @@
         <v>1.01</v>
       </c>
       <c r="N18">
+        <v>1.26</v>
+      </c>
+      <c r="O18">
+        <v>1.02</v>
+      </c>
+      <c r="P18">
+        <v>1.26</v>
+      </c>
+      <c r="Q18">
+        <v>1.02</v>
+      </c>
+      <c r="R18">
         <v>1.25</v>
       </c>
-      <c r="O18">
-        <v>1.01</v>
-      </c>
-      <c r="P18">
-        <v>1.25</v>
-      </c>
-      <c r="Q18">
-        <v>1.01</v>
-      </c>
-      <c r="R18">
-        <v>1.24</v>
-      </c>
       <c r="S18">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T18">
         <v>1.11</v>
@@ -5339,22 +5339,22 @@
         <v>1.01</v>
       </c>
       <c r="N19">
+        <v>1.26</v>
+      </c>
+      <c r="O19">
+        <v>1.02</v>
+      </c>
+      <c r="P19">
+        <v>1.26</v>
+      </c>
+      <c r="Q19">
+        <v>1.02</v>
+      </c>
+      <c r="R19">
         <v>1.25</v>
       </c>
-      <c r="O19">
-        <v>1.01</v>
-      </c>
-      <c r="P19">
-        <v>1.25</v>
-      </c>
-      <c r="Q19">
-        <v>1.01</v>
-      </c>
-      <c r="R19">
-        <v>1.24</v>
-      </c>
       <c r="S19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T19">
         <v>1.11</v>
@@ -5569,7 +5569,7 @@
         <v>3.4</v>
       </c>
       <c r="J20">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K20">
         <v>3.85</v>
@@ -5587,13 +5587,13 @@
         <v>1.25</v>
       </c>
       <c r="P20">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="R20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S20">
         <v>2.88</v>
@@ -5605,10 +5605,10 @@
         <v>2.36</v>
       </c>
       <c r="V20">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X20">
         <v>18.5</v>
@@ -5802,16 +5802,16 @@
         <v>1.04</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H21">
         <v>1.04</v>
       </c>
       <c r="I21">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J21">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -5823,28 +5823,28 @@
         <v>1.01</v>
       </c>
       <c r="N21">
+        <v>1.26</v>
+      </c>
+      <c r="O21">
+        <v>1.02</v>
+      </c>
+      <c r="P21">
+        <v>1.26</v>
+      </c>
+      <c r="Q21">
+        <v>1.02</v>
+      </c>
+      <c r="R21">
         <v>1.25</v>
       </c>
-      <c r="O21">
-        <v>1.01</v>
-      </c>
-      <c r="P21">
-        <v>1.25</v>
-      </c>
-      <c r="Q21">
-        <v>1.01</v>
-      </c>
-      <c r="R21">
-        <v>1.24</v>
-      </c>
       <c r="S21">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V21">
         <v>1.02</v>
@@ -6044,7 +6044,7 @@
         <v>2.62</v>
       </c>
       <c r="G22">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H22">
         <v>3.2</v>
@@ -6059,22 +6059,22 @@
         <v>3.2</v>
       </c>
       <c r="L22">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="M22">
         <v>1.11</v>
       </c>
       <c r="N22">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O22">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P22">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q22">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
         <v>1.25</v>
@@ -6083,19 +6083,19 @@
         <v>4.7</v>
       </c>
       <c r="T22">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U22">
         <v>1.96</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y22">
         <v>10.5</v>
@@ -6119,7 +6119,7 @@
         <v>44</v>
       </c>
       <c r="AF22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG22">
         <v>12.5</v>
@@ -6149,7 +6149,7 @@
         <v>48</v>
       </c>
       <c r="AP22">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ22">
         <v>9.6</v>
@@ -6161,10 +6161,10 @@
         <v>50</v>
       </c>
       <c r="AT22">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU22">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV22">
         <v>13</v>
@@ -6185,28 +6185,28 @@
         <v>50</v>
       </c>
       <c r="BB22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC22">
         <v>30</v>
       </c>
       <c r="BD22">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="BE22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF22">
         <v>30</v>
       </c>
       <c r="BG22">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BH22">
         <v>2.9</v>
       </c>
       <c r="BI22">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ22">
         <v>12.5</v>
@@ -6218,7 +6218,7 @@
         <v>190</v>
       </c>
       <c r="BM22">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="BN22">
         <v>5.4</v>
@@ -6283,7 +6283,7 @@
         <v>175</v>
       </c>
       <c r="F23">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="G23">
         <v>3.2</v>
@@ -6292,13 +6292,13 @@
         <v>2.48</v>
       </c>
       <c r="I23">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="J23">
         <v>3.3</v>
       </c>
       <c r="K23">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6322,16 +6322,16 @@
         <v>1.35</v>
       </c>
       <c r="S23">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T23">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
         <v>1.45</v>
@@ -6543,13 +6543,13 @@
         <v>4.2</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M24">
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O24">
         <v>1.19</v>
@@ -6558,19 +6558,19 @@
         <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R24">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S24">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="T24">
         <v>1.4</v>
       </c>
       <c r="U24">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V24">
         <v>1.55</v>
@@ -6708,7 +6708,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO24">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP24">
         <v>26</v>
@@ -6726,7 +6726,7 @@
         <v>8</v>
       </c>
       <c r="BU24">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV24">
         <v>25</v>
@@ -6767,19 +6767,19 @@
         <v>177</v>
       </c>
       <c r="F25">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G25">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H25">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I25">
         <v>3.9</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K25">
         <v>4.7</v>
@@ -6788,37 +6788,37 @@
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P25">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q25">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R25">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="S25">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="U25">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="V25">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X25">
         <v>38</v>
@@ -6836,7 +6836,7 @@
         <v>19</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD25">
         <v>20</v>
@@ -6845,7 +6845,7 @@
         <v>44</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG25">
         <v>1000</v>
@@ -6869,13 +6869,13 @@
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO25">
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25">
         <v>16</v>
@@ -6923,10 +6923,10 @@
         <v>1.03</v>
       </c>
       <c r="BF25">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG25">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7015,13 +7015,13 @@
         <v>1.68</v>
       </c>
       <c r="H26">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I26">
         <v>5.6</v>
       </c>
       <c r="J26">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K26">
         <v>5.4</v>
@@ -7033,25 +7033,25 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O26">
         <v>1.1</v>
       </c>
       <c r="P26">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q26">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="R26">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="S26">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="T26">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U26">
         <v>1.11</v>
@@ -7260,10 +7260,10 @@
         <v>2.26</v>
       </c>
       <c r="I27">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J27">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K27">
         <v>4.3</v>
@@ -7278,13 +7278,13 @@
         <v>5.3</v>
       </c>
       <c r="O27">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P27">
         <v>2.5</v>
       </c>
       <c r="Q27">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R27">
         <v>1.6</v>
@@ -7293,112 +7293,112 @@
         <v>2.36</v>
       </c>
       <c r="T27">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V27">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W27">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB27">
         <v>22</v>
       </c>
       <c r="AC27">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP27">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AQ27">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR27">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AT27">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AU27">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV27">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW27">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AX27">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AY27">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ27">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA27">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BC27">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD27">
         <v>1.03</v>
@@ -7407,10 +7407,10 @@
         <v>1.03</v>
       </c>
       <c r="BF27">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BG27">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7434,7 +7434,7 @@
         <v>9.6</v>
       </c>
       <c r="BO27">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP27">
         <v>30</v>
@@ -7502,7 +7502,7 @@
         <v>1.73</v>
       </c>
       <c r="I28">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J28">
         <v>3.45</v>
@@ -7514,13 +7514,13 @@
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O28">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P28">
         <v>1.67</v>
@@ -7529,106 +7529,106 @@
         <v>2.26</v>
       </c>
       <c r="R28">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S28">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U28">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="V28">
         <v>2.16</v>
       </c>
       <c r="W28">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X28">
+        <v>11.5</v>
+      </c>
+      <c r="Y28">
+        <v>7</v>
+      </c>
+      <c r="Z28">
+        <v>10</v>
+      </c>
+      <c r="AA28">
+        <v>22</v>
+      </c>
+      <c r="AB28">
+        <v>16.5</v>
+      </c>
+      <c r="AC28">
+        <v>8.6</v>
+      </c>
+      <c r="AD28">
+        <v>11</v>
+      </c>
+      <c r="AE28">
+        <v>26</v>
+      </c>
+      <c r="AF28">
+        <v>55</v>
+      </c>
+      <c r="AG28">
+        <v>28</v>
+      </c>
+      <c r="AH28">
+        <v>29</v>
+      </c>
+      <c r="AI28">
+        <v>60</v>
+      </c>
+      <c r="AJ28">
+        <v>220</v>
+      </c>
+      <c r="AK28">
+        <v>120</v>
+      </c>
+      <c r="AL28">
+        <v>130</v>
+      </c>
+      <c r="AM28">
+        <v>210</v>
+      </c>
+      <c r="AN28">
+        <v>200</v>
+      </c>
+      <c r="AO28">
+        <v>18.5</v>
+      </c>
+      <c r="AP28">
+        <v>9.4</v>
+      </c>
+      <c r="AQ28">
+        <v>5.9</v>
+      </c>
+      <c r="AR28">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS28">
         <v>16</v>
       </c>
-      <c r="Y28">
-        <v>9.4</v>
-      </c>
-      <c r="Z28">
-        <v>15.5</v>
-      </c>
-      <c r="AA28">
-        <v>1000</v>
-      </c>
-      <c r="AB28">
-        <v>1000</v>
-      </c>
-      <c r="AC28">
+      <c r="AT28">
         <v>13.5</v>
       </c>
-      <c r="AD28">
-        <v>22</v>
-      </c>
-      <c r="AE28">
-        <v>1000</v>
-      </c>
-      <c r="AF28">
-        <v>1000</v>
-      </c>
-      <c r="AG28">
-        <v>1000</v>
-      </c>
-      <c r="AH28">
-        <v>1000</v>
-      </c>
-      <c r="AI28">
-        <v>1000</v>
-      </c>
-      <c r="AJ28">
-        <v>1000</v>
-      </c>
-      <c r="AK28">
-        <v>1000</v>
-      </c>
-      <c r="AL28">
-        <v>1000</v>
-      </c>
-      <c r="AM28">
-        <v>1000</v>
-      </c>
-      <c r="AN28">
-        <v>1000</v>
-      </c>
-      <c r="AO28">
-        <v>1000</v>
-      </c>
-      <c r="AP28">
-        <v>1.03</v>
-      </c>
-      <c r="AQ28">
-        <v>1.03</v>
-      </c>
-      <c r="AR28">
-        <v>1.03</v>
-      </c>
-      <c r="AS28">
-        <v>1.03</v>
-      </c>
-      <c r="AT28">
-        <v>1.03</v>
-      </c>
       <c r="AU28">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV28">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW28">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AX28">
         <v>1.03</v>
       </c>
       <c r="AY28">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AZ28">
         <v>1.03</v>
@@ -7649,10 +7649,10 @@
         <v>1.03</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BG28">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7741,13 +7741,13 @@
         <v>1.46</v>
       </c>
       <c r="H29">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I29">
         <v>9</v>
       </c>
       <c r="J29">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>5.2</v>
@@ -7762,16 +7762,16 @@
         <v>4.7</v>
       </c>
       <c r="O29">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P29">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R29">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S29">
         <v>2.98</v>
@@ -7780,28 +7780,28 @@
         <v>2.04</v>
       </c>
       <c r="U29">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V29">
         <v>1.12</v>
       </c>
       <c r="W29">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X29">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y29">
         <v>29</v>
       </c>
       <c r="Z29">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA29">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC29">
         <v>11</v>
@@ -7828,22 +7828,22 @@
         <v>11.5</v>
       </c>
       <c r="AK29">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL29">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN29">
         <v>6.6</v>
       </c>
       <c r="AO29">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP29">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ29">
         <v>26</v>
@@ -7855,7 +7855,7 @@
         <v>48</v>
       </c>
       <c r="AT29">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU29">
         <v>10</v>
@@ -7867,7 +7867,7 @@
         <v>40</v>
       </c>
       <c r="AX29">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY29">
         <v>9.6</v>
@@ -7882,7 +7882,7 @@
         <v>11</v>
       </c>
       <c r="BC29">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD29">
         <v>32</v>
@@ -7906,37 +7906,37 @@
         <v>13.5</v>
       </c>
       <c r="BK29">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL29">
         <v>170</v>
       </c>
       <c r="BM29">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN29">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BO29">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP29">
         <v>9.6</v>
       </c>
       <c r="BQ29">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR29">
         <v>28</v>
       </c>
       <c r="BS29">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT29">
         <v>14</v>
       </c>
       <c r="BU29">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV29">
         <v>90</v>
@@ -7951,10 +7951,10 @@
         <v>8.4</v>
       </c>
       <c r="BZ29">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA29">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB29" t="s">
         <v>197</v>
@@ -8001,22 +8001,22 @@
         <v>1.01</v>
       </c>
       <c r="N30">
+        <v>1.26</v>
+      </c>
+      <c r="O30">
+        <v>1.02</v>
+      </c>
+      <c r="P30">
+        <v>1.26</v>
+      </c>
+      <c r="Q30">
+        <v>1.01</v>
+      </c>
+      <c r="R30">
         <v>1.25</v>
       </c>
-      <c r="O30">
-        <v>1.01</v>
-      </c>
-      <c r="P30">
-        <v>1.25</v>
-      </c>
-      <c r="Q30">
-        <v>1.01</v>
-      </c>
-      <c r="R30">
-        <v>1.24</v>
-      </c>
       <c r="S30">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T30">
         <v>1.11</v>
@@ -8025,7 +8025,7 @@
         <v>1.11</v>
       </c>
       <c r="V30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30">
         <v>1.01</v>
@@ -8085,52 +8085,52 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF30">
         <v>1.01</v>
@@ -8222,16 +8222,16 @@
         <v>1.04</v>
       </c>
       <c r="G31">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H31">
         <v>1.04</v>
       </c>
       <c r="I31">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J31">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K31">
         <v>950</v>
@@ -8243,28 +8243,28 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P31">
         <v>1.07</v>
       </c>
       <c r="Q31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R31">
         <v>1.07</v>
       </c>
       <c r="S31">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T31">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U31">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V31">
         <v>1.02</v>
@@ -8327,52 +8327,52 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF31">
         <v>1.01</v>
@@ -8461,34 +8461,34 @@
         <v>184</v>
       </c>
       <c r="F32">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="H32">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="I32">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="J32">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K32">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P32">
         <v>2.56</v>
@@ -8497,190 +8497,190 @@
         <v>1.46</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
         <v>197</v>
@@ -8706,223 +8706,223 @@
         <v>1.69</v>
       </c>
       <c r="G33">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H33">
         <v>4.7</v>
       </c>
       <c r="I33">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J33">
         <v>3.85</v>
       </c>
       <c r="K33">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P33">
         <v>1.98</v>
       </c>
       <c r="Q33">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF33">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="s">
         <v>197</v>
@@ -8945,226 +8945,226 @@
         <v>186</v>
       </c>
       <c r="F34">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G34">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H34">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I34">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J34">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K34">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P34">
         <v>2.06</v>
       </c>
       <c r="Q34">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP34">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU34">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV34">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW34">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX34">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ34">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA34">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC34">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE34">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG34">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK34">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN34">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BO34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ34">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BR34">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS34">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BT34">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU34">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV34">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW34">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BX34">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY34">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BZ34">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA34">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CB34" t="s">
         <v>197</v>
@@ -9190,7 +9190,7 @@
         <v>1.04</v>
       </c>
       <c r="G35">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H35">
         <v>1.04</v>
@@ -9199,214 +9199,214 @@
         <v>1000</v>
       </c>
       <c r="J35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K35">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P35">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q35">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ35">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB35" t="s">
         <v>197</v>
@@ -9429,16 +9429,16 @@
         <v>188</v>
       </c>
       <c r="F36">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G36">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H36">
         <v>5.3</v>
       </c>
       <c r="I36">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J36">
         <v>4.2</v>
@@ -9447,7 +9447,7 @@
         <v>4.5</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M36">
         <v>1.05</v>
@@ -9477,10 +9477,10 @@
         <v>2.14</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X36">
         <v>22</v>
@@ -9522,7 +9522,7 @@
         <v>18</v>
       </c>
       <c r="AK36">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL36">
         <v>38</v>
@@ -9543,7 +9543,7 @@
         <v>18.5</v>
       </c>
       <c r="AR36">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="AS36">
         <v>10</v>
@@ -9570,7 +9570,7 @@
         <v>17</v>
       </c>
       <c r="BA36">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB36">
         <v>15</v>
@@ -9582,13 +9582,13 @@
         <v>8.4</v>
       </c>
       <c r="BE36">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF36">
         <v>7.6</v>
       </c>
       <c r="BG36">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH36">
         <v>3.9</v>
@@ -9606,7 +9606,7 @@
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN36">
         <v>4.4</v>
@@ -9671,61 +9671,61 @@
         <v>189</v>
       </c>
       <c r="F37">
+        <v>3.6</v>
+      </c>
+      <c r="G37">
         <v>3.65</v>
       </c>
-      <c r="G37">
-        <v>3.75</v>
-      </c>
       <c r="H37">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I37">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="J37">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K37">
         <v>3.9</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P37">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q37">
         <v>1.7</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T37">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U37">
         <v>2.5</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X37">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y37">
         <v>13</v>
@@ -9743,13 +9743,13 @@
         <v>9</v>
       </c>
       <c r="AD37">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE37">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF37">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG37">
         <v>16</v>
@@ -9758,22 +9758,22 @@
         <v>16</v>
       </c>
       <c r="AI37">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ37">
         <v>1000</v>
       </c>
       <c r="AK37">
+        <v>38</v>
+      </c>
+      <c r="AL37">
         <v>42</v>
       </c>
-      <c r="AL37">
-        <v>48</v>
-      </c>
       <c r="AM37">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN37">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO37">
         <v>11.5</v>
@@ -9785,112 +9785,112 @@
         <v>11.5</v>
       </c>
       <c r="AR37">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS37">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT37">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV37">
         <v>10</v>
       </c>
       <c r="AW37">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX37">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY37">
         <v>14</v>
       </c>
       <c r="AZ37">
+        <v>14</v>
+      </c>
+      <c r="BA37">
+        <v>26</v>
+      </c>
+      <c r="BB37">
+        <v>55</v>
+      </c>
+      <c r="BC37">
+        <v>32</v>
+      </c>
+      <c r="BD37">
+        <v>36</v>
+      </c>
+      <c r="BE37">
+        <v>30</v>
+      </c>
+      <c r="BF37">
+        <v>25</v>
+      </c>
+      <c r="BG37">
+        <v>10</v>
+      </c>
+      <c r="BH37">
+        <v>4.1</v>
+      </c>
+      <c r="BI37">
+        <v>3.6</v>
+      </c>
+      <c r="BJ37">
+        <v>9</v>
+      </c>
+      <c r="BK37">
+        <v>7.6</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>21</v>
+      </c>
+      <c r="BN37">
+        <v>7.4</v>
+      </c>
+      <c r="BO37">
+        <v>6.2</v>
+      </c>
+      <c r="BP37">
+        <v>27</v>
+      </c>
+      <c r="BQ37">
+        <v>20</v>
+      </c>
+      <c r="BR37">
+        <v>34</v>
+      </c>
+      <c r="BS37">
+        <v>24</v>
+      </c>
+      <c r="BT37">
+        <v>5.2</v>
+      </c>
+      <c r="BU37">
+        <v>4.5</v>
+      </c>
+      <c r="BV37">
+        <v>14</v>
+      </c>
+      <c r="BW37">
+        <v>12</v>
+      </c>
+      <c r="BX37">
+        <v>24</v>
+      </c>
+      <c r="BY37">
+        <v>17.5</v>
+      </c>
+      <c r="BZ37">
+        <v>18</v>
+      </c>
+      <c r="CA37">
         <v>13.5</v>
-      </c>
-      <c r="BA37">
-        <v>19.5</v>
-      </c>
-      <c r="BB37">
-        <v>32</v>
-      </c>
-      <c r="BC37">
-        <v>28</v>
-      </c>
-      <c r="BD37">
-        <v>28</v>
-      </c>
-      <c r="BE37">
-        <v>40</v>
-      </c>
-      <c r="BF37">
-        <v>19.5</v>
-      </c>
-      <c r="BG37">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH37">
-        <v>0</v>
-      </c>
-      <c r="BI37">
-        <v>0</v>
-      </c>
-      <c r="BJ37">
-        <v>0</v>
-      </c>
-      <c r="BK37">
-        <v>0</v>
-      </c>
-      <c r="BL37">
-        <v>0</v>
-      </c>
-      <c r="BM37">
-        <v>0</v>
-      </c>
-      <c r="BN37">
-        <v>0</v>
-      </c>
-      <c r="BO37">
-        <v>0</v>
-      </c>
-      <c r="BP37">
-        <v>0</v>
-      </c>
-      <c r="BQ37">
-        <v>0</v>
-      </c>
-      <c r="BR37">
-        <v>0</v>
-      </c>
-      <c r="BS37">
-        <v>0</v>
-      </c>
-      <c r="BT37">
-        <v>0</v>
-      </c>
-      <c r="BU37">
-        <v>0</v>
-      </c>
-      <c r="BV37">
-        <v>0</v>
-      </c>
-      <c r="BW37">
-        <v>0</v>
-      </c>
-      <c r="BX37">
-        <v>0</v>
-      </c>
-      <c r="BY37">
-        <v>0</v>
-      </c>
-      <c r="BZ37">
-        <v>0</v>
-      </c>
-      <c r="CA37">
-        <v>0</v>
       </c>
       <c r="CB37" t="s">
         <v>197</v>
@@ -9913,7 +9913,7 @@
         <v>190</v>
       </c>
       <c r="F38">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G38">
         <v>3.9</v>
@@ -9922,25 +9922,25 @@
         <v>2.02</v>
       </c>
       <c r="I38">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J38">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K38">
         <v>4.1</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P38">
         <v>2.3</v>
@@ -9949,10 +9949,10 @@
         <v>1.69</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T38">
         <v>1.65</v>
@@ -9961,13 +9961,13 @@
         <v>2.4</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X38">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y38">
         <v>12</v>
@@ -9976,19 +9976,19 @@
         <v>14.5</v>
       </c>
       <c r="AA38">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB38">
         <v>18</v>
       </c>
       <c r="AC38">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD38">
         <v>11</v>
       </c>
       <c r="AE38">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF38">
         <v>34</v>
@@ -9997,25 +9997,25 @@
         <v>16</v>
       </c>
       <c r="AH38">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI38">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ38">
         <v>80</v>
       </c>
       <c r="AK38">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL38">
         <v>55</v>
       </c>
       <c r="AM38">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN38">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO38">
         <v>11</v>
@@ -10024,7 +10024,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR38">
         <v>12.5</v>
@@ -10033,10 +10033,10 @@
         <v>22</v>
       </c>
       <c r="AT38">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU38">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV38">
         <v>9.800000000000001</v>
@@ -10045,94 +10045,94 @@
         <v>17</v>
       </c>
       <c r="AX38">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AY38">
+        <v>14</v>
+      </c>
+      <c r="AZ38">
+        <v>14.5</v>
+      </c>
+      <c r="BA38">
+        <v>26</v>
+      </c>
+      <c r="BB38">
+        <v>60</v>
+      </c>
+      <c r="BC38">
+        <v>34</v>
+      </c>
+      <c r="BD38">
+        <v>38</v>
+      </c>
+      <c r="BE38">
         <v>13.5</v>
       </c>
-      <c r="AZ38">
-        <v>14</v>
-      </c>
-      <c r="BA38">
-        <v>9</v>
-      </c>
-      <c r="BB38">
-        <v>11.5</v>
-      </c>
-      <c r="BC38">
-        <v>10.5</v>
-      </c>
-      <c r="BD38">
-        <v>10</v>
-      </c>
-      <c r="BE38">
-        <v>11.5</v>
-      </c>
       <c r="BF38">
-        <v>9.6</v>
+        <v>25</v>
       </c>
       <c r="BG38">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI38">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BJ38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK38">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO38">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BP38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT38">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BU38">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW38">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="s">
         <v>197</v>
@@ -10155,16 +10155,16 @@
         <v>191</v>
       </c>
       <c r="F39">
+        <v>2.22</v>
+      </c>
+      <c r="G39">
         <v>2.24</v>
-      </c>
-      <c r="G39">
-        <v>2.26</v>
       </c>
       <c r="H39">
         <v>3.5</v>
       </c>
       <c r="I39">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J39">
         <v>3.7</v>
@@ -10173,13 +10173,13 @@
         <v>3.75</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M39">
         <v>1.06</v>
       </c>
       <c r="N39">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O39">
         <v>1.25</v>
@@ -10194,7 +10194,7 @@
         <v>1.49</v>
       </c>
       <c r="S39">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T39">
         <v>1.64</v>
@@ -10203,22 +10203,22 @@
         <v>2.46</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X39">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y39">
         <v>16.5</v>
       </c>
       <c r="Z39">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB39">
         <v>12.5</v>
@@ -10236,7 +10236,7 @@
         <v>16</v>
       </c>
       <c r="AG39">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH39">
         <v>16</v>
@@ -10245,46 +10245,46 @@
         <v>48</v>
       </c>
       <c r="AJ39">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK39">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL39">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN39">
         <v>13.5</v>
       </c>
       <c r="AO39">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP39">
         <v>16</v>
       </c>
       <c r="AQ39">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR39">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AS39">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AT39">
         <v>11</v>
       </c>
       <c r="AU39">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV39">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW39">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX39">
         <v>14</v>
@@ -10293,31 +10293,31 @@
         <v>10</v>
       </c>
       <c r="AZ39">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA39">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB39">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC39">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD39">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BE39">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BF39">
         <v>11.5</v>
       </c>
       <c r="BG39">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BH39">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI39">
         <v>3.45</v>
@@ -10332,7 +10332,7 @@
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="BN39">
         <v>5.3</v>
@@ -10397,7 +10397,7 @@
         <v>192</v>
       </c>
       <c r="F40">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G40">
         <v>1.42</v>
@@ -10406,7 +10406,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I40">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J40">
         <v>5.4</v>
@@ -10415,16 +10415,16 @@
         <v>5.7</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P40">
         <v>2.34</v>
@@ -10433,22 +10433,22 @@
         <v>1.66</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T40">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U40">
         <v>1.91</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X40">
         <v>23</v>
@@ -10460,7 +10460,7 @@
         <v>110</v>
       </c>
       <c r="AA40">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AB40">
         <v>9.6</v>
@@ -10475,7 +10475,7 @@
         <v>1000</v>
       </c>
       <c r="AF40">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG40">
         <v>11</v>
@@ -10487,10 +10487,10 @@
         <v>140</v>
       </c>
       <c r="AJ40">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK40">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL40">
         <v>38</v>
@@ -10502,13 +10502,13 @@
         <v>5.7</v>
       </c>
       <c r="AO40">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP40">
         <v>18.5</v>
       </c>
       <c r="AQ40">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR40">
         <v>34</v>
@@ -10547,76 +10547,76 @@
         <v>13.5</v>
       </c>
       <c r="BD40">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE40">
         <v>42</v>
       </c>
       <c r="BF40">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG40">
         <v>44</v>
       </c>
       <c r="BH40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BJ40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK40">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN40">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BO40">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BR40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU40">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BV40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB40" t="s">
         <v>197</v>
@@ -10639,16 +10639,16 @@
         <v>193</v>
       </c>
       <c r="F41">
+        <v>3.85</v>
+      </c>
+      <c r="G41">
         <v>3.95</v>
       </c>
-      <c r="G41">
-        <v>4.1</v>
-      </c>
       <c r="H41">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="J41">
         <v>4</v>
@@ -10657,43 +10657,43 @@
         <v>4.1</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P41">
         <v>2.42</v>
       </c>
       <c r="Q41">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T41">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U41">
         <v>2.46</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X41">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y41">
         <v>12</v>
@@ -10708,58 +10708,58 @@
         <v>18.5</v>
       </c>
       <c r="AC41">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD41">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE41">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF41">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG41">
+        <v>16</v>
+      </c>
+      <c r="AH41">
         <v>16.5</v>
       </c>
-      <c r="AH41">
-        <v>17</v>
-      </c>
       <c r="AI41">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ41">
         <v>1000</v>
       </c>
       <c r="AK41">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL41">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="AM41">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN41">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO41">
         <v>10.5</v>
       </c>
       <c r="AP41">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AQ41">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR41">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS41">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU41">
         <v>8.6</v>
@@ -10771,94 +10771,94 @@
         <v>16.5</v>
       </c>
       <c r="AX41">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AY41">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ41">
         <v>14.5</v>
       </c>
       <c r="BA41">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BB41">
         <v>34</v>
       </c>
       <c r="BC41">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BD41">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BE41">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BF41">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BG41">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI41">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BJ41">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK41">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM41">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN41">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BO41">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP41">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BQ41">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BR41">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS41">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT41">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BU41">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV41">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BW41">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BX41">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY41">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BZ41">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA41">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CB41" t="s">
         <v>197</v>
@@ -10881,10 +10881,10 @@
         <v>194</v>
       </c>
       <c r="F42">
+        <v>1.16</v>
+      </c>
+      <c r="G42">
         <v>1.17</v>
-      </c>
-      <c r="G42">
-        <v>1.18</v>
       </c>
       <c r="H42">
         <v>19</v>
@@ -10893,13 +10893,13 @@
         <v>21</v>
       </c>
       <c r="J42">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="K42">
         <v>10.5</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M42">
         <v>1.01</v>
@@ -10914,25 +10914,25 @@
         <v>4.1</v>
       </c>
       <c r="Q42">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R42">
         <v>2.28</v>
       </c>
       <c r="S42">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="T42">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U42">
         <v>2.04</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="X42">
         <v>1000</v>
@@ -10965,7 +10965,7 @@
         <v>14</v>
       </c>
       <c r="AH42">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI42">
         <v>1000</v>
@@ -10983,7 +10983,7 @@
         <v>1000</v>
       </c>
       <c r="AN42">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AO42">
         <v>1000</v>
@@ -10998,7 +10998,7 @@
         <v>48</v>
       </c>
       <c r="AS42">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AT42">
         <v>15</v>
@@ -11013,13 +11013,13 @@
         <v>50</v>
       </c>
       <c r="AX42">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY42">
         <v>12</v>
       </c>
       <c r="AZ42">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BA42">
         <v>44</v>
@@ -11031,7 +11031,7 @@
         <v>11.5</v>
       </c>
       <c r="BD42">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE42">
         <v>42</v>
@@ -11058,7 +11058,7 @@
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN42">
         <v>4.3</v>
@@ -11088,16 +11088,16 @@
         <v>1000</v>
       </c>
       <c r="BW42">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="BZ42">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CA42">
         <v>4.6</v>
@@ -11129,7 +11129,7 @@
         <v>1.08</v>
       </c>
       <c r="H43">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I43">
         <v>40</v>
@@ -11141,7 +11141,7 @@
         <v>24</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M43">
         <v>1.01</v>
@@ -11159,22 +11159,22 @@
         <v>1.15</v>
       </c>
       <c r="R43">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="S43">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T43">
+        <v>1.96</v>
+      </c>
+      <c r="U43">
         <v>2</v>
       </c>
-      <c r="U43">
-        <v>1.98</v>
-      </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="X43">
         <v>240</v>
@@ -11189,7 +11189,7 @@
         <v>1000</v>
       </c>
       <c r="AB43">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC43">
         <v>70</v>
@@ -11201,7 +11201,7 @@
         <v>550</v>
       </c>
       <c r="AF43">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG43">
         <v>22</v>
@@ -11213,7 +11213,7 @@
         <v>1000</v>
       </c>
       <c r="AJ43">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AK43">
         <v>16.5</v>
@@ -11225,7 +11225,7 @@
         <v>1000</v>
       </c>
       <c r="AN43">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AO43">
         <v>340</v>
@@ -11240,7 +11240,7 @@
         <v>55</v>
       </c>
       <c r="AS43">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT43">
         <v>25</v>
@@ -11255,19 +11255,19 @@
         <v>120</v>
       </c>
       <c r="AX43">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY43">
         <v>19.5</v>
       </c>
       <c r="AZ43">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BA43">
         <v>48</v>
       </c>
       <c r="BB43">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC43">
         <v>15</v>
@@ -11279,28 +11279,28 @@
         <v>48</v>
       </c>
       <c r="BF43">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BG43">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BH43">
         <v>12</v>
       </c>
       <c r="BI43">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BJ43">
         <v>18</v>
       </c>
       <c r="BK43">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BL43">
         <v>120</v>
       </c>
       <c r="BM43">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BN43">
         <v>5.9</v>
@@ -11309,40 +11309,40 @@
         <v>4.5</v>
       </c>
       <c r="BP43">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BQ43">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BR43">
         <v>19</v>
       </c>
       <c r="BS43">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BT43">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BU43">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV43">
         <v>200</v>
       </c>
       <c r="BW43">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BX43">
         <v>120</v>
       </c>
       <c r="BY43">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BZ43">
         <v>4.2</v>
       </c>
       <c r="CA43">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="CB43" t="s">
         <v>197</v>
@@ -11365,7 +11365,7 @@
         <v>196</v>
       </c>
       <c r="F44">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G44">
         <v>3.65</v>
@@ -11374,7 +11374,7 @@
         <v>2.22</v>
       </c>
       <c r="I44">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J44">
         <v>3.6</v>
@@ -11383,7 +11383,7 @@
         <v>3.65</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M44">
         <v>1.07</v>
@@ -11392,10 +11392,10 @@
         <v>4.1</v>
       </c>
       <c r="O44">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P44">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q44">
         <v>1.89</v>
@@ -11413,10 +11413,10 @@
         <v>2.26</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X44">
         <v>15.5</v>
@@ -11440,34 +11440,34 @@
         <v>11</v>
       </c>
       <c r="AE44">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF44">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG44">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH44">
         <v>16.5</v>
       </c>
       <c r="AI44">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ44">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK44">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL44">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM44">
         <v>85</v>
       </c>
       <c r="AN44">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO44">
         <v>16</v>
@@ -11476,16 +11476,16 @@
         <v>14</v>
       </c>
       <c r="AQ44">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR44">
         <v>13</v>
       </c>
       <c r="AS44">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AT44">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU44">
         <v>7.6</v>
@@ -11494,97 +11494,97 @@
         <v>10</v>
       </c>
       <c r="AW44">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX44">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY44">
         <v>13.5</v>
       </c>
       <c r="AZ44">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA44">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BB44">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BC44">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BD44">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BE44">
         <v>36</v>
       </c>
       <c r="BF44">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BG44">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH44">
         <v>3.5</v>
       </c>
       <c r="BI44">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="BJ44">
         <v>9.800000000000001</v>
       </c>
       <c r="BK44">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BL44">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM44">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BN44">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO44">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BP44">
         <v>29</v>
       </c>
       <c r="BQ44">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BR44">
         <v>40</v>
       </c>
       <c r="BS44">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT44">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BU44">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BV44">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW44">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BX44">
         <v>29</v>
       </c>
       <c r="BY44">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ44">
         <v>25</v>
       </c>
       <c r="CA44">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB44" t="s">
         <v>197</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -607,7 +607,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-09-14 17:40:22</t>
+    <t>2026-09-14 19:56:13</t>
   </si>
 </sst>
 </file>
@@ -1210,13 +1210,13 @@
         <v>4.4</v>
       </c>
       <c r="I2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
         <v>3.75</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1234,7 +1234,7 @@
         <v>2.16</v>
       </c>
       <c r="Q2">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R2">
         <v>1.45</v>
@@ -1246,7 +1246,7 @@
         <v>1.74</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
         <v>1.27</v>
@@ -1309,7 +1309,7 @@
         <v>60</v>
       </c>
       <c r="AP2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2">
         <v>15</v>
@@ -1372,7 +1372,7 @@
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1402,7 +1402,7 @@
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1446,7 +1446,7 @@
         <v>2.28</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
         <v>3.55</v>
@@ -1458,7 +1458,7 @@
         <v>3.25</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
         <v>1.02</v>
@@ -1473,7 +1473,7 @@
         <v>1.51</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -1485,7 +1485,7 @@
         <v>5.1</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
         <v>1.82</v>
@@ -1566,7 +1566,7 @@
         <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>14</v>
@@ -1608,61 +1608,61 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>197</v>
@@ -1685,7 +1685,7 @@
         <v>156</v>
       </c>
       <c r="F4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>5.4</v>
@@ -1718,7 +1718,7 @@
         <v>2.5</v>
       </c>
       <c r="Q4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
         <v>1.59</v>
@@ -1745,7 +1745,7 @@
         <v>12</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AA4">
         <v>18.5</v>
@@ -1817,7 +1817,7 @@
         <v>14.5</v>
       </c>
       <c r="AX4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY4">
         <v>17.5</v>
@@ -1826,22 +1826,22 @@
         <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG4">
         <v>6.8</v>
@@ -1850,61 +1850,61 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>197</v>
@@ -1927,13 +1927,13 @@
         <v>157</v>
       </c>
       <c r="F5">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I5">
         <v>4.4</v>
@@ -1942,7 +1942,7 @@
         <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1951,7 +1951,7 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O5">
         <v>1.23</v>
@@ -1966,7 +1966,7 @@
         <v>1.46</v>
       </c>
       <c r="S5">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T5">
         <v>1.63</v>
@@ -2092,61 +2092,61 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>197</v>
@@ -2169,22 +2169,22 @@
         <v>158</v>
       </c>
       <c r="F6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H6">
         <v>2.52</v>
       </c>
       <c r="I6">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J6">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="K6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
         <v>1.45</v>
@@ -2202,10 +2202,10 @@
         <v>1.5</v>
       </c>
       <c r="Q6">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S6">
         <v>4.8</v>
@@ -2217,10 +2217,10 @@
         <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W6">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X6">
         <v>11.5</v>
@@ -2334,61 +2334,61 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>197</v>
@@ -2459,10 +2459,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2576,61 +2576,61 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>197</v>
@@ -2818,61 +2818,61 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>197</v>
@@ -3060,61 +3060,61 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>197</v>
@@ -3137,7 +3137,7 @@
         <v>162</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G10">
         <v>990</v>
@@ -3149,7 +3149,7 @@
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3167,7 +3167,7 @@
         <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q10">
         <v>1.37</v>
@@ -3176,7 +3176,7 @@
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>1.05</v>
+        <v>2.72</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3185,10 +3185,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3302,61 +3302,61 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>197</v>
@@ -3379,13 +3379,13 @@
         <v>163</v>
       </c>
       <c r="F11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G11">
         <v>6.4</v>
       </c>
       <c r="H11">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="I11">
         <v>1.68</v>
@@ -3394,7 +3394,7 @@
         <v>4.3</v>
       </c>
       <c r="K11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3418,10 +3418,10 @@
         <v>1.54</v>
       </c>
       <c r="S11">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T11">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U11">
         <v>2.2</v>
@@ -3430,7 +3430,7 @@
         <v>2.46</v>
       </c>
       <c r="W11">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X11">
         <v>26</v>
@@ -3457,7 +3457,7 @@
         <v>16.5</v>
       </c>
       <c r="AF11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG11">
         <v>26</v>
@@ -3481,7 +3481,7 @@
         <v>100</v>
       </c>
       <c r="AN11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO11">
         <v>7.4</v>
@@ -3514,7 +3514,7 @@
         <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ11">
         <v>16.5</v>
@@ -3550,55 +3550,55 @@
         <v>13</v>
       </c>
       <c r="BK11">
-        <v>6.2</v>
+        <v>2.62</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>3.25</v>
       </c>
       <c r="BN11">
         <v>13</v>
       </c>
       <c r="BO11">
-        <v>6.2</v>
+        <v>2.62</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>21</v>
+        <v>3.1</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>21</v>
+        <v>3.1</v>
       </c>
       <c r="BT11">
         <v>5.9</v>
       </c>
       <c r="BU11">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="BV11">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BW11">
-        <v>6.6</v>
+        <v>2.64</v>
       </c>
       <c r="BX11">
         <v>30</v>
       </c>
       <c r="BY11">
-        <v>14</v>
+        <v>2.96</v>
       </c>
       <c r="BZ11">
         <v>20</v>
       </c>
       <c r="CA11">
-        <v>9.199999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="CB11" t="s">
         <v>197</v>
@@ -3627,16 +3627,16 @@
         <v>4.4</v>
       </c>
       <c r="H12">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I12">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J12">
+        <v>3.5</v>
+      </c>
+      <c r="K12">
         <v>3.55</v>
-      </c>
-      <c r="K12">
-        <v>3.65</v>
       </c>
       <c r="L12">
         <v>1.46</v>
@@ -3651,7 +3651,7 @@
         <v>1.38</v>
       </c>
       <c r="P12">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q12">
         <v>2.16</v>
@@ -3663,13 +3663,13 @@
         <v>3.95</v>
       </c>
       <c r="T12">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V12">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W12">
         <v>1.29</v>
@@ -3747,7 +3747,7 @@
         <v>7.4</v>
       </c>
       <c r="AV12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12">
         <v>20</v>
@@ -3783,64 +3783,64 @@
         <v>15</v>
       </c>
       <c r="BH12">
-        <v>3.25</v>
+        <v>14</v>
       </c>
       <c r="BI12">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="BJ12">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BL12">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>21</v>
+        <v>1.96</v>
       </c>
       <c r="BN12">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BO12">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BP12">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>29</v>
+        <v>3.45</v>
       </c>
       <c r="BR12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>38</v>
+        <v>1.91</v>
       </c>
       <c r="BT12">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BU12">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BV12">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BW12">
-        <v>9.6</v>
+        <v>3.7</v>
       </c>
       <c r="BX12">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BY12">
-        <v>23</v>
+        <v>1.88</v>
       </c>
       <c r="BZ12">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="CA12">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="CB12" t="s">
         <v>197</v>
@@ -3869,10 +3869,10 @@
         <v>5.6</v>
       </c>
       <c r="H13">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I13">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="J13">
         <v>4.3</v>
@@ -3881,10 +3881,10 @@
         <v>4.5</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M13">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
         <v>4.8</v>
@@ -3905,13 +3905,13 @@
         <v>2.84</v>
       </c>
       <c r="T13">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V13">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="W13">
         <v>1.21</v>
@@ -4001,7 +4001,7 @@
         <v>18.5</v>
       </c>
       <c r="AZ13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA13">
         <v>26</v>
@@ -4016,7 +4016,7 @@
         <v>50</v>
       </c>
       <c r="BE13">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="BF13">
         <v>48</v>
@@ -4040,25 +4040,25 @@
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>6.4</v>
+        <v>2.16</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BT13">
         <v>1000</v>
@@ -4070,19 +4070,19 @@
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>7.4</v>
+        <v>2.28</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="CB13" t="s">
         <v>197</v>
@@ -4153,10 +4153,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4270,55 +4270,55 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4347,13 +4347,13 @@
         <v>167</v>
       </c>
       <c r="F15">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G15">
         <v>2.98</v>
       </c>
       <c r="H15">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I15">
         <v>2.48</v>
@@ -4377,13 +4377,13 @@
         <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q15">
         <v>1.53</v>
       </c>
       <c r="R15">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="S15">
         <v>2.18</v>
@@ -4395,118 +4395,118 @@
         <v>2.8</v>
       </c>
       <c r="V15">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W15">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X15">
+        <v>29</v>
+      </c>
+      <c r="Y15">
+        <v>17.5</v>
+      </c>
+      <c r="Z15">
+        <v>21</v>
+      </c>
+      <c r="AA15">
         <v>34</v>
       </c>
-      <c r="Y15">
+      <c r="AB15">
+        <v>19</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+      <c r="AD15">
+        <v>12.5</v>
+      </c>
+      <c r="AE15">
         <v>23</v>
       </c>
-      <c r="Z15">
-        <v>23</v>
-      </c>
-      <c r="AA15">
-        <v>38</v>
-      </c>
-      <c r="AB15">
+      <c r="AF15">
         <v>25</v>
       </c>
-      <c r="AC15">
+      <c r="AG15">
+        <v>14</v>
+      </c>
+      <c r="AH15">
+        <v>15</v>
+      </c>
+      <c r="AI15">
+        <v>27</v>
+      </c>
+      <c r="AJ15">
+        <v>46</v>
+      </c>
+      <c r="AK15">
+        <v>27</v>
+      </c>
+      <c r="AL15">
+        <v>30</v>
+      </c>
+      <c r="AM15">
+        <v>50</v>
+      </c>
+      <c r="AN15">
+        <v>15.5</v>
+      </c>
+      <c r="AO15">
+        <v>11.5</v>
+      </c>
+      <c r="AP15">
+        <v>9.4</v>
+      </c>
+      <c r="AQ15">
+        <v>15</v>
+      </c>
+      <c r="AR15">
+        <v>17.5</v>
+      </c>
+      <c r="AS15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT15">
+        <v>16.5</v>
+      </c>
+      <c r="AU15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15">
+        <v>11</v>
+      </c>
+      <c r="AW15">
+        <v>19.5</v>
+      </c>
+      <c r="AX15">
+        <v>21</v>
+      </c>
+      <c r="AY15">
         <v>12</v>
       </c>
-      <c r="AD15">
-        <v>15</v>
-      </c>
-      <c r="AE15">
-        <v>25</v>
-      </c>
-      <c r="AF15">
-        <v>28</v>
-      </c>
-      <c r="AG15">
-        <v>16</v>
-      </c>
-      <c r="AH15">
-        <v>17</v>
-      </c>
-      <c r="AI15">
-        <v>32</v>
-      </c>
-      <c r="AJ15">
-        <v>65</v>
-      </c>
-      <c r="AK15">
-        <v>30</v>
-      </c>
-      <c r="AL15">
-        <v>34</v>
-      </c>
-      <c r="AM15">
-        <v>65</v>
-      </c>
-      <c r="AN15">
-        <v>18.5</v>
-      </c>
-      <c r="AO15">
+      <c r="AZ15">
         <v>13</v>
       </c>
-      <c r="AP15">
-        <v>19</v>
-      </c>
-      <c r="AQ15">
-        <v>13</v>
-      </c>
-      <c r="AR15">
-        <v>15.5</v>
-      </c>
-      <c r="AS15">
-        <v>4.6</v>
-      </c>
-      <c r="AT15">
-        <v>14.5</v>
-      </c>
-      <c r="AU15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV15">
+      <c r="BA15">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW15">
-        <v>16.5</v>
-      </c>
-      <c r="AX15">
-        <v>16</v>
-      </c>
-      <c r="AY15">
+      <c r="BB15">
         <v>10.5</v>
       </c>
-      <c r="AZ15">
-        <v>11.5</v>
-      </c>
-      <c r="BA15">
-        <v>16.5</v>
-      </c>
-      <c r="BB15">
-        <v>4.9</v>
-      </c>
       <c r="BC15">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD15">
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>4.9</v>
+        <v>36</v>
       </c>
       <c r="BF15">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG15">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4518,55 +4518,55 @@
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>5</v>
+        <v>1.42</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.3</v>
+        <v>1.42</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>3.85</v>
+        <v>1.23</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB15" t="s">
         <v>197</v>
@@ -4625,16 +4625,16 @@
         <v>1.47</v>
       </c>
       <c r="R16">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S16">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T16">
         <v>1.49</v>
       </c>
       <c r="U16">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="V16">
         <v>1.38</v>
@@ -4691,22 +4691,22 @@
         <v>48</v>
       </c>
       <c r="AN16">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO16">
         <v>19</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ16">
         <v>20</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT16">
         <v>15</v>
@@ -4718,7 +4718,7 @@
         <v>14</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AX16">
         <v>15.5</v>
@@ -4730,10 +4730,10 @@
         <v>13</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BC16">
         <v>16</v>
@@ -4742,7 +4742,7 @@
         <v>21</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BF16">
         <v>7.2</v>
@@ -4766,7 +4766,7 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>21</v>
+        <v>2.42</v>
       </c>
       <c r="BN16">
         <v>6</v>
@@ -4775,16 +4775,16 @@
         <v>4.5</v>
       </c>
       <c r="BP16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ16">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="BR16">
         <v>28</v>
       </c>
       <c r="BS16">
-        <v>12</v>
+        <v>2.28</v>
       </c>
       <c r="BT16">
         <v>9</v>
@@ -4796,19 +4796,19 @@
         <v>32</v>
       </c>
       <c r="BW16">
-        <v>14.5</v>
+        <v>2.3</v>
       </c>
       <c r="BX16">
         <v>38</v>
       </c>
       <c r="BY16">
-        <v>16.5</v>
+        <v>2.34</v>
       </c>
       <c r="BZ16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA16">
-        <v>8</v>
+        <v>3.55</v>
       </c>
       <c r="CB16" t="s">
         <v>197</v>
@@ -4879,10 +4879,10 @@
         <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4996,61 +4996,61 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
         <v>197</v>
@@ -5121,10 +5121,10 @@
         <v>1.11</v>
       </c>
       <c r="V18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5238,55 +5238,55 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5363,10 +5363,10 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5480,55 +5480,55 @@
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5557,19 +5557,19 @@
         <v>172</v>
       </c>
       <c r="F20">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G20">
         <v>2.34</v>
       </c>
       <c r="H20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I20">
         <v>3.4</v>
       </c>
       <c r="J20">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
         <v>3.85</v>
@@ -5590,13 +5590,13 @@
         <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="R20">
         <v>1.48</v>
       </c>
       <c r="S20">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T20">
         <v>1.66</v>
@@ -5722,7 +5722,7 @@
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>3.15</v>
+        <v>1.49</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
@@ -5734,7 +5734,7 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BN20">
         <v>7.4</v>
@@ -5752,7 +5752,7 @@
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BT20">
         <v>1000</v>
@@ -5764,19 +5764,19 @@
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="CB20" t="s">
         <v>197</v>
@@ -5847,10 +5847,10 @@
         <v>1.11</v>
       </c>
       <c r="V21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5964,61 +5964,61 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>197</v>
@@ -6044,7 +6044,7 @@
         <v>2.62</v>
       </c>
       <c r="G22">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H22">
         <v>3.2</v>
@@ -6068,10 +6068,10 @@
         <v>3.1</v>
       </c>
       <c r="O22">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P22">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q22">
         <v>2.4</v>
@@ -6083,16 +6083,16 @@
         <v>4.7</v>
       </c>
       <c r="T22">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U22">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V22">
         <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X22">
         <v>10.5</v>
@@ -6113,19 +6113,19 @@
         <v>7</v>
       </c>
       <c r="AD22">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG22">
         <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI22">
         <v>65</v>
@@ -6197,7 +6197,7 @@
         <v>42</v>
       </c>
       <c r="BF22">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG22">
         <v>26</v>
@@ -6286,13 +6286,13 @@
         <v>2.68</v>
       </c>
       <c r="G23">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H23">
         <v>2.48</v>
       </c>
       <c r="I23">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="J23">
         <v>3.3</v>
@@ -6304,13 +6304,13 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N23">
         <v>3.4</v>
       </c>
       <c r="O23">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P23">
         <v>1.92</v>
@@ -6319,10 +6319,10 @@
         <v>1.83</v>
       </c>
       <c r="R23">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S23">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="T23">
         <v>1.11</v>
@@ -6331,10 +6331,10 @@
         <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W23">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6448,61 +6448,61 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
         <v>197</v>
@@ -6525,22 +6525,22 @@
         <v>176</v>
       </c>
       <c r="F24">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="G24">
         <v>2.9</v>
       </c>
       <c r="H24">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I24">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="J24">
         <v>3.65</v>
       </c>
       <c r="K24">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L24">
         <v>1.22</v>
@@ -6549,31 +6549,31 @@
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O24">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P24">
         <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R24">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S24">
         <v>2.06</v>
       </c>
       <c r="T24">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="U24">
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W24">
         <v>1.52</v>
@@ -6582,13 +6582,13 @@
         <v>1000</v>
       </c>
       <c r="Y24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z24">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA24">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB24">
         <v>21</v>
@@ -6597,7 +6597,7 @@
         <v>13</v>
       </c>
       <c r="AD24">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE24">
         <v>34</v>
@@ -6606,7 +6606,7 @@
         <v>30</v>
       </c>
       <c r="AG24">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH24">
         <v>21</v>
@@ -6615,7 +6615,7 @@
         <v>46</v>
       </c>
       <c r="AJ24">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK24">
         <v>38</v>
@@ -6627,10 +6627,10 @@
         <v>85</v>
       </c>
       <c r="AN24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO24">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP24">
         <v>1.03</v>
@@ -6639,7 +6639,7 @@
         <v>9.6</v>
       </c>
       <c r="AR24">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS24">
         <v>1.03</v>
@@ -6651,13 +6651,13 @@
         <v>6.2</v>
       </c>
       <c r="AV24">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AW24">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AX24">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY24">
         <v>8.199999999999999</v>
@@ -6672,7 +6672,7 @@
         <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD24">
         <v>1.03</v>
@@ -6681,46 +6681,46 @@
         <v>1.03</v>
       </c>
       <c r="BF24">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG24">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BJ24">
         <v>11.5</v>
       </c>
       <c r="BK24">
-        <v>5.6</v>
+        <v>1.76</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>21</v>
+        <v>2.02</v>
       </c>
       <c r="BN24">
         <v>8.199999999999999</v>
       </c>
       <c r="BO24">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP24">
         <v>26</v>
       </c>
       <c r="BQ24">
-        <v>12</v>
+        <v>1.92</v>
       </c>
       <c r="BR24">
         <v>36</v>
       </c>
       <c r="BS24">
-        <v>16.5</v>
+        <v>1.96</v>
       </c>
       <c r="BT24">
         <v>8</v>
@@ -6732,19 +6732,19 @@
         <v>25</v>
       </c>
       <c r="BW24">
-        <v>11.5</v>
+        <v>1.91</v>
       </c>
       <c r="BX24">
         <v>36</v>
       </c>
       <c r="BY24">
-        <v>16.5</v>
+        <v>1.96</v>
       </c>
       <c r="BZ24">
         <v>25</v>
       </c>
       <c r="CA24">
-        <v>11.5</v>
+        <v>1.91</v>
       </c>
       <c r="CB24" t="s">
         <v>197</v>
@@ -6797,16 +6797,16 @@
         <v>1.15</v>
       </c>
       <c r="P25">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="Q25">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R25">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S25">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="T25">
         <v>1.41</v>
@@ -6875,31 +6875,31 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AQ25">
         <v>16</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="AU25">
         <v>8</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="AY25">
         <v>8.4</v>
@@ -6908,85 +6908,85 @@
         <v>11</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="BB25">
         <v>17</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BD25">
         <v>17.5</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="BF25">
-        <v>6</v>
+        <v>1.81</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
         <v>197</v>
@@ -7045,7 +7045,7 @@
         <v>1.35</v>
       </c>
       <c r="R26">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S26">
         <v>1.92</v>
@@ -7174,61 +7174,61 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
         <v>197</v>
@@ -7263,7 +7263,7 @@
         <v>2.4</v>
       </c>
       <c r="J27">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K27">
         <v>4.3</v>
@@ -7416,61 +7416,61 @@
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
         <v>197</v>
@@ -7493,7 +7493,7 @@
         <v>180</v>
       </c>
       <c r="F28">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G28">
         <v>6.6</v>
@@ -7508,7 +7508,7 @@
         <v>3.45</v>
       </c>
       <c r="K28">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7598,7 +7598,7 @@
         <v>200</v>
       </c>
       <c r="AO28">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP28">
         <v>9.4</v>
@@ -7658,61 +7658,61 @@
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="s">
         <v>197</v>
@@ -7741,13 +7741,13 @@
         <v>1.46</v>
       </c>
       <c r="H29">
+        <v>8.6</v>
+      </c>
+      <c r="I29">
         <v>8.800000000000001</v>
       </c>
-      <c r="I29">
-        <v>9</v>
-      </c>
       <c r="J29">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K29">
         <v>5.2</v>
@@ -7777,7 +7777,7 @@
         <v>2.98</v>
       </c>
       <c r="T29">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U29">
         <v>1.89</v>
@@ -7786,16 +7786,16 @@
         <v>1.12</v>
       </c>
       <c r="W29">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X29">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y29">
         <v>29</v>
       </c>
       <c r="Z29">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA29">
         <v>350</v>
@@ -7828,7 +7828,7 @@
         <v>11.5</v>
       </c>
       <c r="AK29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL29">
         <v>40</v>
@@ -7867,7 +7867,7 @@
         <v>40</v>
       </c>
       <c r="AX29">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY29">
         <v>9.6</v>
@@ -7888,7 +7888,7 @@
         <v>32</v>
       </c>
       <c r="BE29">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF29">
         <v>6</v>
@@ -7897,64 +7897,64 @@
         <v>44</v>
       </c>
       <c r="BH29">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BJ29">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL29">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BN29">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BP29">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>7.6</v>
+        <v>1.98</v>
       </c>
       <c r="BR29">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BT29">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>5.9</v>
+        <v>2.34</v>
       </c>
       <c r="BV29">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BX29">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ29">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="CB29" t="s">
         <v>197</v>
@@ -8025,10 +8025,10 @@
         <v>1.11</v>
       </c>
       <c r="V30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8142,61 +8142,61 @@
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
       </c>
       <c r="BK30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30">
         <v>1000</v>
       </c>
       <c r="BO30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30">
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="s">
         <v>197</v>
@@ -8267,10 +8267,10 @@
         <v>1.11</v>
       </c>
       <c r="V31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8384,61 +8384,61 @@
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN31">
         <v>1000</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP31">
         <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT31">
         <v>1000</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31">
         <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="s">
         <v>197</v>
@@ -8464,16 +8464,16 @@
         <v>3.9</v>
       </c>
       <c r="G32">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H32">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I32">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="J32">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K32">
         <v>4.8</v>
@@ -8485,19 +8485,19 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="O32">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P32">
         <v>2.56</v>
       </c>
       <c r="Q32">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R32">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="S32">
         <v>2.2</v>
@@ -8506,13 +8506,13 @@
         <v>1.51</v>
       </c>
       <c r="U32">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V32">
         <v>2.06</v>
       </c>
       <c r="W32">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8566,7 +8566,7 @@
         <v>1000</v>
       </c>
       <c r="AO32">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP32">
         <v>1.03</v>
@@ -8626,61 +8626,61 @@
         <v>1000</v>
       </c>
       <c r="BI32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ32">
         <v>1000</v>
       </c>
       <c r="BK32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP32">
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT32">
         <v>1000</v>
       </c>
       <c r="BU32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB32" t="s">
         <v>197</v>
@@ -8703,7 +8703,7 @@
         <v>185</v>
       </c>
       <c r="F33">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G33">
         <v>1.86</v>
@@ -8712,13 +8712,13 @@
         <v>4.7</v>
       </c>
       <c r="I33">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>3.85</v>
       </c>
       <c r="K33">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8730,7 +8730,7 @@
         <v>4.1</v>
       </c>
       <c r="O33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P33">
         <v>1.98</v>
@@ -8739,19 +8739,19 @@
         <v>1.77</v>
       </c>
       <c r="R33">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S33">
         <v>2.86</v>
       </c>
       <c r="T33">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U33">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V33">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W33">
         <v>2.16</v>
@@ -8868,61 +8868,61 @@
         <v>1000</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="s">
         <v>197</v>
@@ -8954,13 +8954,13 @@
         <v>2.98</v>
       </c>
       <c r="I34">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J34">
         <v>3.55</v>
       </c>
       <c r="K34">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L34">
         <v>1.28</v>
@@ -8996,7 +8996,7 @@
         <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X34">
         <v>21</v>
@@ -9110,19 +9110,19 @@
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BJ34">
         <v>13</v>
       </c>
       <c r="BK34">
-        <v>5.6</v>
+        <v>1.63</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>21</v>
+        <v>1.86</v>
       </c>
       <c r="BN34">
         <v>7.8</v>
@@ -9134,13 +9134,13 @@
         <v>25</v>
       </c>
       <c r="BQ34">
-        <v>10.5</v>
+        <v>1.73</v>
       </c>
       <c r="BR34">
         <v>40</v>
       </c>
       <c r="BS34">
-        <v>16.5</v>
+        <v>1.78</v>
       </c>
       <c r="BT34">
         <v>9</v>
@@ -9152,19 +9152,19 @@
         <v>34</v>
       </c>
       <c r="BW34">
-        <v>14</v>
+        <v>1.77</v>
       </c>
       <c r="BX34">
         <v>48</v>
       </c>
       <c r="BY34">
-        <v>19</v>
+        <v>1.79</v>
       </c>
       <c r="BZ34">
         <v>32</v>
       </c>
       <c r="CA34">
-        <v>13.5</v>
+        <v>1.76</v>
       </c>
       <c r="CB34" t="s">
         <v>197</v>
@@ -9196,10 +9196,10 @@
         <v>1.04</v>
       </c>
       <c r="I35">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J35">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9217,7 +9217,7 @@
         <v>1.15</v>
       </c>
       <c r="P35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q35">
         <v>1.15</v>
@@ -9226,7 +9226,7 @@
         <v>1.18</v>
       </c>
       <c r="S35">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T35">
         <v>1.11</v>
@@ -9235,10 +9235,10 @@
         <v>1.11</v>
       </c>
       <c r="V35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9352,61 +9352,61 @@
         <v>1000</v>
       </c>
       <c r="BI35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ35">
         <v>1000</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN35">
         <v>1000</v>
       </c>
       <c r="BO35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP35">
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT35">
         <v>1000</v>
       </c>
       <c r="BU35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB35" t="s">
         <v>197</v>
@@ -9429,13 +9429,13 @@
         <v>188</v>
       </c>
       <c r="F36">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G36">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H36">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I36">
         <v>5.8</v>
@@ -9444,31 +9444,31 @@
         <v>4.2</v>
       </c>
       <c r="K36">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L36">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M36">
         <v>1.05</v>
       </c>
       <c r="N36">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O36">
         <v>1.25</v>
       </c>
       <c r="P36">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q36">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R36">
         <v>1.48</v>
       </c>
       <c r="S36">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="T36">
         <v>1.79</v>
@@ -9480,10 +9480,10 @@
         <v>1.2</v>
       </c>
       <c r="W36">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X36">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y36">
         <v>22</v>
@@ -9519,10 +9519,10 @@
         <v>75</v>
       </c>
       <c r="AJ36">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK36">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL36">
         <v>38</v>
@@ -9543,10 +9543,10 @@
         <v>18.5</v>
       </c>
       <c r="AR36">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS36">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT36">
         <v>9</v>
@@ -9558,7 +9558,7 @@
         <v>17.5</v>
       </c>
       <c r="AW36">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX36">
         <v>9.800000000000001</v>
@@ -9570,7 +9570,7 @@
         <v>17</v>
       </c>
       <c r="BA36">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB36">
         <v>15</v>
@@ -9579,76 +9579,76 @@
         <v>14.5</v>
       </c>
       <c r="BD36">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE36">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF36">
         <v>7.6</v>
       </c>
       <c r="BG36">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH36">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI36">
-        <v>3.5</v>
+        <v>1.59</v>
       </c>
       <c r="BJ36">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK36">
-        <v>8.6</v>
+        <v>2.2</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>21</v>
+        <v>2.48</v>
       </c>
       <c r="BN36">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO36">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BP36">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ36">
-        <v>9.4</v>
+        <v>2.24</v>
       </c>
       <c r="BR36">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS36">
-        <v>17.5</v>
+        <v>2.48</v>
       </c>
       <c r="BT36">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU36">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>32</v>
+        <v>2.48</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>36</v>
+        <v>2.48</v>
       </c>
       <c r="BZ36">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA36">
-        <v>13</v>
+        <v>2.48</v>
       </c>
       <c r="CB36" t="s">
         <v>197</v>
@@ -9674,7 +9674,7 @@
         <v>3.6</v>
       </c>
       <c r="G37">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H37">
         <v>2.16</v>
@@ -9683,10 +9683,10 @@
         <v>2.18</v>
       </c>
       <c r="J37">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K37">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L37">
         <v>1.33</v>
@@ -9695,13 +9695,13 @@
         <v>1.05</v>
       </c>
       <c r="N37">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O37">
         <v>1.23</v>
       </c>
       <c r="P37">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q37">
         <v>1.7</v>
@@ -9710,7 +9710,7 @@
         <v>1.54</v>
       </c>
       <c r="S37">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T37">
         <v>1.62</v>
@@ -9719,40 +9719,40 @@
         <v>2.5</v>
       </c>
       <c r="V37">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="W37">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X37">
         <v>21</v>
       </c>
       <c r="Y37">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z37">
         <v>15.5</v>
       </c>
       <c r="AA37">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AB37">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC37">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD37">
         <v>11</v>
       </c>
       <c r="AE37">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF37">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG37">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH37">
         <v>16</v>
@@ -9767,7 +9767,7 @@
         <v>38</v>
       </c>
       <c r="AL37">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM37">
         <v>70</v>
@@ -9776,10 +9776,10 @@
         <v>29</v>
       </c>
       <c r="AO37">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP37">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ37">
         <v>11.5</v>
@@ -9803,10 +9803,10 @@
         <v>17.5</v>
       </c>
       <c r="AX37">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AY37">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ37">
         <v>14</v>
@@ -9815,82 +9815,82 @@
         <v>26</v>
       </c>
       <c r="BB37">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC37">
         <v>32</v>
       </c>
       <c r="BD37">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE37">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF37">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG37">
         <v>10</v>
       </c>
       <c r="BH37">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI37">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ37">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK37">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN37">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO37">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP37">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="BR37">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS37">
-        <v>24</v>
+        <v>1.04</v>
       </c>
       <c r="BT37">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU37">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV37">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW37">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX37">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY37">
-        <v>17.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ37">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA37">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB37" t="s">
         <v>197</v>
@@ -9913,7 +9913,7 @@
         <v>190</v>
       </c>
       <c r="F38">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G38">
         <v>3.9</v>
@@ -9922,7 +9922,7 @@
         <v>2.02</v>
       </c>
       <c r="I38">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J38">
         <v>4</v>
@@ -9931,28 +9931,28 @@
         <v>4.1</v>
       </c>
       <c r="L38">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M38">
         <v>1.05</v>
       </c>
       <c r="N38">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>1.23</v>
       </c>
       <c r="P38">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q38">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R38">
         <v>1.52</v>
       </c>
       <c r="S38">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T38">
         <v>1.65</v>
@@ -9961,7 +9961,7 @@
         <v>2.4</v>
       </c>
       <c r="V38">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W38">
         <v>1.34</v>
@@ -10000,7 +10000,7 @@
         <v>16.5</v>
       </c>
       <c r="AI38">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ38">
         <v>80</v>
@@ -10084,31 +10084,31 @@
         <v>1000</v>
       </c>
       <c r="BK38">
-        <v>6.4</v>
+        <v>1.92</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BN38">
         <v>1000</v>
       </c>
       <c r="BO38">
-        <v>5.6</v>
+        <v>1.84</v>
       </c>
       <c r="BP38">
         <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BT38">
         <v>6.2</v>
@@ -10120,19 +10120,19 @@
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>8.800000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="CB38" t="s">
         <v>197</v>
@@ -10155,22 +10155,22 @@
         <v>191</v>
       </c>
       <c r="F39">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G39">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="H39">
+        <v>3.4</v>
+      </c>
+      <c r="I39">
         <v>3.5</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>3.6</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>3.7</v>
-      </c>
-      <c r="K39">
-        <v>3.75</v>
       </c>
       <c r="L39">
         <v>1.35</v>
@@ -10188,13 +10188,13 @@
         <v>2.24</v>
       </c>
       <c r="Q39">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R39">
         <v>1.49</v>
       </c>
       <c r="S39">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="T39">
         <v>1.64</v>
@@ -10203,49 +10203,49 @@
         <v>2.46</v>
       </c>
       <c r="V39">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="X39">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y39">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z39">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA39">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB39">
         <v>12.5</v>
       </c>
       <c r="AC39">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD39">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE39">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF39">
         <v>16</v>
       </c>
       <c r="AG39">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH39">
         <v>16</v>
       </c>
       <c r="AI39">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ39">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK39">
         <v>22</v>
@@ -10257,10 +10257,10 @@
         <v>75</v>
       </c>
       <c r="AN39">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO39">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP39">
         <v>16</v>
@@ -10269,7 +10269,7 @@
         <v>14.5</v>
       </c>
       <c r="AR39">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS39">
         <v>50</v>
@@ -10281,10 +10281,10 @@
         <v>7.6</v>
       </c>
       <c r="AV39">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW39">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX39">
         <v>14</v>
@@ -10305,76 +10305,76 @@
         <v>19</v>
       </c>
       <c r="BD39">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE39">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="BF39">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG39">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BH39">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI39">
-        <v>3.45</v>
+        <v>1.48</v>
       </c>
       <c r="BJ39">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK39">
-        <v>7.8</v>
+        <v>1.98</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>21</v>
+        <v>2.26</v>
       </c>
       <c r="BN39">
+        <v>1000</v>
+      </c>
+      <c r="BO39">
+        <v>4.5</v>
+      </c>
+      <c r="BP39">
+        <v>1000</v>
+      </c>
+      <c r="BQ39">
+        <v>2.26</v>
+      </c>
+      <c r="BR39">
+        <v>1000</v>
+      </c>
+      <c r="BS39">
+        <v>2.26</v>
+      </c>
+      <c r="BT39">
+        <v>1000</v>
+      </c>
+      <c r="BU39">
         <v>5.3</v>
       </c>
-      <c r="BO39">
-        <v>4.6</v>
-      </c>
-      <c r="BP39">
-        <v>15.5</v>
-      </c>
-      <c r="BQ39">
-        <v>11</v>
-      </c>
-      <c r="BR39">
-        <v>26</v>
-      </c>
-      <c r="BS39">
-        <v>18.5</v>
-      </c>
-      <c r="BT39">
-        <v>7</v>
-      </c>
-      <c r="BU39">
-        <v>6</v>
-      </c>
       <c r="BV39">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW39">
-        <v>18.5</v>
+        <v>2.26</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>24</v>
+        <v>2.26</v>
       </c>
       <c r="BZ39">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA39">
-        <v>14.5</v>
+        <v>2.26</v>
       </c>
       <c r="CB39" t="s">
         <v>197</v>
@@ -10406,7 +10406,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I40">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J40">
         <v>5.4</v>
@@ -10415,7 +10415,7 @@
         <v>5.7</v>
       </c>
       <c r="L40">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M40">
         <v>1.04</v>
@@ -10427,16 +10427,16 @@
         <v>1.23</v>
       </c>
       <c r="P40">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q40">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R40">
         <v>1.53</v>
       </c>
       <c r="S40">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="T40">
         <v>2</v>
@@ -10469,7 +10469,7 @@
         <v>12.5</v>
       </c>
       <c r="AD40">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE40">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
         <v>9</v>
       </c>
       <c r="AG40">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH40">
         <v>27</v>
@@ -10487,7 +10487,7 @@
         <v>140</v>
       </c>
       <c r="AJ40">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK40">
         <v>15.5</v>
@@ -10517,7 +10517,7 @@
         <v>50</v>
       </c>
       <c r="AT40">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU40">
         <v>11</v>
@@ -10529,10 +10529,10 @@
         <v>42</v>
       </c>
       <c r="AX40">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY40">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ40">
         <v>20</v>
@@ -10568,13 +10568,13 @@
         <v>1000</v>
       </c>
       <c r="BK40">
-        <v>8</v>
+        <v>2.28</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BN40">
         <v>4.4</v>
@@ -10586,37 +10586,37 @@
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>6</v>
+        <v>2.08</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BT40">
         <v>1000</v>
       </c>
       <c r="BU40">
-        <v>8.4</v>
+        <v>2.36</v>
       </c>
       <c r="BV40">
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BZ40">
         <v>1000</v>
       </c>
       <c r="CA40">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="CB40" t="s">
         <v>197</v>
@@ -10648,7 +10648,7 @@
         <v>2</v>
       </c>
       <c r="I41">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J41">
         <v>4</v>
@@ -10657,28 +10657,28 @@
         <v>4.1</v>
       </c>
       <c r="L41">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M41">
         <v>1.05</v>
       </c>
       <c r="N41">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>1.23</v>
       </c>
       <c r="P41">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R41">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S41">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T41">
         <v>1.64</v>
@@ -10702,7 +10702,7 @@
         <v>14.5</v>
       </c>
       <c r="AA41">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB41">
         <v>18.5</v>
@@ -10726,7 +10726,7 @@
         <v>16.5</v>
       </c>
       <c r="AI41">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ41">
         <v>1000</v>
@@ -10750,7 +10750,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ41">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR41">
         <v>13</v>
@@ -10774,7 +10774,7 @@
         <v>27</v>
       </c>
       <c r="AY41">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ41">
         <v>14.5</v>
@@ -10801,7 +10801,7 @@
         <v>9.4</v>
       </c>
       <c r="BH41">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BI41">
         <v>3.25</v>
@@ -10816,49 +10816,49 @@
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BN41">
         <v>9</v>
       </c>
       <c r="BO41">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BP41">
         <v>44</v>
       </c>
       <c r="BQ41">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="BR41">
         <v>50</v>
       </c>
       <c r="BS41">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="BT41">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BU41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV41">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW41">
-        <v>9.6</v>
+        <v>3.55</v>
       </c>
       <c r="BX41">
         <v>34</v>
       </c>
       <c r="BY41">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="BZ41">
         <v>26</v>
       </c>
       <c r="CA41">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="CB41" t="s">
         <v>197</v>
@@ -10881,10 +10881,10 @@
         <v>194</v>
       </c>
       <c r="F42">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G42">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="H42">
         <v>19</v>
@@ -10917,22 +10917,22 @@
         <v>1.29</v>
       </c>
       <c r="R42">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="S42">
         <v>1.75</v>
       </c>
       <c r="T42">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U42">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V42">
         <v>1.05</v>
       </c>
       <c r="W42">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="X42">
         <v>1000</v>
@@ -10965,7 +10965,7 @@
         <v>14</v>
       </c>
       <c r="AH42">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI42">
         <v>1000</v>
@@ -11031,7 +11031,7 @@
         <v>11.5</v>
       </c>
       <c r="BD42">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE42">
         <v>42</v>
@@ -11052,13 +11052,13 @@
         <v>12.5</v>
       </c>
       <c r="BK42">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BN42">
         <v>4.3</v>
@@ -11076,31 +11076,31 @@
         <v>17.5</v>
       </c>
       <c r="BS42">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT42">
         <v>18.5</v>
       </c>
       <c r="BU42">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BV42">
         <v>1000</v>
       </c>
       <c r="BW42">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BZ42">
         <v>5.8</v>
       </c>
       <c r="CA42">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="CB42" t="s">
         <v>197</v>
@@ -11129,16 +11129,16 @@
         <v>1.08</v>
       </c>
       <c r="H43">
+        <v>34</v>
+      </c>
+      <c r="I43">
         <v>36</v>
-      </c>
-      <c r="I43">
-        <v>40</v>
       </c>
       <c r="J43">
         <v>22</v>
       </c>
       <c r="K43">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L43">
         <v>1.11</v>
@@ -11147,28 +11147,28 @@
         <v>1.01</v>
       </c>
       <c r="N43">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="O43">
         <v>1.04</v>
       </c>
       <c r="P43">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="Q43">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R43">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="S43">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T43">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U43">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V43">
         <v>1.02</v>
@@ -11201,7 +11201,7 @@
         <v>550</v>
       </c>
       <c r="AF43">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG43">
         <v>22</v>
@@ -11240,7 +11240,7 @@
         <v>55</v>
       </c>
       <c r="AS43">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AT43">
         <v>25</v>
@@ -11261,7 +11261,7 @@
         <v>19.5</v>
       </c>
       <c r="AZ43">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BA43">
         <v>48</v>
@@ -11276,34 +11276,34 @@
         <v>36</v>
       </c>
       <c r="BE43">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF43">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BG43">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BH43">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BI43">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BJ43">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BK43">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BL43">
         <v>120</v>
       </c>
       <c r="BM43">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN43">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BO43">
         <v>4.5</v>
@@ -11315,31 +11315,31 @@
         <v>4.8</v>
       </c>
       <c r="BR43">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BS43">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BT43">
         <v>36</v>
       </c>
       <c r="BU43">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BV43">
         <v>200</v>
       </c>
       <c r="BW43">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX43">
         <v>120</v>
       </c>
       <c r="BY43">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ43">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="CA43">
         <v>3.25</v>
@@ -11374,7 +11374,7 @@
         <v>2.22</v>
       </c>
       <c r="I44">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J44">
         <v>3.6</v>
@@ -11389,7 +11389,7 @@
         <v>1.07</v>
       </c>
       <c r="N44">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O44">
         <v>1.3</v>
@@ -11404,7 +11404,7 @@
         <v>1.41</v>
       </c>
       <c r="S44">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T44">
         <v>1.74</v>
@@ -11470,7 +11470,7 @@
         <v>38</v>
       </c>
       <c r="AO44">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP44">
         <v>14</v>
@@ -11521,7 +11521,7 @@
         <v>36</v>
       </c>
       <c r="BF44">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG44">
         <v>14</v>
@@ -11548,7 +11548,7 @@
         <v>6.8</v>
       </c>
       <c r="BO44">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BP44">
         <v>29</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -607,7 +607,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-09-14 19:56:13</t>
+    <t>2026-09-14 22:11:53</t>
   </si>
 </sst>
 </file>
@@ -1201,64 +1201,64 @@
         <v>154</v>
       </c>
       <c r="F2">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G2">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
         <v>4.7</v>
       </c>
       <c r="J2">
+        <v>3.6</v>
+      </c>
+      <c r="K2">
         <v>3.75</v>
       </c>
-      <c r="K2">
-        <v>3.9</v>
-      </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="O2">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="R2">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="S2">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
         <v>1.27</v>
       </c>
       <c r="W2">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X2">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
         <v>38</v>
@@ -1267,13 +1267,13 @@
         <v>110</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE2">
         <v>60</v>
@@ -1282,82 +1282,82 @@
         <v>13</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI2">
         <v>65</v>
       </c>
       <c r="AJ2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO2">
         <v>60</v>
       </c>
       <c r="AP2">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT2">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX2">
         <v>11</v>
       </c>
       <c r="AY2">
+        <v>9.6</v>
+      </c>
+      <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>10</v>
+      </c>
+      <c r="BB2">
+        <v>7.8</v>
+      </c>
+      <c r="BC2">
+        <v>18</v>
+      </c>
+      <c r="BD2">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>9</v>
-      </c>
-      <c r="BB2">
-        <v>18</v>
-      </c>
-      <c r="BC2">
-        <v>16.5</v>
-      </c>
-      <c r="BD2">
-        <v>8</v>
-      </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG2">
         <v>36</v>
@@ -1366,13 +1366,13 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1384,7 +1384,7 @@
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP2">
         <v>1000</v>
@@ -1402,7 +1402,7 @@
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1446,19 +1446,19 @@
         <v>2.28</v>
       </c>
       <c r="G3">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H3">
         <v>3.55</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
         <v>1.02</v>
@@ -1467,16 +1467,16 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P3">
         <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R3">
         <v>1.22</v>
@@ -1494,7 +1494,7 @@
         <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X3">
         <v>12</v>
@@ -1694,13 +1694,13 @@
         <v>1.67</v>
       </c>
       <c r="I4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="J4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L4">
         <v>1.26</v>
@@ -1724,7 +1724,7 @@
         <v>1.59</v>
       </c>
       <c r="S4">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T4">
         <v>1.68</v>
@@ -1733,25 +1733,25 @@
         <v>2.34</v>
       </c>
       <c r="V4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="W4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X4">
         <v>28</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AA4">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AB4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AC4">
         <v>10.5</v>
@@ -1769,10 +1769,10 @@
         <v>24</v>
       </c>
       <c r="AH4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ4">
         <v>130</v>
@@ -1817,94 +1817,94 @@
         <v>14.5</v>
       </c>
       <c r="AX4">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB4">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BC4">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE4">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF4">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG4">
         <v>6.8</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="CB4" t="s">
         <v>197</v>
@@ -1930,19 +1930,19 @@
         <v>1.91</v>
       </c>
       <c r="G5">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H5">
         <v>3.7</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J5">
         <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1951,7 +1951,7 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O5">
         <v>1.23</v>
@@ -1960,7 +1960,7 @@
         <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R5">
         <v>1.46</v>
@@ -2041,10 +2041,10 @@
         <v>15</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -2056,7 +2056,7 @@
         <v>14</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX5">
         <v>12</v>
@@ -2068,7 +2068,7 @@
         <v>14</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB5">
         <v>17</v>
@@ -2080,13 +2080,13 @@
         <v>21</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF5">
         <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>26</v>
+        <v>4.1</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2172,16 +2172,16 @@
         <v>3.1</v>
       </c>
       <c r="G6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H6">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I6">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J6">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K6">
         <v>3.5</v>
@@ -2193,7 +2193,7 @@
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
         <v>1.51</v>
@@ -2211,19 +2211,19 @@
         <v>4.8</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="U6">
         <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Y6">
         <v>15.5</v>
@@ -2235,13 +2235,13 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AC6">
         <v>11</v>
       </c>
       <c r="AD6">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AE6">
         <v>1000</v>
@@ -2286,7 +2286,7 @@
         <v>8.4</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AT6">
         <v>5.8</v>
@@ -2298,7 +2298,7 @@
         <v>7.4</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AX6">
         <v>10</v>
@@ -2307,28 +2307,28 @@
         <v>8</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2411,19 +2411,19 @@
         <v>159</v>
       </c>
       <c r="F7">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>2.46</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2435,13 +2435,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O7">
         <v>1.12</v>
       </c>
       <c r="P7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q7">
         <v>1.12</v>
@@ -2459,10 +2459,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2513,64 +2513,64 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO7">
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2761,52 +2761,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2895,19 +2895,19 @@
         <v>161</v>
       </c>
       <c r="F9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
         <v>990</v>
       </c>
-      <c r="H9">
-        <v>1.02</v>
-      </c>
-      <c r="I9">
-        <v>1000</v>
-      </c>
       <c r="J9">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2919,13 +2919,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O9">
         <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q9">
         <v>1.01</v>
@@ -2946,7 +2946,7 @@
         <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2997,64 +2997,64 @@
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO9">
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3137,46 +3137,46 @@
         <v>162</v>
       </c>
       <c r="F10">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="G10">
         <v>990</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="I10">
-        <v>990</v>
+        <v>1.65</v>
       </c>
       <c r="J10">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="O10">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="P10">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="Q10">
-        <v>1.37</v>
+        <v>2.08</v>
       </c>
       <c r="R10">
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3185,7 +3185,7 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="W10">
         <v>1.03</v>
@@ -3245,52 +3245,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3379,25 +3379,25 @@
         <v>163</v>
       </c>
       <c r="F11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H11">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="I11">
         <v>1.68</v>
       </c>
       <c r="J11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K11">
         <v>4.9</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M11">
         <v>1.04</v>
@@ -3424,13 +3424,13 @@
         <v>1.72</v>
       </c>
       <c r="U11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V11">
         <v>2.46</v>
       </c>
       <c r="W11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X11">
         <v>26</v>
@@ -3511,7 +3511,7 @@
         <v>13.5</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY11">
         <v>19</v>
@@ -3520,85 +3520,85 @@
         <v>16.5</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF11">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="BG11">
         <v>6.4</v>
       </c>
       <c r="BH11">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>3.25</v>
+        <v>2.04</v>
       </c>
       <c r="BJ11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK11">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>3.25</v>
+        <v>2.04</v>
       </c>
       <c r="BN11">
         <v>13</v>
       </c>
       <c r="BO11">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="BT11">
         <v>5.9</v>
       </c>
       <c r="BU11">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="BV11">
         <v>13.5</v>
       </c>
       <c r="BW11">
-        <v>2.64</v>
+        <v>1.77</v>
       </c>
       <c r="BX11">
         <v>30</v>
       </c>
       <c r="BY11">
-        <v>2.96</v>
+        <v>1.91</v>
       </c>
       <c r="BZ11">
         <v>20</v>
       </c>
       <c r="CA11">
-        <v>2.82</v>
+        <v>1.85</v>
       </c>
       <c r="CB11" t="s">
         <v>197</v>
@@ -3624,13 +3624,13 @@
         <v>4.2</v>
       </c>
       <c r="G12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H12">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I12">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J12">
         <v>3.5</v>
@@ -3642,7 +3642,7 @@
         <v>1.46</v>
       </c>
       <c r="M12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N12">
         <v>3.5</v>
@@ -3654,25 +3654,25 @@
         <v>1.83</v>
       </c>
       <c r="Q12">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R12">
         <v>1.32</v>
       </c>
       <c r="S12">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T12">
         <v>1.93</v>
       </c>
       <c r="U12">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V12">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X12">
         <v>12</v>
@@ -3690,7 +3690,7 @@
         <v>14</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD12">
         <v>10.5</v>
@@ -3774,7 +3774,7 @@
         <v>55</v>
       </c>
       <c r="BE12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF12">
         <v>55</v>
@@ -3786,10 +3786,10 @@
         <v>14</v>
       </c>
       <c r="BI12">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK12">
         <v>7.2</v>
@@ -3798,10 +3798,10 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="BN12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BO12">
         <v>5.6</v>
@@ -3816,10 +3816,10 @@
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="BT12">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BU12">
         <v>3.85</v>
@@ -3828,19 +3828,19 @@
         <v>20</v>
       </c>
       <c r="BW12">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BX12">
         <v>44</v>
       </c>
       <c r="BY12">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BZ12">
         <v>40</v>
       </c>
       <c r="CA12">
-        <v>4</v>
+        <v>1.89</v>
       </c>
       <c r="CB12" t="s">
         <v>197</v>
@@ -4016,7 +4016,7 @@
         <v>50</v>
       </c>
       <c r="BE13">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BF13">
         <v>48</v>
@@ -4105,19 +4105,19 @@
         <v>166</v>
       </c>
       <c r="F14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G14">
         <v>1000</v>
       </c>
       <c r="H14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I14">
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4153,10 +4153,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4213,52 +4213,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4347,13 +4347,13 @@
         <v>167</v>
       </c>
       <c r="F15">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G15">
         <v>2.98</v>
       </c>
       <c r="H15">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I15">
         <v>2.48</v>
@@ -4362,7 +4362,7 @@
         <v>4</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
         <v>1.22</v>
@@ -4383,10 +4383,10 @@
         <v>1.53</v>
       </c>
       <c r="R15">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="S15">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="T15">
         <v>1.5</v>
@@ -4395,19 +4395,19 @@
         <v>2.8</v>
       </c>
       <c r="V15">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W15">
         <v>1.5</v>
       </c>
       <c r="X15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA15">
         <v>34</v>
@@ -4425,7 +4425,7 @@
         <v>23</v>
       </c>
       <c r="AF15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG15">
         <v>14</v>
@@ -4455,7 +4455,7 @@
         <v>11.5</v>
       </c>
       <c r="AP15">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ15">
         <v>15</v>
@@ -4464,7 +4464,7 @@
         <v>17.5</v>
       </c>
       <c r="AS15">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT15">
         <v>16.5</v>
@@ -4488,13 +4488,13 @@
         <v>13</v>
       </c>
       <c r="BA15">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB15">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC15">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD15">
         <v>23</v>
@@ -4592,7 +4592,7 @@
         <v>2</v>
       </c>
       <c r="G16">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H16">
         <v>3.4</v>
@@ -4607,7 +4607,7 @@
         <v>4.5</v>
       </c>
       <c r="L16">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M16">
         <v>1.01</v>
@@ -4640,7 +4640,7 @@
         <v>1.38</v>
       </c>
       <c r="W16">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X16">
         <v>32</v>
@@ -4754,37 +4754,37 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>3.85</v>
+        <v>2.42</v>
       </c>
       <c r="BJ16">
         <v>10</v>
       </c>
       <c r="BK16">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="BN16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BO16">
         <v>4.5</v>
       </c>
       <c r="BP16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ16">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BR16">
         <v>28</v>
       </c>
       <c r="BS16">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="BT16">
         <v>9</v>
@@ -4796,19 +4796,19 @@
         <v>32</v>
       </c>
       <c r="BW16">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="BX16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY16">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="BZ16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA16">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="CB16" t="s">
         <v>197</v>
@@ -4831,19 +4831,19 @@
         <v>169</v>
       </c>
       <c r="F17">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G17">
-        <v>990</v>
+        <v>4.8</v>
       </c>
       <c r="H17">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I17">
-        <v>990</v>
+        <v>55</v>
       </c>
       <c r="J17">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>950</v>
@@ -4879,10 +4879,10 @@
         <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4939,52 +4939,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -5073,19 +5073,19 @@
         <v>170</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="G18">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J18">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5121,10 +5121,10 @@
         <v>1.11</v>
       </c>
       <c r="V18">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5181,52 +5181,52 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -5315,22 +5315,22 @@
         <v>171</v>
       </c>
       <c r="F19">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="G19">
-        <v>990</v>
+        <v>2.4</v>
       </c>
       <c r="H19">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="I19">
-        <v>990</v>
+        <v>48</v>
       </c>
       <c r="J19">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5363,10 +5363,10 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5423,52 +5423,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5566,16 +5566,16 @@
         <v>3.25</v>
       </c>
       <c r="I20">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J20">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K20">
         <v>3.85</v>
       </c>
       <c r="L20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M20">
         <v>1.05</v>
@@ -5587,7 +5587,7 @@
         <v>1.25</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q20">
         <v>1.76</v>
@@ -5605,10 +5605,10 @@
         <v>2.36</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W20">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X20">
         <v>18.5</v>
@@ -5799,19 +5799,19 @@
         <v>173</v>
       </c>
       <c r="F21">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="G21">
-        <v>990</v>
+        <v>4.2</v>
       </c>
       <c r="H21">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I21">
         <v>990</v>
       </c>
       <c r="J21">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -5847,10 +5847,10 @@
         <v>1.11</v>
       </c>
       <c r="V21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5907,52 +5907,52 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
         <v>1.01</v>
@@ -6125,7 +6125,7 @@
         <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI22">
         <v>65</v>
@@ -6182,7 +6182,7 @@
         <v>18</v>
       </c>
       <c r="BA22">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB22">
         <v>36</v>
@@ -6203,22 +6203,22 @@
         <v>26</v>
       </c>
       <c r="BH22">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="BI22">
         <v>2.76</v>
       </c>
       <c r="BJ22">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BK22">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL22">
         <v>190</v>
       </c>
       <c r="BM22">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BN22">
         <v>5.4</v>
@@ -6227,40 +6227,40 @@
         <v>4.9</v>
       </c>
       <c r="BP22">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BQ22">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR22">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BS22">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT22">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BU22">
         <v>5.5</v>
       </c>
       <c r="BV22">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW22">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BX22">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BY22">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BZ22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA22">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB22" t="s">
         <v>197</v>
@@ -6283,10 +6283,10 @@
         <v>175</v>
       </c>
       <c r="F23">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G23">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H23">
         <v>2.48</v>
@@ -6295,10 +6295,10 @@
         <v>2.92</v>
       </c>
       <c r="J23">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K23">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6307,142 +6307,142 @@
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="O23">
         <v>1.29</v>
       </c>
       <c r="P23">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q23">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R23">
         <v>1.33</v>
       </c>
       <c r="S23">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="T23">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="U23">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V23">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W23">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP23">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR23">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU23">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV23">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW23">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX23">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY23">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ23">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
         <v>1.03</v>
       </c>
       <c r="BD23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6558,7 +6558,7 @@
         <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R24">
         <v>1.47</v>
@@ -6588,19 +6588,19 @@
         <v>28</v>
       </c>
       <c r="AA24">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC24">
         <v>13</v>
       </c>
       <c r="AD24">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF24">
         <v>30</v>
@@ -6609,34 +6609,34 @@
         <v>18.5</v>
       </c>
       <c r="AH24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI24">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ24">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK24">
         <v>38</v>
       </c>
       <c r="AL24">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM24">
         <v>85</v>
       </c>
       <c r="AN24">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AO24">
         <v>20</v>
       </c>
       <c r="AP24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR24">
         <v>12</v>
@@ -6645,22 +6645,22 @@
         <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU24">
         <v>6.2</v>
       </c>
       <c r="AV24">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW24">
         <v>14.5</v>
       </c>
       <c r="AX24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY24">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ24">
         <v>9.6</v>
@@ -6669,7 +6669,7 @@
         <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
         <v>18.5</v>
@@ -6678,13 +6678,13 @@
         <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
         <v>12.5</v>
       </c>
       <c r="BG24">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6797,10 +6797,10 @@
         <v>1.15</v>
       </c>
       <c r="P25">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Q25">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="R25">
         <v>1.71</v>
@@ -6821,7 +6821,7 @@
         <v>1.92</v>
       </c>
       <c r="X25">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="Y25">
         <v>1000</v>
@@ -6836,7 +6836,7 @@
         <v>19</v>
       </c>
       <c r="AC25">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
         <v>20</v>
@@ -6881,25 +6881,25 @@
         <v>16</v>
       </c>
       <c r="AR25">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AS25">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AT25">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="AU25">
         <v>8</v>
       </c>
       <c r="AV25">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="AW25">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AX25">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AY25">
         <v>8.4</v>
@@ -6908,25 +6908,25 @@
         <v>11</v>
       </c>
       <c r="BA25">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="BB25">
         <v>17</v>
       </c>
       <c r="BC25">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="BD25">
         <v>17.5</v>
       </c>
       <c r="BE25">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="BF25">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="BG25">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7117,52 +7117,52 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
         <v>1.01</v>
@@ -7395,16 +7395,16 @@
         <v>20</v>
       </c>
       <c r="BB27">
-        <v>34</v>
+        <v>4.2</v>
       </c>
       <c r="BC27">
         <v>21</v>
       </c>
       <c r="BD27">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE27">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF27">
         <v>15.5</v>
@@ -7493,7 +7493,7 @@
         <v>180</v>
       </c>
       <c r="F28">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G28">
         <v>6.6</v>
@@ -7619,37 +7619,37 @@
         <v>7.2</v>
       </c>
       <c r="AV28">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW28">
         <v>18.5</v>
       </c>
       <c r="AX28">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AY28">
         <v>20</v>
       </c>
       <c r="AZ28">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BA28">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB28">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BC28">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BD28">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BE28">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF28">
-        <v>120</v>
+        <v>7.8</v>
       </c>
       <c r="BG28">
         <v>13.5</v>
@@ -7780,7 +7780,7 @@
         <v>2.06</v>
       </c>
       <c r="U29">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V29">
         <v>1.12</v>
@@ -7789,13 +7789,13 @@
         <v>3.2</v>
       </c>
       <c r="X29">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y29">
         <v>29</v>
       </c>
       <c r="Z29">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA29">
         <v>350</v>
@@ -7840,7 +7840,7 @@
         <v>6.6</v>
       </c>
       <c r="AO29">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP29">
         <v>17</v>
@@ -7855,7 +7855,7 @@
         <v>48</v>
       </c>
       <c r="AT29">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU29">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>14</v>
       </c>
       <c r="BD29">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE29">
         <v>44</v>
@@ -7924,7 +7924,7 @@
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="BR29">
         <v>1000</v>
@@ -7977,19 +7977,19 @@
         <v>182</v>
       </c>
       <c r="F30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G30">
         <v>990</v>
       </c>
       <c r="H30">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I30">
         <v>990</v>
       </c>
       <c r="J30">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K30">
         <v>950</v>
@@ -8025,10 +8025,10 @@
         <v>1.11</v>
       </c>
       <c r="V30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8085,52 +8085,52 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
         <v>1.01</v>
@@ -8219,19 +8219,19 @@
         <v>183</v>
       </c>
       <c r="F31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G31">
         <v>990</v>
       </c>
       <c r="H31">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I31">
         <v>990</v>
       </c>
       <c r="J31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K31">
         <v>950</v>
@@ -8267,10 +8267,10 @@
         <v>1.11</v>
       </c>
       <c r="V31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W31">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8327,52 +8327,52 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
         <v>1.01</v>
@@ -8485,10 +8485,10 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="O32">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P32">
         <v>2.56</v>
@@ -8500,13 +8500,13 @@
         <v>1.67</v>
       </c>
       <c r="S32">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T32">
         <v>1.51</v>
       </c>
       <c r="U32">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="V32">
         <v>2.06</v>
@@ -8530,10 +8530,10 @@
         <v>1000</v>
       </c>
       <c r="AC32">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="AD32">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="AE32">
         <v>1000</v>
@@ -8569,58 +8569,58 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AP32">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AQ32">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AR32">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AS32">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AT32">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AU32">
         <v>7</v>
       </c>
       <c r="AV32">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AW32">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AX32">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AY32">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AZ32">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="BA32">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BB32">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BC32">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BD32">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BE32">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BG32">
-        <v>5.4</v>
+        <v>1.12</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8703,7 +8703,7 @@
         <v>185</v>
       </c>
       <c r="F33">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G33">
         <v>1.86</v>
@@ -8712,13 +8712,13 @@
         <v>4.7</v>
       </c>
       <c r="I33">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J33">
         <v>3.85</v>
       </c>
       <c r="K33">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8727,10 +8727,10 @@
         <v>1.02</v>
       </c>
       <c r="N33">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O33">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P33">
         <v>1.98</v>
@@ -8739,7 +8739,7 @@
         <v>1.77</v>
       </c>
       <c r="R33">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S33">
         <v>2.86</v>
@@ -8751,7 +8751,7 @@
         <v>1.98</v>
       </c>
       <c r="V33">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W33">
         <v>2.16</v>
@@ -8769,7 +8769,7 @@
         <v>1000</v>
       </c>
       <c r="AB33">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="AC33">
         <v>1000</v>
@@ -8784,7 +8784,7 @@
         <v>20</v>
       </c>
       <c r="AG33">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AH33">
         <v>1000</v>
@@ -8811,58 +8811,58 @@
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AQ33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AR33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AS33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AT33">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AU33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AV33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AW33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AX33">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AY33">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AZ33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BA33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BB33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BC33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BD33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BE33">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BF33">
-        <v>6.6</v>
+        <v>1.19</v>
       </c>
       <c r="BG33">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8951,7 +8951,7 @@
         <v>2.48</v>
       </c>
       <c r="H34">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I34">
         <v>3.3</v>
@@ -8960,10 +8960,10 @@
         <v>3.55</v>
       </c>
       <c r="K34">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L34">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M34">
         <v>1.06</v>
@@ -8996,7 +8996,7 @@
         <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X34">
         <v>21</v>
@@ -9199,7 +9199,7 @@
         <v>990</v>
       </c>
       <c r="J35">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9211,16 +9211,16 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O35">
         <v>1.15</v>
       </c>
       <c r="P35">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q35">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="R35">
         <v>1.18</v>
@@ -9235,10 +9235,10 @@
         <v>1.11</v>
       </c>
       <c r="V35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9295,52 +9295,52 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35">
         <v>1.01</v>
@@ -9429,7 +9429,7 @@
         <v>188</v>
       </c>
       <c r="F36">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G36">
         <v>1.71</v>
@@ -9438,7 +9438,7 @@
         <v>5.4</v>
       </c>
       <c r="I36">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J36">
         <v>4.2</v>
@@ -9477,13 +9477,13 @@
         <v>2.14</v>
       </c>
       <c r="V36">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W36">
         <v>2.4</v>
       </c>
       <c r="X36">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y36">
         <v>22</v>
@@ -9522,7 +9522,7 @@
         <v>17.5</v>
       </c>
       <c r="AK36">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL36">
         <v>38</v>
@@ -9579,10 +9579,10 @@
         <v>14.5</v>
       </c>
       <c r="BD36">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE36">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF36">
         <v>7.6</v>
@@ -9612,7 +9612,7 @@
         <v>1000</v>
       </c>
       <c r="BO36">
-        <v>3.65</v>
+        <v>1.67</v>
       </c>
       <c r="BP36">
         <v>1000</v>
@@ -9704,7 +9704,7 @@
         <v>2.36</v>
       </c>
       <c r="Q37">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R37">
         <v>1.54</v>
@@ -9764,7 +9764,7 @@
         <v>1000</v>
       </c>
       <c r="AK37">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL37">
         <v>48</v>
@@ -9773,7 +9773,7 @@
         <v>70</v>
       </c>
       <c r="AN37">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO37">
         <v>12</v>
@@ -9922,7 +9922,7 @@
         <v>2.02</v>
       </c>
       <c r="I38">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J38">
         <v>4</v>
@@ -9961,7 +9961,7 @@
         <v>2.4</v>
       </c>
       <c r="V38">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W38">
         <v>1.34</v>
@@ -10200,7 +10200,7 @@
         <v>1.64</v>
       </c>
       <c r="U39">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
         <v>1.4</v>
@@ -10254,7 +10254,7 @@
         <v>32</v>
       </c>
       <c r="AM39">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN39">
         <v>14</v>
@@ -10281,7 +10281,7 @@
         <v>7.6</v>
       </c>
       <c r="AV39">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW39">
         <v>30</v>
@@ -10338,7 +10338,7 @@
         <v>1000</v>
       </c>
       <c r="BO39">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="BP39">
         <v>1000</v>
@@ -10356,7 +10356,7 @@
         <v>1000</v>
       </c>
       <c r="BU39">
-        <v>5.3</v>
+        <v>1.81</v>
       </c>
       <c r="BV39">
         <v>1000</v>
@@ -10406,13 +10406,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I40">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J40">
         <v>5.4</v>
       </c>
       <c r="K40">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L40">
         <v>1.33</v>
@@ -10421,7 +10421,7 @@
         <v>1.04</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O40">
         <v>1.23</v>
@@ -10442,7 +10442,7 @@
         <v>2</v>
       </c>
       <c r="U40">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V40">
         <v>1.11</v>
@@ -10469,7 +10469,7 @@
         <v>12.5</v>
       </c>
       <c r="AD40">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE40">
         <v>1000</v>
@@ -10508,22 +10508,22 @@
         <v>18.5</v>
       </c>
       <c r="AQ40">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR40">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS40">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="AT40">
         <v>8.6</v>
       </c>
       <c r="AU40">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV40">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW40">
         <v>42</v>
@@ -10556,7 +10556,7 @@
         <v>5.2</v>
       </c>
       <c r="BG40">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10639,13 +10639,13 @@
         <v>193</v>
       </c>
       <c r="F41">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G41">
         <v>3.95</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I41">
         <v>2.02</v>
@@ -10678,7 +10678,7 @@
         <v>1.54</v>
       </c>
       <c r="S41">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T41">
         <v>1.64</v>
@@ -10687,7 +10687,7 @@
         <v>2.46</v>
       </c>
       <c r="V41">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W41">
         <v>1.33</v>
@@ -10753,7 +10753,7 @@
         <v>11</v>
       </c>
       <c r="AR41">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS41">
         <v>21</v>
@@ -10774,7 +10774,7 @@
         <v>27</v>
       </c>
       <c r="AY41">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ41">
         <v>14.5</v>
@@ -10795,7 +10795,7 @@
         <v>60</v>
       </c>
       <c r="BF41">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BG41">
         <v>9.4</v>
@@ -10920,13 +10920,13 @@
         <v>2.24</v>
       </c>
       <c r="S42">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="T42">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U42">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V42">
         <v>1.05</v>
@@ -10935,10 +10935,10 @@
         <v>6.4</v>
       </c>
       <c r="X42">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="Y42">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z42">
         <v>1000</v>
@@ -10947,13 +10947,13 @@
         <v>1000</v>
       </c>
       <c r="AB42">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC42">
         <v>25</v>
       </c>
       <c r="AD42">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE42">
         <v>1000</v>
@@ -10998,7 +10998,7 @@
         <v>48</v>
       </c>
       <c r="AS42">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AT42">
         <v>15</v>
@@ -11052,7 +11052,7 @@
         <v>12.5</v>
       </c>
       <c r="BK42">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL42">
         <v>1000</v>
@@ -11082,7 +11082,7 @@
         <v>18.5</v>
       </c>
       <c r="BU42">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BV42">
         <v>1000</v>
@@ -11138,7 +11138,7 @@
         <v>22</v>
       </c>
       <c r="K43">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L43">
         <v>1.11</v>
@@ -11153,7 +11153,7 @@
         <v>1.04</v>
       </c>
       <c r="P43">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q43">
         <v>1.14</v>
@@ -11165,10 +11165,10 @@
         <v>1.38</v>
       </c>
       <c r="T43">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U43">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V43">
         <v>1.02</v>
@@ -11195,7 +11195,7 @@
         <v>70</v>
       </c>
       <c r="AD43">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="AE43">
         <v>550</v>
@@ -11225,25 +11225,25 @@
         <v>1000</v>
       </c>
       <c r="AN43">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AO43">
         <v>340</v>
       </c>
       <c r="AP43">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AQ43">
         <v>46</v>
       </c>
       <c r="AR43">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AS43">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AT43">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU43">
         <v>48</v>
@@ -11261,7 +11261,7 @@
         <v>19.5</v>
       </c>
       <c r="AZ43">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BA43">
         <v>48</v>
@@ -11282,25 +11282,25 @@
         <v>1.67</v>
       </c>
       <c r="BG43">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BH43">
         <v>10.5</v>
       </c>
       <c r="BI43">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="BJ43">
         <v>15.5</v>
       </c>
       <c r="BK43">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL43">
         <v>120</v>
       </c>
       <c r="BM43">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN43">
         <v>5.2</v>
@@ -11321,7 +11321,7 @@
         <v>6.4</v>
       </c>
       <c r="BT43">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BU43">
         <v>8</v>
@@ -11330,13 +11330,13 @@
         <v>200</v>
       </c>
       <c r="BW43">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX43">
         <v>120</v>
       </c>
       <c r="BY43">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ43">
         <v>3.7</v>
@@ -11521,7 +11521,7 @@
         <v>36</v>
       </c>
       <c r="BF44">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG44">
         <v>14</v>
@@ -11530,7 +11530,7 @@
         <v>3.5</v>
       </c>
       <c r="BI44">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ44">
         <v>9.800000000000001</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
   <si>
     <t>League</t>
   </si>
@@ -256,18 +256,15 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Spanish La Liga</t>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
+    <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
     <t>Venezuelan Primera Division</t>
   </si>
   <si>
-    <t>Bolivian Liga de Futbol Profesional</t>
-  </si>
-  <si>
-    <t>CONMEBOL Copa Libertadores</t>
-  </si>
-  <si>
     <t>Brazilian Serie A</t>
   </si>
   <si>
@@ -277,12 +274,6 @@
     <t>2026-09-16</t>
   </si>
   <si>
-    <t>19:30:00</t>
-  </si>
-  <si>
-    <t>21:00:00</t>
-  </si>
-  <si>
     <t>22:00:00</t>
   </si>
   <si>
@@ -298,12 +289,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Portuguesa FC</t>
-  </si>
-  <si>
     <t>Nacional Potosi</t>
   </si>
   <si>
@@ -325,12 +310,6 @@
     <t>Metropolitanos</t>
   </si>
   <si>
-    <t>Racing Santander</t>
-  </si>
-  <si>
-    <t>Estudiantes de Merida</t>
-  </si>
-  <si>
     <t>Always Ready</t>
   </si>
   <si>
@@ -352,7 +331,7 @@
     <t>Caracas</t>
   </si>
   <si>
-    <t>2026-09-16 18:32:21</t>
+    <t>2026-09-16 20:49:16</t>
   </si>
 </sst>
 </file>
@@ -684,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -934,31 +913,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
         <v>86</v>
       </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F2">
+        <v>110</v>
+      </c>
+      <c r="G2">
+        <v>1000</v>
+      </c>
+      <c r="H2">
         <v>1.01</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>1.01</v>
       </c>
-      <c r="H2">
-        <v>1000</v>
-      </c>
-      <c r="I2">
-        <v>1000</v>
-      </c>
       <c r="J2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <v>1000</v>
@@ -982,23 +961,23 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V2">
+        <v>100</v>
+      </c>
+      <c r="W2">
         <v>1.01</v>
       </c>
-      <c r="W2">
-        <v>500</v>
-      </c>
       <c r="X2">
         <v>1000</v>
       </c>
@@ -1009,7 +988,7 @@
         <v>1000</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>1.6</v>
       </c>
       <c r="AB2">
         <v>1000</v>
@@ -1021,7 +1000,7 @@
         <v>1000</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AF2">
         <v>1000</v>
@@ -1048,64 +1027,64 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="AP2">
-        <v>220</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="AR2">
-        <v>220</v>
+        <v>12.5</v>
       </c>
       <c r="AS2">
-        <v>220</v>
+        <v>1.57</v>
       </c>
       <c r="AT2">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="AU2">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="AV2">
-        <v>220</v>
+        <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>220</v>
+        <v>6</v>
       </c>
       <c r="AX2">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="AY2">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="AZ2">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="BB2">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="BC2">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="BD2">
-        <v>220</v>
+        <v>12.5</v>
       </c>
       <c r="BE2">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="BH2">
         <v>0</v>
@@ -1168,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1176,241 +1155,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
         <v>86</v>
       </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
       <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+      <c r="G3">
+        <v>70</v>
+      </c>
+      <c r="H3">
+        <v>1.23</v>
+      </c>
+      <c r="I3">
+        <v>1.24</v>
+      </c>
+      <c r="J3">
+        <v>5.8</v>
+      </c>
+      <c r="K3">
+        <v>5.9</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>1.48</v>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>5</v>
+      </c>
+      <c r="W3">
+        <v>1.02</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1.64</v>
+      </c>
+      <c r="AE3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>6</v>
+      </c>
+      <c r="AI3">
+        <v>38</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
         <v>95</v>
       </c>
-      <c r="E3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3">
-        <v>1.6</v>
-      </c>
-      <c r="G3">
-        <v>1.61</v>
-      </c>
-      <c r="H3">
-        <v>6.8</v>
-      </c>
-      <c r="I3">
-        <v>7.6</v>
-      </c>
-      <c r="J3">
-        <v>4.1</v>
-      </c>
-      <c r="K3">
-        <v>4.3</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>7.6</v>
-      </c>
-      <c r="O3">
-        <v>1.14</v>
-      </c>
-      <c r="P3">
-        <v>2.5</v>
-      </c>
-      <c r="Q3">
-        <v>1.65</v>
-      </c>
-      <c r="R3">
-        <v>1.42</v>
-      </c>
-      <c r="S3">
-        <v>3.2</v>
-      </c>
-      <c r="T3">
-        <v>1.51</v>
-      </c>
-      <c r="U3">
-        <v>2.8</v>
-      </c>
-      <c r="V3">
-        <v>1.15</v>
-      </c>
-      <c r="W3">
-        <v>2.66</v>
-      </c>
-      <c r="X3">
-        <v>1000</v>
-      </c>
-      <c r="Y3">
-        <v>1000</v>
-      </c>
-      <c r="Z3">
-        <v>1000</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
-        <v>8</v>
-      </c>
-      <c r="AC3">
-        <v>7</v>
-      </c>
-      <c r="AD3">
-        <v>13.5</v>
-      </c>
-      <c r="AE3">
-        <v>55</v>
-      </c>
-      <c r="AF3">
-        <v>8</v>
-      </c>
-      <c r="AG3">
-        <v>7.2</v>
-      </c>
-      <c r="AH3">
-        <v>14</v>
-      </c>
-      <c r="AI3">
-        <v>55</v>
-      </c>
-      <c r="AJ3">
-        <v>17</v>
-      </c>
-      <c r="AK3">
-        <v>18.5</v>
-      </c>
-      <c r="AL3">
-        <v>36</v>
-      </c>
       <c r="AM3">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AN3">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP3">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="AR3">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AT3">
+        <v>9</v>
+      </c>
+      <c r="AU3">
+        <v>8.6</v>
+      </c>
+      <c r="AV3">
+        <v>1.58</v>
+      </c>
+      <c r="AW3">
         <v>7.4</v>
       </c>
-      <c r="AU3">
-        <v>6.4</v>
-      </c>
-      <c r="AV3">
-        <v>12</v>
-      </c>
-      <c r="AW3">
-        <v>42</v>
-      </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AY3">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BB3">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="BC3">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="BD3">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BE3">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="BF3">
-        <v>15.5</v>
+        <v>300</v>
       </c>
       <c r="BG3">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1418,241 +1397,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
         <v>86</v>
       </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>1.1</v>
+      </c>
+      <c r="G4">
+        <v>1.11</v>
+      </c>
+      <c r="H4">
+        <v>150</v>
+      </c>
+      <c r="I4">
+        <v>1000</v>
+      </c>
+      <c r="J4">
+        <v>8.6</v>
+      </c>
+      <c r="K4">
+        <v>15</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>1.25</v>
+      </c>
+      <c r="O4">
+        <v>4.2</v>
+      </c>
+      <c r="P4">
+        <v>1.01</v>
+      </c>
+      <c r="Q4">
+        <v>55</v>
+      </c>
+      <c r="R4">
+        <v>1.01</v>
+      </c>
+      <c r="S4">
+        <v>180</v>
+      </c>
+      <c r="T4">
+        <v>1.52</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.01</v>
+      </c>
+      <c r="W4">
+        <v>10</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1.27</v>
+      </c>
+      <c r="AC4">
+        <v>120</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>48</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>5.1</v>
+      </c>
+      <c r="AQ4">
+        <v>5.1</v>
+      </c>
+      <c r="AR4">
+        <v>5.1</v>
+      </c>
+      <c r="AS4">
+        <v>5.1</v>
+      </c>
+      <c r="AT4">
+        <v>1.22</v>
+      </c>
+      <c r="AU4">
+        <v>10</v>
+      </c>
+      <c r="AV4">
+        <v>110</v>
+      </c>
+      <c r="AW4">
+        <v>9.4</v>
+      </c>
+      <c r="AX4">
+        <v>4.9</v>
+      </c>
+      <c r="AY4">
+        <v>5.3</v>
+      </c>
+      <c r="AZ4">
+        <v>5.1</v>
+      </c>
+      <c r="BA4">
+        <v>5.5</v>
+      </c>
+      <c r="BB4">
+        <v>5.3</v>
+      </c>
+      <c r="BC4">
+        <v>5.3</v>
+      </c>
+      <c r="BD4">
+        <v>5.1</v>
+      </c>
+      <c r="BE4">
+        <v>5.3</v>
+      </c>
+      <c r="BF4">
+        <v>5.3</v>
+      </c>
+      <c r="BG4">
+        <v>5.5</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
         <v>105</v>
-      </c>
-      <c r="F4">
-        <v>3.1</v>
-      </c>
-      <c r="G4">
-        <v>3.2</v>
-      </c>
-      <c r="H4">
-        <v>2.36</v>
-      </c>
-      <c r="I4">
-        <v>2.4</v>
-      </c>
-      <c r="J4">
-        <v>3.7</v>
-      </c>
-      <c r="K4">
-        <v>3.8</v>
-      </c>
-      <c r="L4">
-        <v>1.31</v>
-      </c>
-      <c r="M4">
-        <v>1.04</v>
-      </c>
-      <c r="N4">
-        <v>5.2</v>
-      </c>
-      <c r="O4">
-        <v>1.22</v>
-      </c>
-      <c r="P4">
-        <v>2.38</v>
-      </c>
-      <c r="Q4">
-        <v>1.7</v>
-      </c>
-      <c r="R4">
-        <v>1.55</v>
-      </c>
-      <c r="S4">
-        <v>2.72</v>
-      </c>
-      <c r="T4">
-        <v>1.58</v>
-      </c>
-      <c r="U4">
-        <v>2.58</v>
-      </c>
-      <c r="V4">
-        <v>1.71</v>
-      </c>
-      <c r="W4">
-        <v>1.45</v>
-      </c>
-      <c r="X4">
-        <v>22</v>
-      </c>
-      <c r="Y4">
-        <v>14.5</v>
-      </c>
-      <c r="Z4">
-        <v>18</v>
-      </c>
-      <c r="AA4">
-        <v>34</v>
-      </c>
-      <c r="AB4">
-        <v>16</v>
-      </c>
-      <c r="AC4">
-        <v>9</v>
-      </c>
-      <c r="AD4">
-        <v>12</v>
-      </c>
-      <c r="AE4">
-        <v>23</v>
-      </c>
-      <c r="AF4">
-        <v>26</v>
-      </c>
-      <c r="AG4">
-        <v>14</v>
-      </c>
-      <c r="AH4">
-        <v>15</v>
-      </c>
-      <c r="AI4">
-        <v>32</v>
-      </c>
-      <c r="AJ4">
-        <v>55</v>
-      </c>
-      <c r="AK4">
-        <v>32</v>
-      </c>
-      <c r="AL4">
-        <v>38</v>
-      </c>
-      <c r="AM4">
-        <v>60</v>
-      </c>
-      <c r="AN4">
-        <v>21</v>
-      </c>
-      <c r="AO4">
-        <v>13</v>
-      </c>
-      <c r="AP4">
-        <v>19</v>
-      </c>
-      <c r="AQ4">
-        <v>12.5</v>
-      </c>
-      <c r="AR4">
-        <v>15.5</v>
-      </c>
-      <c r="AS4">
-        <v>29</v>
-      </c>
-      <c r="AT4">
-        <v>15.5</v>
-      </c>
-      <c r="AU4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV4">
-        <v>10</v>
-      </c>
-      <c r="AW4">
-        <v>19</v>
-      </c>
-      <c r="AX4">
-        <v>22</v>
-      </c>
-      <c r="AY4">
-        <v>12.5</v>
-      </c>
-      <c r="AZ4">
-        <v>13.5</v>
-      </c>
-      <c r="BA4">
-        <v>25</v>
-      </c>
-      <c r="BB4">
-        <v>28</v>
-      </c>
-      <c r="BC4">
-        <v>27</v>
-      </c>
-      <c r="BD4">
-        <v>30</v>
-      </c>
-      <c r="BE4">
-        <v>46</v>
-      </c>
-      <c r="BF4">
-        <v>19</v>
-      </c>
-      <c r="BG4">
-        <v>12</v>
-      </c>
-      <c r="BH4">
-        <v>5</v>
-      </c>
-      <c r="BI4">
-        <v>3.75</v>
-      </c>
-      <c r="BJ4">
-        <v>9</v>
-      </c>
-      <c r="BK4">
-        <v>7.2</v>
-      </c>
-      <c r="BL4">
-        <v>90</v>
-      </c>
-      <c r="BM4">
-        <v>5.2</v>
-      </c>
-      <c r="BN4">
-        <v>7.8</v>
-      </c>
-      <c r="BO4">
-        <v>5.8</v>
-      </c>
-      <c r="BP4">
-        <v>23</v>
-      </c>
-      <c r="BQ4">
-        <v>4.4</v>
-      </c>
-      <c r="BR4">
-        <v>29</v>
-      </c>
-      <c r="BS4">
-        <v>4.6</v>
-      </c>
-      <c r="BT4">
-        <v>6.8</v>
-      </c>
-      <c r="BU4">
-        <v>4.9</v>
-      </c>
-      <c r="BV4">
-        <v>18.5</v>
-      </c>
-      <c r="BW4">
-        <v>4.2</v>
-      </c>
-      <c r="BX4">
-        <v>25</v>
-      </c>
-      <c r="BY4">
-        <v>4.5</v>
-      </c>
-      <c r="BZ4">
-        <v>20</v>
-      </c>
-      <c r="CA4">
-        <v>4.3</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1660,483 +1639,483 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F5">
+        <v>2.54</v>
+      </c>
+      <c r="G5">
+        <v>2.6</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4.3</v>
+      </c>
+      <c r="J5">
         <v>2.66</v>
       </c>
-      <c r="G5">
+      <c r="K5">
         <v>2.7</v>
       </c>
-      <c r="H5">
-        <v>3.2</v>
-      </c>
-      <c r="I5">
-        <v>3.25</v>
-      </c>
-      <c r="J5">
-        <v>3.15</v>
-      </c>
-      <c r="K5">
-        <v>3.2</v>
-      </c>
       <c r="L5">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.58</v>
+        <v>4.5</v>
       </c>
       <c r="Q5">
-        <v>2.68</v>
+        <v>1.28</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="S5">
-        <v>5.6</v>
+        <v>2.26</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="X5">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>4.7</v>
+      </c>
+      <c r="AD5">
         <v>7.8</v>
       </c>
-      <c r="AC5">
+      <c r="AE5">
+        <v>28</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>5.2</v>
+      </c>
+      <c r="AH5">
+        <v>8</v>
+      </c>
+      <c r="AI5">
+        <v>30</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>12.5</v>
+      </c>
+      <c r="AL5">
+        <v>19.5</v>
+      </c>
+      <c r="AM5">
+        <v>70</v>
+      </c>
+      <c r="AN5">
+        <v>22</v>
+      </c>
+      <c r="AO5">
+        <v>60</v>
+      </c>
+      <c r="AP5">
+        <v>36</v>
+      </c>
+      <c r="AQ5">
+        <v>36</v>
+      </c>
+      <c r="AR5">
+        <v>36</v>
+      </c>
+      <c r="AS5">
+        <v>36</v>
+      </c>
+      <c r="AT5">
+        <v>36</v>
+      </c>
+      <c r="AU5">
+        <v>4.3</v>
+      </c>
+      <c r="AV5">
         <v>7</v>
       </c>
-      <c r="AD5">
-        <v>14</v>
-      </c>
-      <c r="AE5">
-        <v>48</v>
-      </c>
-      <c r="AF5">
-        <v>15.5</v>
-      </c>
-      <c r="AG5">
-        <v>12.5</v>
-      </c>
-      <c r="AH5">
-        <v>22</v>
-      </c>
-      <c r="AI5">
-        <v>85</v>
-      </c>
-      <c r="AJ5">
-        <v>44</v>
-      </c>
-      <c r="AK5">
-        <v>38</v>
-      </c>
-      <c r="AL5">
-        <v>65</v>
-      </c>
-      <c r="AM5">
-        <v>210</v>
-      </c>
-      <c r="AN5">
-        <v>46</v>
-      </c>
-      <c r="AO5">
-        <v>75</v>
-      </c>
-      <c r="AP5">
-        <v>8.4</v>
-      </c>
-      <c r="AQ5">
-        <v>9</v>
-      </c>
-      <c r="AR5">
+      <c r="AW5">
+        <v>25</v>
+      </c>
+      <c r="AX5">
+        <v>36</v>
+      </c>
+      <c r="AY5">
+        <v>4.8</v>
+      </c>
+      <c r="AZ5">
+        <v>7.6</v>
+      </c>
+      <c r="BA5">
+        <v>23</v>
+      </c>
+      <c r="BB5">
+        <v>34</v>
+      </c>
+      <c r="BC5">
+        <v>11</v>
+      </c>
+      <c r="BD5">
         <v>17.5</v>
       </c>
-      <c r="AS5">
-        <v>55</v>
-      </c>
-      <c r="AT5">
-        <v>7.4</v>
-      </c>
-      <c r="AU5">
-        <v>6.8</v>
-      </c>
-      <c r="AV5">
-        <v>13.5</v>
-      </c>
-      <c r="AW5">
+      <c r="BE5">
+        <v>50</v>
+      </c>
+      <c r="BF5">
+        <v>20</v>
+      </c>
+      <c r="BG5">
         <v>42</v>
       </c>
-      <c r="AX5">
-        <v>14.5</v>
-      </c>
-      <c r="AY5">
-        <v>12</v>
-      </c>
-      <c r="AZ5">
-        <v>20</v>
-      </c>
-      <c r="BA5">
-        <v>60</v>
-      </c>
-      <c r="BB5">
-        <v>40</v>
-      </c>
-      <c r="BC5">
-        <v>34</v>
-      </c>
-      <c r="BD5">
-        <v>55</v>
-      </c>
-      <c r="BE5">
-        <v>90</v>
-      </c>
-      <c r="BF5">
-        <v>40</v>
-      </c>
-      <c r="BG5">
-        <v>50</v>
-      </c>
       <c r="BH5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F6">
-        <v>1.86</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1.94</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>4.6</v>
+        <v>1.14</v>
       </c>
       <c r="I6">
-        <v>5.1</v>
+        <v>1.17</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="K6">
-        <v>3.95</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.24</v>
+        <v>6.8</v>
       </c>
       <c r="W6">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>6.8</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>6.8</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
         <v>14</v>
       </c>
-      <c r="Y6">
-        <v>17.5</v>
-      </c>
-      <c r="Z6">
-        <v>42</v>
-      </c>
-      <c r="AA6">
-        <v>150</v>
-      </c>
-      <c r="AB6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD6">
-        <v>22</v>
-      </c>
-      <c r="AE6">
-        <v>85</v>
-      </c>
-      <c r="AF6">
+      <c r="AN6">
+        <v>36</v>
+      </c>
+      <c r="AO6">
+        <v>1.9</v>
+      </c>
+      <c r="AP6">
+        <v>14.5</v>
+      </c>
+      <c r="AQ6">
+        <v>14.5</v>
+      </c>
+      <c r="AR6">
+        <v>14.5</v>
+      </c>
+      <c r="AS6">
+        <v>14.5</v>
+      </c>
+      <c r="AT6">
+        <v>14.5</v>
+      </c>
+      <c r="AU6">
+        <v>14.5</v>
+      </c>
+      <c r="AV6">
+        <v>14.5</v>
+      </c>
+      <c r="AW6">
+        <v>6</v>
+      </c>
+      <c r="AX6">
+        <v>14.5</v>
+      </c>
+      <c r="AY6">
+        <v>14.5</v>
+      </c>
+      <c r="AZ6">
+        <v>14.5</v>
+      </c>
+      <c r="BA6">
+        <v>5.6</v>
+      </c>
+      <c r="BB6">
+        <v>14.5</v>
+      </c>
+      <c r="BC6">
+        <v>14.5</v>
+      </c>
+      <c r="BD6">
+        <v>14.5</v>
+      </c>
+      <c r="BE6">
         <v>10.5</v>
       </c>
-      <c r="AG6">
-        <v>10.5</v>
-      </c>
-      <c r="AH6">
-        <v>23</v>
-      </c>
-      <c r="AI6">
-        <v>95</v>
-      </c>
-      <c r="AJ6">
-        <v>20</v>
-      </c>
-      <c r="AK6">
-        <v>21</v>
-      </c>
-      <c r="AL6">
-        <v>44</v>
-      </c>
-      <c r="AM6">
-        <v>140</v>
-      </c>
-      <c r="AN6">
-        <v>13</v>
-      </c>
-      <c r="AO6">
-        <v>120</v>
-      </c>
-      <c r="AP6">
-        <v>12.5</v>
-      </c>
-      <c r="AQ6">
-        <v>15</v>
-      </c>
-      <c r="AR6">
-        <v>29</v>
-      </c>
-      <c r="AS6">
-        <v>85</v>
-      </c>
-      <c r="AT6">
-        <v>7.6</v>
-      </c>
-      <c r="AU6">
-        <v>7.8</v>
-      </c>
-      <c r="AV6">
-        <v>18</v>
-      </c>
-      <c r="AW6">
-        <v>48</v>
-      </c>
-      <c r="AX6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ6">
-        <v>18.5</v>
-      </c>
-      <c r="BA6">
-        <v>46</v>
-      </c>
-      <c r="BB6">
-        <v>17</v>
-      </c>
-      <c r="BC6">
-        <v>17.5</v>
-      </c>
-      <c r="BD6">
-        <v>32</v>
-      </c>
-      <c r="BE6">
-        <v>85</v>
-      </c>
       <c r="BF6">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="BG6">
-        <v>50</v>
+        <v>1.72</v>
       </c>
       <c r="BH6">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BI6">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BJ6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK6">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM6">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BN6">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BO6">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BP6">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BQ6">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BR6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BT6">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BU6">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BV6">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BW6">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY6">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BZ6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2144,109 +2123,109 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F7">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="G7">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K7">
         <v>4.2</v>
       </c>
       <c r="L7">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="O7">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="P7">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="Q7">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="R7">
+        <v>1.48</v>
+      </c>
+      <c r="S7">
+        <v>2.98</v>
+      </c>
+      <c r="T7">
         <v>1.47</v>
       </c>
-      <c r="S7">
-        <v>3</v>
-      </c>
-      <c r="T7">
-        <v>1.77</v>
-      </c>
       <c r="U7">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="X7">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AD7">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AG7">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AH7">
+        <v>13.5</v>
+      </c>
+      <c r="AI7">
+        <v>55</v>
+      </c>
+      <c r="AJ7">
         <v>17.5</v>
-      </c>
-      <c r="AI7">
-        <v>60</v>
-      </c>
-      <c r="AJ7">
-        <v>18.5</v>
       </c>
       <c r="AK7">
         <v>17</v>
@@ -2255,856 +2234,372 @@
         <v>32</v>
       </c>
       <c r="AM7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN7">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AO7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AQ7">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AR7">
+        <v>14</v>
+      </c>
+      <c r="AS7">
+        <v>14</v>
+      </c>
+      <c r="AT7">
+        <v>7.8</v>
+      </c>
+      <c r="AU7">
+        <v>6.4</v>
+      </c>
+      <c r="AV7">
+        <v>11.5</v>
+      </c>
+      <c r="AW7">
         <v>36</v>
       </c>
-      <c r="AS7">
-        <v>85</v>
-      </c>
-      <c r="AT7">
-        <v>9.4</v>
-      </c>
-      <c r="AU7">
-        <v>8.6</v>
-      </c>
-      <c r="AV7">
-        <v>17.5</v>
-      </c>
-      <c r="AW7">
-        <v>50</v>
-      </c>
       <c r="AX7">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AY7">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA7">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BB7">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC7">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD7">
+        <v>25</v>
+      </c>
+      <c r="BE7">
+        <v>70</v>
+      </c>
+      <c r="BF7">
+        <v>14</v>
+      </c>
+      <c r="BG7">
+        <v>48</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>13.5</v>
+      </c>
+      <c r="BJ7">
+        <v>5.7</v>
+      </c>
+      <c r="BK7">
+        <v>4.9</v>
+      </c>
+      <c r="BL7">
+        <v>960</v>
+      </c>
+      <c r="BM7">
+        <v>13</v>
+      </c>
+      <c r="BN7">
+        <v>1.79</v>
+      </c>
+      <c r="BO7">
+        <v>1.73</v>
+      </c>
+      <c r="BP7">
+        <v>7.2</v>
+      </c>
+      <c r="BQ7">
+        <v>6</v>
+      </c>
+      <c r="BR7">
         <v>28</v>
       </c>
-      <c r="BE7">
-        <v>75</v>
-      </c>
-      <c r="BF7">
-        <v>9.4</v>
-      </c>
-      <c r="BG7">
-        <v>50</v>
-      </c>
-      <c r="BH7">
-        <v>3.8</v>
-      </c>
-      <c r="BI7">
-        <v>3.6</v>
-      </c>
-      <c r="BJ7">
-        <v>9.4</v>
-      </c>
-      <c r="BK7">
-        <v>8.4</v>
-      </c>
-      <c r="BL7">
-        <v>120</v>
-      </c>
-      <c r="BM7">
-        <v>16.5</v>
-      </c>
-      <c r="BN7">
-        <v>4.5</v>
-      </c>
-      <c r="BO7">
-        <v>4.1</v>
-      </c>
-      <c r="BP7">
-        <v>11.5</v>
-      </c>
-      <c r="BQ7">
-        <v>10</v>
-      </c>
-      <c r="BR7">
-        <v>24</v>
-      </c>
       <c r="BS7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BT7">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>13.5</v>
+      </c>
+      <c r="BX7">
+        <v>60</v>
+      </c>
+      <c r="BY7">
         <v>40</v>
       </c>
-      <c r="BW7">
-        <v>20</v>
-      </c>
-      <c r="BX7">
+      <c r="BZ7">
         <v>46</v>
       </c>
-      <c r="BY7">
-        <v>24</v>
-      </c>
-      <c r="BZ7">
-        <v>17.5</v>
-      </c>
       <c r="CA7">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="CB7" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F8">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="G8">
-        <v>1.94</v>
+        <v>2.92</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="N8">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="P8">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S8">
-        <v>3.55</v>
+        <v>2.32</v>
       </c>
       <c r="T8">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
-        <v>2.06</v>
+        <v>1.52</v>
       </c>
       <c r="X8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y8">
+        <v>9.6</v>
+      </c>
+      <c r="Z8">
+        <v>21</v>
+      </c>
+      <c r="AA8">
+        <v>55</v>
+      </c>
+      <c r="AB8">
+        <v>9</v>
+      </c>
+      <c r="AC8">
+        <v>7</v>
+      </c>
+      <c r="AD8">
         <v>15</v>
       </c>
-      <c r="Y8">
-        <v>17</v>
-      </c>
-      <c r="Z8">
-        <v>38</v>
-      </c>
-      <c r="AA8">
-        <v>200</v>
-      </c>
-      <c r="AB8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8">
-        <v>19.5</v>
-      </c>
       <c r="AE8">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AF8">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AH8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI8">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AJ8">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="AK8">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AL8">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AM8">
-        <v>390</v>
+        <v>190</v>
       </c>
       <c r="AN8">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="AO8">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AP8">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="AR8">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="AS8">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="AT8">
         <v>8</v>
       </c>
       <c r="AU8">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW8">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AX8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AY8">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AZ8">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BA8">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="BB8">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="BC8">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="BD8">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BE8">
-        <v>9.800000000000001</v>
+        <v>140</v>
       </c>
       <c r="BF8">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BG8">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BH8">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>29</v>
+        <v>910</v>
       </c>
       <c r="BS8">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>25</v>
+        <v>960</v>
       </c>
       <c r="CA8">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:80">
-      <c r="A9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F9">
-        <v>2.34</v>
-      </c>
-      <c r="G9">
-        <v>2.4</v>
-      </c>
-      <c r="H9">
-        <v>3.5</v>
-      </c>
-      <c r="I9">
-        <v>3.6</v>
-      </c>
-      <c r="J9">
-        <v>3.3</v>
-      </c>
-      <c r="K9">
-        <v>3.45</v>
-      </c>
-      <c r="L9">
-        <v>1.47</v>
-      </c>
-      <c r="M9">
-        <v>1.09</v>
-      </c>
-      <c r="N9">
-        <v>3.35</v>
-      </c>
-      <c r="O9">
-        <v>1.41</v>
-      </c>
-      <c r="P9">
-        <v>1.77</v>
-      </c>
-      <c r="Q9">
-        <v>2.22</v>
-      </c>
-      <c r="R9">
-        <v>1.29</v>
-      </c>
-      <c r="S9">
-        <v>4.2</v>
-      </c>
-      <c r="T9">
-        <v>1.91</v>
-      </c>
-      <c r="U9">
-        <v>2.02</v>
-      </c>
-      <c r="V9">
-        <v>1.38</v>
-      </c>
-      <c r="W9">
-        <v>1.71</v>
-      </c>
-      <c r="X9">
-        <v>12</v>
-      </c>
-      <c r="Y9">
-        <v>12</v>
-      </c>
-      <c r="Z9">
-        <v>25</v>
-      </c>
-      <c r="AA9">
-        <v>70</v>
-      </c>
-      <c r="AB9">
-        <v>9</v>
-      </c>
-      <c r="AC9">
-        <v>7.4</v>
-      </c>
-      <c r="AD9">
-        <v>15</v>
-      </c>
-      <c r="AE9">
-        <v>48</v>
-      </c>
-      <c r="AF9">
-        <v>14.5</v>
-      </c>
-      <c r="AG9">
-        <v>12</v>
-      </c>
-      <c r="AH9">
-        <v>20</v>
-      </c>
-      <c r="AI9">
-        <v>60</v>
-      </c>
-      <c r="AJ9">
-        <v>34</v>
-      </c>
-      <c r="AK9">
-        <v>28</v>
-      </c>
-      <c r="AL9">
-        <v>48</v>
-      </c>
-      <c r="AM9">
-        <v>150</v>
-      </c>
-      <c r="AN9">
-        <v>26</v>
-      </c>
-      <c r="AO9">
-        <v>55</v>
-      </c>
-      <c r="AP9">
-        <v>10.5</v>
-      </c>
-      <c r="AQ9">
-        <v>10.5</v>
-      </c>
-      <c r="AR9">
-        <v>20</v>
-      </c>
-      <c r="AS9">
-        <v>50</v>
-      </c>
-      <c r="AT9">
-        <v>8</v>
-      </c>
-      <c r="AU9">
-        <v>6.8</v>
-      </c>
-      <c r="AV9">
-        <v>13</v>
-      </c>
-      <c r="AW9">
-        <v>38</v>
-      </c>
-      <c r="AX9">
-        <v>12</v>
-      </c>
-      <c r="AY9">
-        <v>10</v>
-      </c>
-      <c r="AZ9">
-        <v>17</v>
-      </c>
-      <c r="BA9">
-        <v>38</v>
-      </c>
-      <c r="BB9">
-        <v>27</v>
-      </c>
-      <c r="BC9">
-        <v>24</v>
-      </c>
-      <c r="BD9">
-        <v>38</v>
-      </c>
-      <c r="BE9">
-        <v>12</v>
-      </c>
-      <c r="BF9">
-        <v>20</v>
-      </c>
-      <c r="BG9">
-        <v>32</v>
-      </c>
-      <c r="BH9">
-        <v>3.1</v>
-      </c>
-      <c r="BI9">
-        <v>2.86</v>
-      </c>
-      <c r="BJ9">
-        <v>10.5</v>
-      </c>
-      <c r="BK9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL9">
-        <v>150</v>
-      </c>
-      <c r="BM9">
-        <v>13</v>
-      </c>
-      <c r="BN9">
-        <v>5.1</v>
-      </c>
-      <c r="BO9">
-        <v>4.6</v>
-      </c>
-      <c r="BP9">
-        <v>19</v>
-      </c>
-      <c r="BQ9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR9">
-        <v>36</v>
-      </c>
-      <c r="BS9">
-        <v>10</v>
-      </c>
-      <c r="BT9">
-        <v>6.6</v>
-      </c>
-      <c r="BU9">
-        <v>5.9</v>
-      </c>
-      <c r="BV9">
-        <v>32</v>
-      </c>
-      <c r="BW9">
-        <v>10</v>
-      </c>
-      <c r="BX9">
-        <v>48</v>
-      </c>
-      <c r="BY9">
-        <v>11</v>
-      </c>
-      <c r="BZ9">
-        <v>36</v>
-      </c>
-      <c r="CA9">
-        <v>10</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:80">
-      <c r="A10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F10">
-        <v>2.34</v>
-      </c>
-      <c r="G10">
-        <v>2.48</v>
-      </c>
-      <c r="H10">
-        <v>3.35</v>
-      </c>
-      <c r="I10">
-        <v>3.7</v>
-      </c>
-      <c r="J10">
-        <v>3.25</v>
-      </c>
-      <c r="K10">
-        <v>3.5</v>
-      </c>
-      <c r="L10">
-        <v>1.44</v>
-      </c>
-      <c r="M10">
-        <v>1.09</v>
-      </c>
-      <c r="N10">
-        <v>3.5</v>
-      </c>
-      <c r="O10">
-        <v>1.36</v>
-      </c>
-      <c r="P10">
-        <v>1.83</v>
-      </c>
-      <c r="Q10">
-        <v>2.06</v>
-      </c>
-      <c r="R10">
-        <v>1.32</v>
-      </c>
-      <c r="S10">
-        <v>3.75</v>
-      </c>
-      <c r="T10">
-        <v>1.84</v>
-      </c>
-      <c r="U10">
-        <v>2.06</v>
-      </c>
-      <c r="V10">
-        <v>1.37</v>
-      </c>
-      <c r="W10">
-        <v>1.68</v>
-      </c>
-      <c r="X10">
-        <v>12.5</v>
-      </c>
-      <c r="Y10">
-        <v>13</v>
-      </c>
-      <c r="Z10">
-        <v>25</v>
-      </c>
-      <c r="AA10">
-        <v>80</v>
-      </c>
-      <c r="AB10">
-        <v>10.5</v>
-      </c>
-      <c r="AC10">
-        <v>7.4</v>
-      </c>
-      <c r="AD10">
-        <v>15.5</v>
-      </c>
-      <c r="AE10">
-        <v>46</v>
-      </c>
-      <c r="AF10">
-        <v>16</v>
-      </c>
-      <c r="AG10">
-        <v>12.5</v>
-      </c>
-      <c r="AH10">
-        <v>18.5</v>
-      </c>
-      <c r="AI10">
-        <v>55</v>
-      </c>
-      <c r="AJ10">
-        <v>38</v>
-      </c>
-      <c r="AK10">
-        <v>28</v>
-      </c>
-      <c r="AL10">
-        <v>46</v>
-      </c>
-      <c r="AM10">
-        <v>300</v>
-      </c>
-      <c r="AN10">
-        <v>23</v>
-      </c>
-      <c r="AO10">
-        <v>55</v>
-      </c>
-      <c r="AP10">
-        <v>10.5</v>
-      </c>
-      <c r="AQ10">
-        <v>11</v>
-      </c>
-      <c r="AR10">
-        <v>21</v>
-      </c>
-      <c r="AS10">
-        <v>46</v>
-      </c>
-      <c r="AT10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU10">
-        <v>6.4</v>
-      </c>
-      <c r="AV10">
-        <v>12.5</v>
-      </c>
-      <c r="AW10">
-        <v>29</v>
-      </c>
-      <c r="AX10">
-        <v>13</v>
-      </c>
-      <c r="AY10">
-        <v>10.5</v>
-      </c>
-      <c r="AZ10">
-        <v>15</v>
-      </c>
-      <c r="BA10">
-        <v>38</v>
-      </c>
-      <c r="BB10">
-        <v>27</v>
-      </c>
-      <c r="BC10">
-        <v>21</v>
-      </c>
-      <c r="BD10">
-        <v>30</v>
-      </c>
-      <c r="BE10">
-        <v>75</v>
-      </c>
-      <c r="BF10">
-        <v>18.5</v>
-      </c>
-      <c r="BG10">
-        <v>29</v>
-      </c>
-      <c r="BH10">
-        <v>3.3</v>
-      </c>
-      <c r="BI10">
-        <v>2.94</v>
-      </c>
-      <c r="BJ10">
-        <v>10.5</v>
-      </c>
-      <c r="BK10">
-        <v>5.4</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>10.5</v>
-      </c>
-      <c r="BN10">
-        <v>5.2</v>
-      </c>
-      <c r="BO10">
-        <v>4.5</v>
-      </c>
-      <c r="BP10">
-        <v>18</v>
-      </c>
-      <c r="BQ10">
-        <v>7</v>
-      </c>
-      <c r="BR10">
-        <v>34</v>
-      </c>
-      <c r="BS10">
-        <v>8.4</v>
-      </c>
-      <c r="BT10">
-        <v>7</v>
-      </c>
-      <c r="BU10">
-        <v>5.7</v>
-      </c>
-      <c r="BV10">
-        <v>30</v>
-      </c>
-      <c r="BW10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX10">
-        <v>44</v>
-      </c>
-      <c r="BY10">
-        <v>9</v>
-      </c>
-      <c r="BZ10">
-        <v>32</v>
-      </c>
-      <c r="CA10">
-        <v>8.4</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
